--- a/templates/ERC000031/metadata_template_ERC000031.xlsx
+++ b/templates/ERC000031/metadata_template_ERC000031.xlsx
@@ -22,17 +22,17 @@
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="filtertype">'cv_sample'!$AS$1:$AS$7</definedName>
     <definedName name="frequencyofcleaning">'cv_sample'!$FK$1:$FK$5</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$EV$1:$EV$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$EV$1:$EV$294</definedName>
     <definedName name="heatingandcoolingsystemtype">'cv_sample'!$AT$1:$AT$5</definedName>
     <definedName name="indoorspace">'cv_sample'!$AR$1:$AR$8</definedName>
     <definedName name="indoorsurface">'cv_sample'!$AQ$1:$AQ$8</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="lighttype">'cv_sample'!$AV$1:$AV$3</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$I$1:$I$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$K$1:$K$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$X$1:$X$3</definedName>
     <definedName name="spacetypicalstate">'cv_sample'!$AY$1:$AY$2</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="1134">
   <si>
     <t>alias</t>
   </si>
@@ -464,6 +464,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -554,6 +557,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1694,13 +1700,13 @@
     <t>door location</t>
   </si>
   <si>
-    <t>(Optional) The relative location of the door in the room (Units: year)</t>
+    <t>(Optional) The relative location of the door in the room (Units: minute)</t>
   </si>
   <si>
     <t>window signs of water/mold</t>
   </si>
   <si>
-    <t>(Optional) Signs of the presence of mold or mildew on the window. (Units: year)</t>
+    <t>(Optional) Signs of the presence of mold or mildew on the window. (Units: minute)</t>
   </si>
   <si>
     <t>window type</t>
@@ -1712,7 +1718,7 @@
     <t>window material</t>
   </si>
   <si>
-    <t>(Optional) The type of material used to finish a window (Units: g/m3)</t>
+    <t>(Optional) The type of material used to finish a window (Units: %)</t>
   </si>
   <si>
     <t>window horizontal position</t>
@@ -1724,13 +1730,13 @@
     <t>room condition</t>
   </si>
   <si>
-    <t>(Optional) The condition of the room at the time of sampling (Units: mm)</t>
+    <t>(Optional) The condition of the room at the time of sampling (Units: m)</t>
   </si>
   <si>
     <t>window area/size</t>
   </si>
   <si>
-    <t>(Optional) The window's length and width (Units: mm)</t>
+    <t>(Optional) The window's length and width (Units: m)</t>
   </si>
   <si>
     <t>sampling floor</t>
@@ -1856,55 +1862,55 @@
     <t>floor structure</t>
   </si>
   <si>
-    <t>(Optional) Refers to the structural elements and subfloor upon which the finish flooring is installed (Units: year)</t>
+    <t>(Optional) Refers to the structural elements and subfloor upon which the finish flooring is installed (Units: minute)</t>
   </si>
   <si>
     <t>rooms that share a wall with sampling room</t>
   </si>
   <si>
-    <t>(Optional) List of room(s) (room number, room name) sharing a wall with the sampling room (Units: year)</t>
+    <t>(Optional) List of room(s) (room number, room name) sharing a wall with the sampling room (Units: minute)</t>
   </si>
   <si>
     <t>wall finish material</t>
   </si>
   <si>
-    <t>(Optional) The material utilized to finish the outer most layer of the wall (Units: year)</t>
+    <t>(Optional) The material utilized to finish the outer most layer of the wall (Units: minute)</t>
   </si>
   <si>
     <t>room occupancy</t>
   </si>
   <si>
-    <t>(Optional) Count of room occupancy at time of sampling (Units: year)</t>
+    <t>(Optional) Count of room occupancy at time of sampling (Units: minute)</t>
   </si>
   <si>
     <t>room location in building</t>
   </si>
   <si>
-    <t>(Optional) The position of the room within the building (Units: year)</t>
+    <t>(Optional) The position of the room within the building (Units: minute)</t>
   </si>
   <si>
     <t>floor finish material</t>
   </si>
   <si>
-    <t>(Optional) The floor covering type; the finished surface that is walked on (Units: year)</t>
+    <t>(Optional) The floor covering type; the finished surface that is walked on (Units: minute)</t>
   </si>
   <si>
     <t>room window count</t>
   </si>
   <si>
-    <t>(Optional) Number of windows in the room (Units: year)</t>
+    <t>(Optional) Number of windows in the room (Units: minute)</t>
   </si>
   <si>
     <t>sampling room id or name</t>
   </si>
   <si>
-    <t>(Optional) Explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other). (Units: year)</t>
+    <t>(Optional) Explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other). (Units: day)</t>
   </si>
   <si>
     <t>height carpet fiber mat</t>
   </si>
   <si>
-    <t>(Optional) The average carpet fiber height in the indoor environment (Units: mm)</t>
+    <t>(Optional) The average carpet fiber height in the indoor environment (Units: cm)</t>
   </si>
   <si>
     <t>ceiling area</t>
@@ -1952,13 +1958,13 @@
     <t>rooms that share a door with sampling room</t>
   </si>
   <si>
-    <t>(Optional) List of room(s) (room number, room name) sharing a door with the sampling room (Units: year)</t>
+    <t>(Optional) List of room(s) (room number, room name) sharing a door with the sampling room (Units: day)</t>
   </si>
   <si>
     <t>orientations of exterior window</t>
   </si>
   <si>
-    <t>(Optional) The compass direction the exterior window of the room is facing (Units: year)</t>
+    <t>(Optional) The compass direction the exterior window of the room is facing (Units: day)</t>
   </si>
   <si>
     <t>wall location</t>
@@ -2102,13 +2108,13 @@
     <t>water feature size</t>
   </si>
   <si>
-    <t>(Optional) The size of the water feature (Units: m2)</t>
+    <t>(Optional) The size of the water feature (Units: ha)</t>
   </si>
   <si>
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>sample size sorting method</t>
@@ -2348,9 +2354,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -2369,6 +2372,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -2570,6 +2576,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -2579,9 +2588,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -2621,7 +2627,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -2690,6 +2696,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -2765,6 +2774,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2786,6 +2798,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2831,6 +2846,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2843,6 +2861,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2852,9 +2873,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2879,6 +2897,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2939,12 +2960,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -3110,7 +3131,7 @@
     <t>frequency of cleaning</t>
   </si>
   <si>
-    <t>(Optional) The number of times the sample location is cleaned. frequency of cleaning might be on a daily basis, weekly, monthly, quarterly or annually. (Units: year)</t>
+    <t>(Optional) The number of times the sample location is cleaned. frequency of cleaning might be on a daily basis, weekly, monthly, quarterly or annually. (Units: minute)</t>
   </si>
   <si>
     <t>carbon dioxide</t>
@@ -3218,7 +3239,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
@@ -3290,7 +3311,7 @@
     <t>sampling day weather</t>
   </si>
   <si>
-    <t>(Optional) The weather on the sampling day (Units: g/m3)</t>
+    <t>(Optional) The weather on the sampling day (Units: %)</t>
   </si>
   <si>
     <t>amount of light</t>
@@ -3308,13 +3329,13 @@
     <t>outside relative humidity</t>
   </si>
   <si>
-    <t>(Optional) The recorded outside relative humidity value at the time of sampling (Units: g/m3)</t>
+    <t>(Optional) The recorded outside relative humidity value at the time of sampling (Units: %)</t>
   </si>
   <si>
     <t>depth</t>
   </si>
   <si>
-    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
   <si>
     <t>door area or size</t>
@@ -3362,31 +3383,31 @@
     <t>occupancy documentation</t>
   </si>
   <si>
-    <t>(Optional) The type of documentation of occupancy (Units: year)</t>
+    <t>(Optional) The type of documentation of occupancy (Units: minute)</t>
   </si>
   <si>
     <t>floor count</t>
   </si>
   <si>
-    <t>(Optional) The number of floors in the building, including basements and mechanical penthouse (Units: year)</t>
+    <t>(Optional) The number of floors in the building, including basements and mechanical penthouse (Units: minute)</t>
   </si>
   <si>
     <t>shading device material</t>
   </si>
   <si>
-    <t>(Optional) The material the shading device is composed of (Units: year)</t>
+    <t>(Optional) The material the shading device is composed of (Units: minute)</t>
   </si>
   <si>
     <t>built structure age</t>
   </si>
   <si>
-    <t>(Optional) The age of the built structure since construction (Units: year)</t>
+    <t>(Optional) The age of the built structure since construction (Units: day)</t>
   </si>
   <si>
     <t>hallway/corridor count</t>
   </si>
   <si>
-    <t>(Optional) The total count of hallways and corridors in the built structure (Units: g/m3)</t>
+    <t>(Optional) The total count of hallways and corridors in the built structure (Units: %)</t>
   </si>
   <si>
     <t>architectural structure</t>
@@ -3955,10 +3976,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3999,10 +4020,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4029,7 +4050,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4046,7 +4067,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -4063,7 +4084,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -4080,7 +4101,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -4097,7 +4118,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -4114,7 +4135,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -4131,7 +4152,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -4148,7 +4169,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -4165,7 +4186,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -4182,7 +4203,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -4196,7 +4217,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -4210,7 +4231,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -4224,7 +4245,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -4238,7 +4259,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -4252,7 +4273,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -4266,7 +4287,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -4280,7 +4301,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -4294,7 +4315,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -4304,8 +4325,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -4316,7 +4340,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -4327,7 +4351,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -4338,7 +4362,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -4349,7 +4373,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -4360,7 +4384,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -4371,7 +4395,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -4382,7 +4406,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -4393,7 +4417,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -4404,7 +4428,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -4415,7 +4439,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -4426,7 +4450,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -4437,7 +4461,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -4448,7 +4472,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -4456,7 +4480,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -4464,7 +4488,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -4472,7 +4496,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -4480,7 +4504,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -4488,7 +4512,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -4496,7 +4520,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -4504,7 +4528,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -4512,7 +4536,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -4520,7 +4544,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -4528,236 +4552,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4779,27 +4808,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4819,122 +4848,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4958,1320 +4987,1320 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="2" spans="1:220" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
     </row>
   </sheetData>
@@ -6337,1863 +6366,1888 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H1:FK289"/>
+  <dimension ref="H1:FK294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="8:167">
       <c r="H1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="X1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AP1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AQ1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AR1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AS1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AT1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AU1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AV1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AW1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AX1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AY1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="BC1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="EV1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="FK1" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="2" spans="8:167">
       <c r="H2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="X2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AO2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AP2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AQ2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AR2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AS2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AT2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AU2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AV2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AW2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AX2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AY2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="BC2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="EV2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="FK2" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="3" spans="8:167">
       <c r="H3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="X3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AP3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AQ3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AR3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AS3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AT3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AU3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AV3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AW3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AX3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="BC3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="EV3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="FK3" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="4" spans="8:167">
       <c r="H4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AO4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AQ4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AR4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AS4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AT4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AW4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AX4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="EV4" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="FK4" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="5" spans="8:167">
       <c r="H5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AO5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AQ5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AR5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AS5" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AT5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AX5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="EV5" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="FK5" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="6" spans="8:167">
       <c r="H6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AO6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AQ6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AR6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AS6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AX6" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="EV6" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="7" spans="8:167">
       <c r="H7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AQ7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AR7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AS7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AX7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="EV7" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8" spans="8:167">
       <c r="H8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AP8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AQ8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AX8" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="EV8" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="9" spans="8:167">
       <c r="H9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AX9" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="EV9" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="10" spans="8:167">
       <c r="H10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AO10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AX10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="EV10" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="8:167">
       <c r="H11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AO11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AX11" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="EV11" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" spans="8:167">
       <c r="H12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO12" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AX12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="EV12" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="13" spans="8:167">
       <c r="H13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO13" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AX13" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="EV13" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="14" spans="8:167">
       <c r="H14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AX14" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="EV14" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="15" spans="8:167">
       <c r="H15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AX15" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="EV15" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="16" spans="8:167">
       <c r="H16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AX16" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="EV16" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="17" spans="8:152">
       <c r="H17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AX17" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="EV17" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18" spans="8:152">
       <c r="H18" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AX18" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="EV18" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="19" spans="8:152">
       <c r="H19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AX19" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="EV19" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="20" spans="8:152">
       <c r="H20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AX20" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="EV20" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="21" spans="8:152">
       <c r="H21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AX21" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="EV21" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="22" spans="8:152">
       <c r="H22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="EV22" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="23" spans="8:152">
       <c r="H23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="EV23" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="24" spans="8:152">
       <c r="H24" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="EV24" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="25" spans="8:152">
       <c r="H25" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="EV25" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="26" spans="8:152">
       <c r="H26" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="EV26" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="27" spans="8:152">
       <c r="H27" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="EV27" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="28" spans="8:152">
       <c r="H28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="EV28" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="29" spans="8:152">
       <c r="H29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="EV29" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="30" spans="8:152">
       <c r="H30" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="EV30" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="31" spans="8:152">
       <c r="EV31" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="32" spans="8:152">
       <c r="EV32" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="33" spans="152:152">
       <c r="EV33" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="34" spans="152:152">
       <c r="EV34" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="35" spans="152:152">
       <c r="EV35" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="36" spans="152:152">
       <c r="EV36" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="37" spans="152:152">
       <c r="EV37" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="38" spans="152:152">
       <c r="EV38" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="39" spans="152:152">
       <c r="EV39" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="40" spans="152:152">
       <c r="EV40" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="41" spans="152:152">
       <c r="EV41" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="42" spans="152:152">
       <c r="EV42" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="43" spans="152:152">
       <c r="EV43" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="44" spans="152:152">
       <c r="EV44" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="45" spans="152:152">
       <c r="EV45" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="46" spans="152:152">
       <c r="EV46" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="47" spans="152:152">
       <c r="EV47" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="48" spans="152:152">
       <c r="EV48" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="49" spans="152:152">
       <c r="EV49" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="50" spans="152:152">
       <c r="EV50" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="51" spans="152:152">
       <c r="EV51" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="52" spans="152:152">
       <c r="EV52" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="53" spans="152:152">
       <c r="EV53" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="54" spans="152:152">
       <c r="EV54" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="55" spans="152:152">
       <c r="EV55" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="56" spans="152:152">
       <c r="EV56" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="57" spans="152:152">
       <c r="EV57" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="58" spans="152:152">
       <c r="EV58" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="59" spans="152:152">
       <c r="EV59" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="60" spans="152:152">
       <c r="EV60" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="61" spans="152:152">
       <c r="EV61" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="62" spans="152:152">
       <c r="EV62" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="63" spans="152:152">
       <c r="EV63" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="64" spans="152:152">
       <c r="EV64" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="65" spans="152:152">
       <c r="EV65" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="66" spans="152:152">
       <c r="EV66" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="67" spans="152:152">
       <c r="EV67" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="68" spans="152:152">
       <c r="EV68" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="69" spans="152:152">
       <c r="EV69" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="70" spans="152:152">
       <c r="EV70" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="71" spans="152:152">
       <c r="EV71" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="72" spans="152:152">
       <c r="EV72" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="73" spans="152:152">
       <c r="EV73" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="74" spans="152:152">
       <c r="EV74" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="75" spans="152:152">
       <c r="EV75" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="76" spans="152:152">
       <c r="EV76" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="77" spans="152:152">
       <c r="EV77" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="78" spans="152:152">
       <c r="EV78" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="79" spans="152:152">
       <c r="EV79" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
     </row>
     <row r="80" spans="152:152">
       <c r="EV80" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="81" spans="152:152">
       <c r="EV81" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="82" spans="152:152">
       <c r="EV82" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="83" spans="152:152">
       <c r="EV83" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
     </row>
     <row r="84" spans="152:152">
       <c r="EV84" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="85" spans="152:152">
       <c r="EV85" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="86" spans="152:152">
       <c r="EV86" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="87" spans="152:152">
       <c r="EV87" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="88" spans="152:152">
       <c r="EV88" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="89" spans="152:152">
       <c r="EV89" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="90" spans="152:152">
       <c r="EV90" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="91" spans="152:152">
       <c r="EV91" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="92" spans="152:152">
       <c r="EV92" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="93" spans="152:152">
       <c r="EV93" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="94" spans="152:152">
       <c r="EV94" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="95" spans="152:152">
       <c r="EV95" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="96" spans="152:152">
       <c r="EV96" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="97" spans="152:152">
       <c r="EV97" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="98" spans="152:152">
       <c r="EV98" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="99" spans="152:152">
       <c r="EV99" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="100" spans="152:152">
       <c r="EV100" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="101" spans="152:152">
       <c r="EV101" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
     </row>
     <row r="102" spans="152:152">
       <c r="EV102" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="103" spans="152:152">
       <c r="EV103" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="104" spans="152:152">
       <c r="EV104" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="105" spans="152:152">
       <c r="EV105" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="106" spans="152:152">
       <c r="EV106" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="107" spans="152:152">
       <c r="EV107" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="108" spans="152:152">
       <c r="EV108" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="109" spans="152:152">
       <c r="EV109" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="110" spans="152:152">
       <c r="EV110" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="111" spans="152:152">
       <c r="EV111" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="112" spans="152:152">
       <c r="EV112" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="113" spans="152:152">
       <c r="EV113" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="114" spans="152:152">
       <c r="EV114" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="115" spans="152:152">
       <c r="EV115" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="116" spans="152:152">
       <c r="EV116" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="117" spans="152:152">
       <c r="EV117" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="118" spans="152:152">
       <c r="EV118" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="119" spans="152:152">
       <c r="EV119" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="120" spans="152:152">
       <c r="EV120" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="121" spans="152:152">
       <c r="EV121" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="122" spans="152:152">
       <c r="EV122" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="123" spans="152:152">
       <c r="EV123" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="124" spans="152:152">
       <c r="EV124" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="125" spans="152:152">
       <c r="EV125" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="126" spans="152:152">
       <c r="EV126" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="127" spans="152:152">
       <c r="EV127" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="128" spans="152:152">
       <c r="EV128" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="129" spans="152:152">
       <c r="EV129" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="130" spans="152:152">
       <c r="EV130" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="131" spans="152:152">
       <c r="EV131" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="132" spans="152:152">
       <c r="EV132" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="133" spans="152:152">
       <c r="EV133" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="134" spans="152:152">
       <c r="EV134" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="135" spans="152:152">
       <c r="EV135" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="136" spans="152:152">
       <c r="EV136" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="137" spans="152:152">
       <c r="EV137" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="138" spans="152:152">
       <c r="EV138" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="139" spans="152:152">
       <c r="EV139" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="140" spans="152:152">
       <c r="EV140" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="141" spans="152:152">
       <c r="EV141" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="142" spans="152:152">
       <c r="EV142" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="143" spans="152:152">
       <c r="EV143" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="144" spans="152:152">
       <c r="EV144" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="145" spans="152:152">
       <c r="EV145" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="146" spans="152:152">
       <c r="EV146" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="147" spans="152:152">
       <c r="EV147" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="148" spans="152:152">
       <c r="EV148" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="149" spans="152:152">
       <c r="EV149" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="150" spans="152:152">
       <c r="EV150" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="151" spans="152:152">
       <c r="EV151" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="152" spans="152:152">
       <c r="EV152" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="153" spans="152:152">
       <c r="EV153" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="154" spans="152:152">
       <c r="EV154" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="155" spans="152:152">
       <c r="EV155" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="156" spans="152:152">
       <c r="EV156" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="157" spans="152:152">
       <c r="EV157" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="158" spans="152:152">
       <c r="EV158" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="159" spans="152:152">
       <c r="EV159" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="160" spans="152:152">
       <c r="EV160" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="161" spans="152:152">
       <c r="EV161" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="162" spans="152:152">
       <c r="EV162" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="163" spans="152:152">
       <c r="EV163" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="164" spans="152:152">
       <c r="EV164" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="165" spans="152:152">
       <c r="EV165" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="166" spans="152:152">
       <c r="EV166" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="167" spans="152:152">
       <c r="EV167" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="168" spans="152:152">
       <c r="EV168" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="169" spans="152:152">
       <c r="EV169" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="170" spans="152:152">
       <c r="EV170" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="171" spans="152:152">
       <c r="EV171" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="172" spans="152:152">
       <c r="EV172" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="173" spans="152:152">
       <c r="EV173" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="174" spans="152:152">
       <c r="EV174" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="175" spans="152:152">
       <c r="EV175" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="176" spans="152:152">
       <c r="EV176" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="177" spans="152:152">
       <c r="EV177" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="178" spans="152:152">
       <c r="EV178" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="179" spans="152:152">
       <c r="EV179" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="180" spans="152:152">
       <c r="EV180" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="181" spans="152:152">
       <c r="EV181" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="182" spans="152:152">
       <c r="EV182" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="183" spans="152:152">
       <c r="EV183" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="184" spans="152:152">
       <c r="EV184" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="185" spans="152:152">
       <c r="EV185" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="186" spans="152:152">
       <c r="EV186" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="187" spans="152:152">
       <c r="EV187" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="188" spans="152:152">
       <c r="EV188" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="189" spans="152:152">
       <c r="EV189" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="190" spans="152:152">
       <c r="EV190" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="191" spans="152:152">
       <c r="EV191" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="192" spans="152:152">
       <c r="EV192" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="193" spans="152:152">
       <c r="EV193" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="194" spans="152:152">
       <c r="EV194" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="195" spans="152:152">
       <c r="EV195" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="196" spans="152:152">
       <c r="EV196" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="197" spans="152:152">
       <c r="EV197" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="198" spans="152:152">
       <c r="EV198" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="199" spans="152:152">
       <c r="EV199" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="200" spans="152:152">
       <c r="EV200" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="201" spans="152:152">
       <c r="EV201" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="202" spans="152:152">
       <c r="EV202" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="203" spans="152:152">
       <c r="EV203" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="204" spans="152:152">
       <c r="EV204" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="205" spans="152:152">
       <c r="EV205" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="206" spans="152:152">
       <c r="EV206" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="207" spans="152:152">
       <c r="EV207" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="208" spans="152:152">
       <c r="EV208" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="209" spans="152:152">
       <c r="EV209" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="210" spans="152:152">
       <c r="EV210" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="211" spans="152:152">
       <c r="EV211" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="212" spans="152:152">
       <c r="EV212" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="213" spans="152:152">
       <c r="EV213" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="214" spans="152:152">
       <c r="EV214" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="215" spans="152:152">
       <c r="EV215" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="216" spans="152:152">
       <c r="EV216" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="217" spans="152:152">
       <c r="EV217" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="218" spans="152:152">
       <c r="EV218" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="219" spans="152:152">
       <c r="EV219" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="220" spans="152:152">
       <c r="EV220" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="221" spans="152:152">
       <c r="EV221" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="222" spans="152:152">
       <c r="EV222" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="223" spans="152:152">
       <c r="EV223" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="224" spans="152:152">
       <c r="EV224" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="225" spans="152:152">
       <c r="EV225" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="226" spans="152:152">
       <c r="EV226" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="227" spans="152:152">
       <c r="EV227" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
     </row>
     <row r="228" spans="152:152">
       <c r="EV228" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="229" spans="152:152">
       <c r="EV229" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="230" spans="152:152">
       <c r="EV230" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="231" spans="152:152">
       <c r="EV231" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
     </row>
     <row r="232" spans="152:152">
       <c r="EV232" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="233" spans="152:152">
       <c r="EV233" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="234" spans="152:152">
       <c r="EV234" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="235" spans="152:152">
       <c r="EV235" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="236" spans="152:152">
       <c r="EV236" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="237" spans="152:152">
       <c r="EV237" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="238" spans="152:152">
       <c r="EV238" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="239" spans="152:152">
       <c r="EV239" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="240" spans="152:152">
       <c r="EV240" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="241" spans="152:152">
       <c r="EV241" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="242" spans="152:152">
       <c r="EV242" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="243" spans="152:152">
       <c r="EV243" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
     <row r="244" spans="152:152">
       <c r="EV244" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="245" spans="152:152">
       <c r="EV245" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
     </row>
     <row r="246" spans="152:152">
       <c r="EV246" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="247" spans="152:152">
       <c r="EV247" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
     </row>
     <row r="248" spans="152:152">
       <c r="EV248" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="249" spans="152:152">
       <c r="EV249" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="250" spans="152:152">
       <c r="EV250" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="251" spans="152:152">
       <c r="EV251" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="252" spans="152:152">
       <c r="EV252" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="253" spans="152:152">
       <c r="EV253" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="254" spans="152:152">
       <c r="EV254" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="255" spans="152:152">
       <c r="EV255" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="256" spans="152:152">
       <c r="EV256" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="257" spans="152:152">
       <c r="EV257" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="258" spans="152:152">
       <c r="EV258" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="259" spans="152:152">
       <c r="EV259" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="260" spans="152:152">
       <c r="EV260" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="261" spans="152:152">
       <c r="EV261" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="262" spans="152:152">
       <c r="EV262" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="263" spans="152:152">
       <c r="EV263" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
     <row r="264" spans="152:152">
       <c r="EV264" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="265" spans="152:152">
       <c r="EV265" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="266" spans="152:152">
       <c r="EV266" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="267" spans="152:152">
       <c r="EV267" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
     <row r="268" spans="152:152">
       <c r="EV268" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="269" spans="152:152">
       <c r="EV269" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="270" spans="152:152">
       <c r="EV270" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="271" spans="152:152">
       <c r="EV271" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="272" spans="152:152">
       <c r="EV272" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="273" spans="152:152">
       <c r="EV273" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="274" spans="152:152">
       <c r="EV274" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="275" spans="152:152">
       <c r="EV275" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
     </row>
     <row r="276" spans="152:152">
       <c r="EV276" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="277" spans="152:152">
       <c r="EV277" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="278" spans="152:152">
       <c r="EV278" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="279" spans="152:152">
       <c r="EV279" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="280" spans="152:152">
       <c r="EV280" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="281" spans="152:152">
       <c r="EV281" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="282" spans="152:152">
       <c r="EV282" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="283" spans="152:152">
       <c r="EV283" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
     </row>
     <row r="284" spans="152:152">
       <c r="EV284" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="285" spans="152:152">
       <c r="EV285" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="286" spans="152:152">
       <c r="EV286" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="287" spans="152:152">
       <c r="EV287" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
     </row>
     <row r="288" spans="152:152">
       <c r="EV288" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="289" spans="152:152">
       <c r="EV289" t="s">
-        <v>983</v>
+        <v>985</v>
+      </c>
+    </row>
+    <row r="290" spans="152:152">
+      <c r="EV290" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="291" spans="152:152">
+      <c r="EV291" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="292" spans="152:152">
+      <c r="EV292" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="293" spans="152:152">
+      <c r="EV293" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="294" spans="152:152">
+      <c r="EV294" t="s">
+        <v>990</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000031/metadata_template_ERC000031.xlsx
+++ b/templates/ERC000031/metadata_template_ERC000031.xlsx
@@ -17,38 +17,38 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="buildingoccupancytype">'cv_sample'!$AV$1:$AV$21</definedName>
-    <definedName name="buildingsetting">'cv_sample'!$AU$1:$AU$4</definedName>
+    <definedName name="buildingoccupancytype">'cv_sample'!$AW$1:$AW$21</definedName>
+    <definedName name="buildingsetting">'cv_sample'!$AV$1:$AV$4</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="filtertype">'cv_sample'!$AQ$1:$AQ$7</definedName>
-    <definedName name="frequencyofcleaning">'cv_sample'!$FI$1:$FI$5</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$ET$1:$ET$289</definedName>
-    <definedName name="heatingandcoolingsystemtype">'cv_sample'!$AR$1:$AR$5</definedName>
-    <definedName name="indoorspace">'cv_sample'!$AP$1:$AP$8</definedName>
-    <definedName name="indoorsurface">'cv_sample'!$AO$1:$AO$8</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="filtertype">'cv_sample'!$AR$1:$AR$7</definedName>
+    <definedName name="frequencyofcleaning">'cv_sample'!$FJ$1:$FJ$5</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$EU$1:$EU$294</definedName>
+    <definedName name="heatingandcoolingsystemtype">'cv_sample'!$AS$1:$AS$5</definedName>
+    <definedName name="indoorspace">'cv_sample'!$AQ$1:$AQ$8</definedName>
+    <definedName name="indoorsurface">'cv_sample'!$AP$1:$AP$8</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="lighttype">'cv_sample'!$AT$1:$AT$3</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$I$1:$I$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$V$1:$V$3</definedName>
-    <definedName name="spacetypicalstate">'cv_sample'!$AW$1:$AW$2</definedName>
+    <definedName name="lighttype">'cv_sample'!$AU$1:$AU$3</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$W$1:$W$3</definedName>
+    <definedName name="spacetypicalstate">'cv_sample'!$AX$1:$AX$2</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="substructuretype">'cv_sample'!$AS$1:$AS$3</definedName>
-    <definedName name="surfaceaircontaminant">'cv_sample'!$AN$1:$AN$8</definedName>
-    <definedName name="surfacematerial">'cv_sample'!$AM$1:$AM$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$F$1:$F$30</definedName>
-    <definedName name="ventilationtype">'cv_sample'!$BA$1:$BA$3</definedName>
+    <definedName name="substructuretype">'cv_sample'!$AT$1:$AT$3</definedName>
+    <definedName name="surfaceaircontaminant">'cv_sample'!$AO$1:$AO$8</definedName>
+    <definedName name="surfacematerial">'cv_sample'!$AN$1:$AN$15</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$G$1:$G$30</definedName>
+    <definedName name="ventilationtype">'cv_sample'!$BB$1:$BB$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="1132">
   <si>
     <t>alias</t>
   </si>
@@ -464,6 +464,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -554,6 +557,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -854,6 +860,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -2336,9 +2348,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -2357,6 +2366,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -2558,6 +2570,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -2567,9 +2582,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -2609,7 +2621,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -2678,6 +2690,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -2753,6 +2768,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2774,6 +2792,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2819,6 +2840,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2831,6 +2855,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2840,9 +2867,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2867,6 +2891,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2927,10 +2954,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3943,10 +3970,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3987,10 +4014,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4017,7 +4044,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4034,7 +4061,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -4051,7 +4078,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -4068,7 +4095,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -4085,7 +4112,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -4102,7 +4129,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -4119,7 +4146,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -4136,7 +4163,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -4153,7 +4180,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -4170,7 +4197,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -4184,7 +4211,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -4198,7 +4225,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -4212,7 +4239,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -4226,7 +4253,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -4240,7 +4267,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -4254,7 +4281,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -4268,7 +4295,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -4282,7 +4309,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -4292,8 +4319,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -4304,7 +4334,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -4315,7 +4345,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -4326,7 +4356,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -4337,7 +4367,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -4348,7 +4378,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -4359,7 +4389,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -4370,7 +4400,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -4381,7 +4411,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -4392,7 +4422,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -4403,7 +4433,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -4414,7 +4444,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -4425,7 +4455,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -4436,7 +4466,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -4444,7 +4474,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -4452,7 +4482,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -4460,7 +4490,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -4468,7 +4498,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -4476,7 +4506,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -4484,7 +4514,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -4492,7 +4522,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -4500,7 +4530,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -4508,7 +4538,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -4516,236 +4546,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4767,27 +4802,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4807,122 +4842,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4932,13 +4967,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:HJ2"/>
+  <dimension ref="A1:HK2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:218">
+    <row r="1" spans="1:219">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4946,1364 +4981,1370 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="AW1" s="1" t="s">
         <v>486</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>980</v>
+        <v>693</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:218" ht="150" customHeight="1">
+        <v>1128</v>
+      </c>
+      <c r="HK1" s="1" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:219" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="AW2" s="2" t="s">
         <v>487</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>981</v>
+        <v>694</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1122</v>
+        <v>1129</v>
+      </c>
+      <c r="HK2" s="2" t="s">
+        <v>1131</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="18">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:V101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM3:AM101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3:AN101">
       <formula1>surfacematerial</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3:AN101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO3:AO101">
       <formula1>surfaceaircontaminant</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO3:AO101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP3:AP101">
       <formula1>indoorsurface</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP3:AP101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ3:AQ101">
       <formula1>indoorspace</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ3:AQ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR3:AR101">
       <formula1>filtertype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR3:AR101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS3:AS101">
       <formula1>heatingandcoolingsystemtype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS3:AS101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT3:AT101">
       <formula1>substructuretype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT3:AT101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU3:AU101">
       <formula1>lighttype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU3:AU101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV101">
       <formula1>buildingsetting</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW3:AW101">
       <formula1>buildingoccupancytype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW3:AW101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX3:AX101">
       <formula1>spacetypicalstate</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA3:BA101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB3:BB101">
       <formula1>ventilationtype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ET3:ET101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EU3:EU101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FI3:FI101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FJ3:FJ101">
       <formula1>frequencyofcleaning</formula1>
     </dataValidation>
   </dataValidations>
@@ -6313,1863 +6354,1888 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:FI289"/>
+  <dimension ref="G1:FJ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:165">
-      <c r="F1" t="s">
-        <v>272</v>
-      </c>
+    <row r="1" spans="7:166">
       <c r="G1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1" t="s">
+        <v>317</v>
+      </c>
+      <c r="W1" t="s">
+        <v>350</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>387</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>404</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>414</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>424</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>434</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>443</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>455</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>460</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>466</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>488</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>498</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>695</v>
+      </c>
+      <c r="FJ1" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="2" spans="7:166">
+      <c r="G2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J2" t="s">
+        <v>318</v>
+      </c>
+      <c r="W2" t="s">
+        <v>351</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>405</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>415</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>425</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>435</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>444</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>451</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>456</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>461</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>467</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>489</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>499</v>
+      </c>
+      <c r="EU2" t="s">
+        <v>696</v>
+      </c>
+      <c r="FJ2" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="3" spans="7:166">
+      <c r="G3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J3" t="s">
+        <v>319</v>
+      </c>
+      <c r="W3" t="s">
+        <v>352</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>416</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>426</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>436</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>445</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>452</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>457</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>462</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>468</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>500</v>
+      </c>
+      <c r="EU3" t="s">
+        <v>697</v>
+      </c>
+      <c r="FJ3" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="4" spans="7:166">
+      <c r="G4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H4" t="s">
+        <v>311</v>
+      </c>
+      <c r="J4" t="s">
+        <v>320</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>390</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>407</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>417</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>427</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>437</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>446</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>463</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>469</v>
+      </c>
+      <c r="EU4" t="s">
+        <v>698</v>
+      </c>
+      <c r="FJ4" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="5" spans="7:166">
+      <c r="G5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H5" t="s">
+        <v>312</v>
+      </c>
+      <c r="J5" t="s">
+        <v>321</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>391</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>408</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>418</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>428</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>438</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>470</v>
+      </c>
+      <c r="EU5" t="s">
+        <v>699</v>
+      </c>
+      <c r="FJ5" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="6" spans="7:166">
+      <c r="G6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J6" t="s">
+        <v>322</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>392</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>409</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>419</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>439</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>471</v>
+      </c>
+      <c r="EU6" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="7" spans="7:166">
+      <c r="G7" t="s">
+        <v>282</v>
+      </c>
+      <c r="J7" t="s">
+        <v>323</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>393</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>410</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>420</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>430</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>440</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>472</v>
+      </c>
+      <c r="EU7" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="8" spans="7:166">
+      <c r="G8" t="s">
+        <v>283</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>394</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>411</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>421</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>431</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>473</v>
+      </c>
+      <c r="EU8" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="9" spans="7:166">
+      <c r="G9" t="s">
+        <v>284</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>395</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>474</v>
+      </c>
+      <c r="EU9" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="10" spans="7:166">
+      <c r="G10" t="s">
+        <v>285</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>396</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>475</v>
+      </c>
+      <c r="EU10" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="11" spans="7:166">
+      <c r="G11" t="s">
+        <v>286</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>397</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>476</v>
+      </c>
+      <c r="EU11" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="12" spans="7:166">
+      <c r="G12" t="s">
+        <v>287</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>398</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>431</v>
+      </c>
+      <c r="EU12" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="13" spans="7:166">
+      <c r="G13" t="s">
+        <v>288</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>399</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>477</v>
+      </c>
+      <c r="EU13" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="14" spans="7:166">
+      <c r="G14" t="s">
+        <v>289</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>400</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>478</v>
+      </c>
+      <c r="EU14" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="15" spans="7:166">
+      <c r="G15" t="s">
+        <v>290</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>401</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>479</v>
+      </c>
+      <c r="EU15" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="16" spans="7:166">
+      <c r="G16" t="s">
+        <v>291</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>480</v>
+      </c>
+      <c r="EU16" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="17" spans="7:151">
+      <c r="G17" t="s">
+        <v>292</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>481</v>
+      </c>
+      <c r="EU17" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="18" spans="7:151">
+      <c r="G18" t="s">
+        <v>293</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>482</v>
+      </c>
+      <c r="EU18" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="19" spans="7:151">
+      <c r="G19" t="s">
+        <v>294</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>483</v>
+      </c>
+      <c r="EU19" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="20" spans="7:151">
+      <c r="G20" t="s">
+        <v>295</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>484</v>
+      </c>
+      <c r="EU20" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="21" spans="7:151">
+      <c r="G21" t="s">
+        <v>296</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>485</v>
+      </c>
+      <c r="EU21" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="22" spans="7:151">
+      <c r="G22" t="s">
+        <v>297</v>
+      </c>
+      <c r="EU22" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="23" spans="7:151">
+      <c r="G23" t="s">
+        <v>298</v>
+      </c>
+      <c r="EU23" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="24" spans="7:151">
+      <c r="G24" t="s">
+        <v>299</v>
+      </c>
+      <c r="EU24" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="25" spans="7:151">
+      <c r="G25" t="s">
+        <v>300</v>
+      </c>
+      <c r="EU25" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="26" spans="7:151">
+      <c r="G26" t="s">
+        <v>301</v>
+      </c>
+      <c r="EU26" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="27" spans="7:151">
+      <c r="G27" t="s">
+        <v>302</v>
+      </c>
+      <c r="EU27" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="28" spans="7:151">
+      <c r="G28" t="s">
+        <v>303</v>
+      </c>
+      <c r="EU28" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="29" spans="7:151">
+      <c r="G29" t="s">
         <v>304</v>
       </c>
-      <c r="I1" t="s">
-        <v>313</v>
-      </c>
-      <c r="V1" t="s">
-        <v>346</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>383</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>400</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>410</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>420</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>430</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>439</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>446</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>451</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>456</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>462</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>484</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>494</v>
-      </c>
-      <c r="ET1" t="s">
-        <v>691</v>
-      </c>
-      <c r="FI1" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="2" spans="6:165">
-      <c r="F2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="EU29" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="30" spans="7:151">
+      <c r="G30" t="s">
         <v>305</v>
       </c>
-      <c r="I2" t="s">
-        <v>314</v>
-      </c>
-      <c r="V2" t="s">
-        <v>347</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>401</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>411</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>421</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>431</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>440</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>447</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>452</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>457</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>463</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>485</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>495</v>
-      </c>
-      <c r="ET2" t="s">
-        <v>692</v>
-      </c>
-      <c r="FI2" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="3" spans="6:165">
-      <c r="F3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G3" t="s">
-        <v>306</v>
-      </c>
-      <c r="I3" t="s">
-        <v>315</v>
-      </c>
-      <c r="V3" t="s">
-        <v>348</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>385</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>402</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>412</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>422</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>432</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>441</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>448</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>453</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>458</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>464</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>496</v>
-      </c>
-      <c r="ET3" t="s">
-        <v>693</v>
-      </c>
-      <c r="FI3" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="4" spans="6:165">
-      <c r="F4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G4" t="s">
-        <v>307</v>
-      </c>
-      <c r="I4" t="s">
-        <v>316</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>386</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>403</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>413</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>423</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>433</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>442</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>459</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>465</v>
-      </c>
-      <c r="ET4" t="s">
-        <v>694</v>
-      </c>
-      <c r="FI4" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="5" spans="6:165">
-      <c r="F5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G5" t="s">
-        <v>308</v>
-      </c>
-      <c r="I5" t="s">
-        <v>317</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>387</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>404</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>414</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>424</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>434</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>443</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>466</v>
-      </c>
-      <c r="ET5" t="s">
-        <v>695</v>
-      </c>
-      <c r="FI5" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="6" spans="6:165">
-      <c r="F6" t="s">
-        <v>277</v>
-      </c>
-      <c r="I6" t="s">
-        <v>318</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>388</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>405</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>415</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>425</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>435</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>467</v>
-      </c>
-      <c r="ET6" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="7" spans="6:165">
-      <c r="F7" t="s">
-        <v>278</v>
-      </c>
-      <c r="I7" t="s">
-        <v>319</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>389</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>406</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>416</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>426</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>436</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>468</v>
-      </c>
-      <c r="ET7" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="8" spans="6:165">
-      <c r="F8" t="s">
-        <v>279</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>390</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>407</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>417</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>427</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>469</v>
-      </c>
-      <c r="ET8" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="9" spans="6:165">
-      <c r="F9" t="s">
-        <v>280</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>391</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>470</v>
-      </c>
-      <c r="ET9" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="10" spans="6:165">
-      <c r="F10" t="s">
-        <v>281</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>392</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>471</v>
-      </c>
-      <c r="ET10" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="11" spans="6:165">
-      <c r="F11" t="s">
-        <v>282</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>393</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>472</v>
-      </c>
-      <c r="ET11" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="12" spans="6:165">
-      <c r="F12" t="s">
-        <v>283</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>394</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>427</v>
-      </c>
-      <c r="ET12" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="13" spans="6:165">
-      <c r="F13" t="s">
-        <v>284</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>395</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>473</v>
-      </c>
-      <c r="ET13" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="14" spans="6:165">
-      <c r="F14" t="s">
-        <v>285</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>396</v>
-      </c>
-      <c r="AV14" t="s">
-        <v>474</v>
-      </c>
-      <c r="ET14" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="15" spans="6:165">
-      <c r="F15" t="s">
-        <v>286</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>397</v>
-      </c>
-      <c r="AV15" t="s">
-        <v>475</v>
-      </c>
-      <c r="ET15" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="16" spans="6:165">
-      <c r="F16" t="s">
-        <v>287</v>
-      </c>
-      <c r="AV16" t="s">
-        <v>476</v>
-      </c>
-      <c r="ET16" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="17" spans="6:150">
-      <c r="F17" t="s">
-        <v>288</v>
-      </c>
-      <c r="AV17" t="s">
-        <v>477</v>
-      </c>
-      <c r="ET17" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="18" spans="6:150">
-      <c r="F18" t="s">
-        <v>289</v>
-      </c>
-      <c r="AV18" t="s">
-        <v>478</v>
-      </c>
-      <c r="ET18" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="19" spans="6:150">
-      <c r="F19" t="s">
-        <v>290</v>
-      </c>
-      <c r="AV19" t="s">
-        <v>479</v>
-      </c>
-      <c r="ET19" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="20" spans="6:150">
-      <c r="F20" t="s">
-        <v>291</v>
-      </c>
-      <c r="AV20" t="s">
-        <v>480</v>
-      </c>
-      <c r="ET20" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="21" spans="6:150">
-      <c r="F21" t="s">
-        <v>292</v>
-      </c>
-      <c r="AV21" t="s">
-        <v>481</v>
-      </c>
-      <c r="ET21" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="22" spans="6:150">
-      <c r="F22" t="s">
-        <v>293</v>
-      </c>
-      <c r="ET22" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="23" spans="6:150">
-      <c r="F23" t="s">
-        <v>294</v>
-      </c>
-      <c r="ET23" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="24" spans="6:150">
-      <c r="F24" t="s">
-        <v>295</v>
-      </c>
-      <c r="ET24" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="25" spans="6:150">
-      <c r="F25" t="s">
-        <v>296</v>
-      </c>
-      <c r="ET25" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="26" spans="6:150">
-      <c r="F26" t="s">
-        <v>297</v>
-      </c>
-      <c r="ET26" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="27" spans="6:150">
-      <c r="F27" t="s">
-        <v>298</v>
-      </c>
-      <c r="ET27" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="28" spans="6:150">
-      <c r="F28" t="s">
-        <v>299</v>
-      </c>
-      <c r="ET28" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="29" spans="6:150">
-      <c r="F29" t="s">
-        <v>300</v>
-      </c>
-      <c r="ET29" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="30" spans="6:150">
-      <c r="F30" t="s">
-        <v>301</v>
-      </c>
-      <c r="ET30" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="31" spans="6:150">
-      <c r="ET31" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="32" spans="6:150">
-      <c r="ET32" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="33" spans="150:150">
-      <c r="ET33" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="34" spans="150:150">
-      <c r="ET34" t="s">
+      <c r="EU30" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="35" spans="150:150">
-      <c r="ET35" t="s">
+    <row r="31" spans="7:151">
+      <c r="EU31" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="36" spans="150:150">
-      <c r="ET36" t="s">
+    <row r="32" spans="7:151">
+      <c r="EU32" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="37" spans="150:150">
-      <c r="ET37" t="s">
+    <row r="33" spans="151:151">
+      <c r="EU33" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="38" spans="150:150">
-      <c r="ET38" t="s">
+    <row r="34" spans="151:151">
+      <c r="EU34" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="39" spans="150:150">
-      <c r="ET39" t="s">
+    <row r="35" spans="151:151">
+      <c r="EU35" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="40" spans="150:150">
-      <c r="ET40" t="s">
+    <row r="36" spans="151:151">
+      <c r="EU36" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="41" spans="150:150">
-      <c r="ET41" t="s">
+    <row r="37" spans="151:151">
+      <c r="EU37" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="42" spans="150:150">
-      <c r="ET42" t="s">
+    <row r="38" spans="151:151">
+      <c r="EU38" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="43" spans="150:150">
-      <c r="ET43" t="s">
+    <row r="39" spans="151:151">
+      <c r="EU39" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="44" spans="150:150">
-      <c r="ET44" t="s">
+    <row r="40" spans="151:151">
+      <c r="EU40" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="45" spans="150:150">
-      <c r="ET45" t="s">
+    <row r="41" spans="151:151">
+      <c r="EU41" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="46" spans="150:150">
-      <c r="ET46" t="s">
+    <row r="42" spans="151:151">
+      <c r="EU42" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="47" spans="150:150">
-      <c r="ET47" t="s">
+    <row r="43" spans="151:151">
+      <c r="EU43" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="48" spans="150:150">
-      <c r="ET48" t="s">
+    <row r="44" spans="151:151">
+      <c r="EU44" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="49" spans="150:150">
-      <c r="ET49" t="s">
+    <row r="45" spans="151:151">
+      <c r="EU45" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="50" spans="150:150">
-      <c r="ET50" t="s">
+    <row r="46" spans="151:151">
+      <c r="EU46" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="51" spans="150:150">
-      <c r="ET51" t="s">
+    <row r="47" spans="151:151">
+      <c r="EU47" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="52" spans="150:150">
-      <c r="ET52" t="s">
+    <row r="48" spans="151:151">
+      <c r="EU48" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="53" spans="150:150">
-      <c r="ET53" t="s">
+    <row r="49" spans="151:151">
+      <c r="EU49" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="54" spans="150:150">
-      <c r="ET54" t="s">
+    <row r="50" spans="151:151">
+      <c r="EU50" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="55" spans="150:150">
-      <c r="ET55" t="s">
+    <row r="51" spans="151:151">
+      <c r="EU51" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="56" spans="150:150">
-      <c r="ET56" t="s">
+    <row r="52" spans="151:151">
+      <c r="EU52" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="57" spans="150:150">
-      <c r="ET57" t="s">
+    <row r="53" spans="151:151">
+      <c r="EU53" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="58" spans="150:150">
-      <c r="ET58" t="s">
+    <row r="54" spans="151:151">
+      <c r="EU54" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="59" spans="150:150">
-      <c r="ET59" t="s">
+    <row r="55" spans="151:151">
+      <c r="EU55" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="60" spans="150:150">
-      <c r="ET60" t="s">
+    <row r="56" spans="151:151">
+      <c r="EU56" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="61" spans="150:150">
-      <c r="ET61" t="s">
+    <row r="57" spans="151:151">
+      <c r="EU57" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="62" spans="150:150">
-      <c r="ET62" t="s">
+    <row r="58" spans="151:151">
+      <c r="EU58" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="63" spans="150:150">
-      <c r="ET63" t="s">
+    <row r="59" spans="151:151">
+      <c r="EU59" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="64" spans="150:150">
-      <c r="ET64" t="s">
+    <row r="60" spans="151:151">
+      <c r="EU60" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="65" spans="150:150">
-      <c r="ET65" t="s">
+    <row r="61" spans="151:151">
+      <c r="EU61" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="66" spans="150:150">
-      <c r="ET66" t="s">
+    <row r="62" spans="151:151">
+      <c r="EU62" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="67" spans="150:150">
-      <c r="ET67" t="s">
+    <row r="63" spans="151:151">
+      <c r="EU63" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="68" spans="150:150">
-      <c r="ET68" t="s">
+    <row r="64" spans="151:151">
+      <c r="EU64" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="69" spans="150:150">
-      <c r="ET69" t="s">
+    <row r="65" spans="151:151">
+      <c r="EU65" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="70" spans="150:150">
-      <c r="ET70" t="s">
+    <row r="66" spans="151:151">
+      <c r="EU66" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="71" spans="150:150">
-      <c r="ET71" t="s">
+    <row r="67" spans="151:151">
+      <c r="EU67" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="72" spans="150:150">
-      <c r="ET72" t="s">
+    <row r="68" spans="151:151">
+      <c r="EU68" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="73" spans="150:150">
-      <c r="ET73" t="s">
+    <row r="69" spans="151:151">
+      <c r="EU69" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="74" spans="150:150">
-      <c r="ET74" t="s">
+    <row r="70" spans="151:151">
+      <c r="EU70" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="75" spans="150:150">
-      <c r="ET75" t="s">
+    <row r="71" spans="151:151">
+      <c r="EU71" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="76" spans="150:150">
-      <c r="ET76" t="s">
+    <row r="72" spans="151:151">
+      <c r="EU72" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="77" spans="150:150">
-      <c r="ET77" t="s">
+    <row r="73" spans="151:151">
+      <c r="EU73" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="78" spans="150:150">
-      <c r="ET78" t="s">
+    <row r="74" spans="151:151">
+      <c r="EU74" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="79" spans="150:150">
-      <c r="ET79" t="s">
+    <row r="75" spans="151:151">
+      <c r="EU75" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="80" spans="150:150">
-      <c r="ET80" t="s">
+    <row r="76" spans="151:151">
+      <c r="EU76" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="81" spans="150:150">
-      <c r="ET81" t="s">
+    <row r="77" spans="151:151">
+      <c r="EU77" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="82" spans="150:150">
-      <c r="ET82" t="s">
+    <row r="78" spans="151:151">
+      <c r="EU78" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="83" spans="150:150">
-      <c r="ET83" t="s">
+    <row r="79" spans="151:151">
+      <c r="EU79" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="84" spans="150:150">
-      <c r="ET84" t="s">
+    <row r="80" spans="151:151">
+      <c r="EU80" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="85" spans="150:150">
-      <c r="ET85" t="s">
+    <row r="81" spans="151:151">
+      <c r="EU81" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="86" spans="150:150">
-      <c r="ET86" t="s">
+    <row r="82" spans="151:151">
+      <c r="EU82" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="87" spans="150:150">
-      <c r="ET87" t="s">
+    <row r="83" spans="151:151">
+      <c r="EU83" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="88" spans="150:150">
-      <c r="ET88" t="s">
+    <row r="84" spans="151:151">
+      <c r="EU84" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="89" spans="150:150">
-      <c r="ET89" t="s">
+    <row r="85" spans="151:151">
+      <c r="EU85" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="90" spans="150:150">
-      <c r="ET90" t="s">
+    <row r="86" spans="151:151">
+      <c r="EU86" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="91" spans="150:150">
-      <c r="ET91" t="s">
+    <row r="87" spans="151:151">
+      <c r="EU87" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="92" spans="150:150">
-      <c r="ET92" t="s">
+    <row r="88" spans="151:151">
+      <c r="EU88" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="93" spans="150:150">
-      <c r="ET93" t="s">
+    <row r="89" spans="151:151">
+      <c r="EU89" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="94" spans="150:150">
-      <c r="ET94" t="s">
+    <row r="90" spans="151:151">
+      <c r="EU90" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="95" spans="150:150">
-      <c r="ET95" t="s">
+    <row r="91" spans="151:151">
+      <c r="EU91" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="96" spans="150:150">
-      <c r="ET96" t="s">
+    <row r="92" spans="151:151">
+      <c r="EU92" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="97" spans="150:150">
-      <c r="ET97" t="s">
+    <row r="93" spans="151:151">
+      <c r="EU93" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="98" spans="150:150">
-      <c r="ET98" t="s">
+    <row r="94" spans="151:151">
+      <c r="EU94" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="99" spans="150:150">
-      <c r="ET99" t="s">
+    <row r="95" spans="151:151">
+      <c r="EU95" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="100" spans="150:150">
-      <c r="ET100" t="s">
+    <row r="96" spans="151:151">
+      <c r="EU96" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="101" spans="150:150">
-      <c r="ET101" t="s">
+    <row r="97" spans="151:151">
+      <c r="EU97" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="102" spans="150:150">
-      <c r="ET102" t="s">
+    <row r="98" spans="151:151">
+      <c r="EU98" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="103" spans="150:150">
-      <c r="ET103" t="s">
+    <row r="99" spans="151:151">
+      <c r="EU99" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="104" spans="150:150">
-      <c r="ET104" t="s">
+    <row r="100" spans="151:151">
+      <c r="EU100" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="105" spans="150:150">
-      <c r="ET105" t="s">
+    <row r="101" spans="151:151">
+      <c r="EU101" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="106" spans="150:150">
-      <c r="ET106" t="s">
+    <row r="102" spans="151:151">
+      <c r="EU102" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="107" spans="150:150">
-      <c r="ET107" t="s">
+    <row r="103" spans="151:151">
+      <c r="EU103" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="108" spans="150:150">
-      <c r="ET108" t="s">
+    <row r="104" spans="151:151">
+      <c r="EU104" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="109" spans="150:150">
-      <c r="ET109" t="s">
+    <row r="105" spans="151:151">
+      <c r="EU105" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="110" spans="150:150">
-      <c r="ET110" t="s">
+    <row r="106" spans="151:151">
+      <c r="EU106" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="111" spans="150:150">
-      <c r="ET111" t="s">
+    <row r="107" spans="151:151">
+      <c r="EU107" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="112" spans="150:150">
-      <c r="ET112" t="s">
+    <row r="108" spans="151:151">
+      <c r="EU108" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="113" spans="150:150">
-      <c r="ET113" t="s">
+    <row r="109" spans="151:151">
+      <c r="EU109" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="114" spans="150:150">
-      <c r="ET114" t="s">
+    <row r="110" spans="151:151">
+      <c r="EU110" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="115" spans="150:150">
-      <c r="ET115" t="s">
+    <row r="111" spans="151:151">
+      <c r="EU111" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="116" spans="150:150">
-      <c r="ET116" t="s">
+    <row r="112" spans="151:151">
+      <c r="EU112" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="117" spans="150:150">
-      <c r="ET117" t="s">
+    <row r="113" spans="151:151">
+      <c r="EU113" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="118" spans="150:150">
-      <c r="ET118" t="s">
+    <row r="114" spans="151:151">
+      <c r="EU114" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="119" spans="150:150">
-      <c r="ET119" t="s">
+    <row r="115" spans="151:151">
+      <c r="EU115" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="120" spans="150:150">
-      <c r="ET120" t="s">
+    <row r="116" spans="151:151">
+      <c r="EU116" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="121" spans="150:150">
-      <c r="ET121" t="s">
+    <row r="117" spans="151:151">
+      <c r="EU117" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="122" spans="150:150">
-      <c r="ET122" t="s">
+    <row r="118" spans="151:151">
+      <c r="EU118" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="123" spans="150:150">
-      <c r="ET123" t="s">
+    <row r="119" spans="151:151">
+      <c r="EU119" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="124" spans="150:150">
-      <c r="ET124" t="s">
+    <row r="120" spans="151:151">
+      <c r="EU120" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="125" spans="150:150">
-      <c r="ET125" t="s">
+    <row r="121" spans="151:151">
+      <c r="EU121" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="126" spans="150:150">
-      <c r="ET126" t="s">
+    <row r="122" spans="151:151">
+      <c r="EU122" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="127" spans="150:150">
-      <c r="ET127" t="s">
+    <row r="123" spans="151:151">
+      <c r="EU123" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="128" spans="150:150">
-      <c r="ET128" t="s">
+    <row r="124" spans="151:151">
+      <c r="EU124" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="129" spans="150:150">
-      <c r="ET129" t="s">
+    <row r="125" spans="151:151">
+      <c r="EU125" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="130" spans="150:150">
-      <c r="ET130" t="s">
+    <row r="126" spans="151:151">
+      <c r="EU126" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="131" spans="150:150">
-      <c r="ET131" t="s">
+    <row r="127" spans="151:151">
+      <c r="EU127" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="132" spans="150:150">
-      <c r="ET132" t="s">
+    <row r="128" spans="151:151">
+      <c r="EU128" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="133" spans="150:150">
-      <c r="ET133" t="s">
+    <row r="129" spans="151:151">
+      <c r="EU129" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="134" spans="150:150">
-      <c r="ET134" t="s">
+    <row r="130" spans="151:151">
+      <c r="EU130" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="135" spans="150:150">
-      <c r="ET135" t="s">
+    <row r="131" spans="151:151">
+      <c r="EU131" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="136" spans="150:150">
-      <c r="ET136" t="s">
+    <row r="132" spans="151:151">
+      <c r="EU132" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="137" spans="150:150">
-      <c r="ET137" t="s">
+    <row r="133" spans="151:151">
+      <c r="EU133" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="138" spans="150:150">
-      <c r="ET138" t="s">
+    <row r="134" spans="151:151">
+      <c r="EU134" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="139" spans="150:150">
-      <c r="ET139" t="s">
+    <row r="135" spans="151:151">
+      <c r="EU135" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="140" spans="150:150">
-      <c r="ET140" t="s">
+    <row r="136" spans="151:151">
+      <c r="EU136" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="141" spans="150:150">
-      <c r="ET141" t="s">
+    <row r="137" spans="151:151">
+      <c r="EU137" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="142" spans="150:150">
-      <c r="ET142" t="s">
+    <row r="138" spans="151:151">
+      <c r="EU138" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="143" spans="150:150">
-      <c r="ET143" t="s">
+    <row r="139" spans="151:151">
+      <c r="EU139" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="144" spans="150:150">
-      <c r="ET144" t="s">
+    <row r="140" spans="151:151">
+      <c r="EU140" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="145" spans="150:150">
-      <c r="ET145" t="s">
+    <row r="141" spans="151:151">
+      <c r="EU141" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="146" spans="150:150">
-      <c r="ET146" t="s">
+    <row r="142" spans="151:151">
+      <c r="EU142" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="147" spans="150:150">
-      <c r="ET147" t="s">
+    <row r="143" spans="151:151">
+      <c r="EU143" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="148" spans="150:150">
-      <c r="ET148" t="s">
+    <row r="144" spans="151:151">
+      <c r="EU144" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="149" spans="150:150">
-      <c r="ET149" t="s">
+    <row r="145" spans="151:151">
+      <c r="EU145" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="150" spans="150:150">
-      <c r="ET150" t="s">
+    <row r="146" spans="151:151">
+      <c r="EU146" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="151" spans="150:150">
-      <c r="ET151" t="s">
+    <row r="147" spans="151:151">
+      <c r="EU147" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="152" spans="150:150">
-      <c r="ET152" t="s">
+    <row r="148" spans="151:151">
+      <c r="EU148" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="153" spans="150:150">
-      <c r="ET153" t="s">
+    <row r="149" spans="151:151">
+      <c r="EU149" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="154" spans="150:150">
-      <c r="ET154" t="s">
+    <row r="150" spans="151:151">
+      <c r="EU150" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="155" spans="150:150">
-      <c r="ET155" t="s">
+    <row r="151" spans="151:151">
+      <c r="EU151" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="156" spans="150:150">
-      <c r="ET156" t="s">
+    <row r="152" spans="151:151">
+      <c r="EU152" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="157" spans="150:150">
-      <c r="ET157" t="s">
+    <row r="153" spans="151:151">
+      <c r="EU153" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="158" spans="150:150">
-      <c r="ET158" t="s">
+    <row r="154" spans="151:151">
+      <c r="EU154" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="159" spans="150:150">
-      <c r="ET159" t="s">
+    <row r="155" spans="151:151">
+      <c r="EU155" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="160" spans="150:150">
-      <c r="ET160" t="s">
+    <row r="156" spans="151:151">
+      <c r="EU156" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="161" spans="150:150">
-      <c r="ET161" t="s">
+    <row r="157" spans="151:151">
+      <c r="EU157" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="162" spans="150:150">
-      <c r="ET162" t="s">
+    <row r="158" spans="151:151">
+      <c r="EU158" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="163" spans="150:150">
-      <c r="ET163" t="s">
+    <row r="159" spans="151:151">
+      <c r="EU159" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="164" spans="150:150">
-      <c r="ET164" t="s">
+    <row r="160" spans="151:151">
+      <c r="EU160" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="165" spans="150:150">
-      <c r="ET165" t="s">
+    <row r="161" spans="151:151">
+      <c r="EU161" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="166" spans="150:150">
-      <c r="ET166" t="s">
+    <row r="162" spans="151:151">
+      <c r="EU162" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="167" spans="150:150">
-      <c r="ET167" t="s">
+    <row r="163" spans="151:151">
+      <c r="EU163" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="168" spans="150:150">
-      <c r="ET168" t="s">
+    <row r="164" spans="151:151">
+      <c r="EU164" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="169" spans="150:150">
-      <c r="ET169" t="s">
+    <row r="165" spans="151:151">
+      <c r="EU165" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="170" spans="150:150">
-      <c r="ET170" t="s">
+    <row r="166" spans="151:151">
+      <c r="EU166" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="171" spans="150:150">
-      <c r="ET171" t="s">
+    <row r="167" spans="151:151">
+      <c r="EU167" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="172" spans="150:150">
-      <c r="ET172" t="s">
+    <row r="168" spans="151:151">
+      <c r="EU168" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="173" spans="150:150">
-      <c r="ET173" t="s">
+    <row r="169" spans="151:151">
+      <c r="EU169" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="174" spans="150:150">
-      <c r="ET174" t="s">
+    <row r="170" spans="151:151">
+      <c r="EU170" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="175" spans="150:150">
-      <c r="ET175" t="s">
+    <row r="171" spans="151:151">
+      <c r="EU171" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="176" spans="150:150">
-      <c r="ET176" t="s">
+    <row r="172" spans="151:151">
+      <c r="EU172" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="177" spans="150:150">
-      <c r="ET177" t="s">
+    <row r="173" spans="151:151">
+      <c r="EU173" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="178" spans="150:150">
-      <c r="ET178" t="s">
+    <row r="174" spans="151:151">
+      <c r="EU174" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="179" spans="150:150">
-      <c r="ET179" t="s">
+    <row r="175" spans="151:151">
+      <c r="EU175" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="180" spans="150:150">
-      <c r="ET180" t="s">
+    <row r="176" spans="151:151">
+      <c r="EU176" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="181" spans="150:150">
-      <c r="ET181" t="s">
+    <row r="177" spans="151:151">
+      <c r="EU177" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="182" spans="150:150">
-      <c r="ET182" t="s">
+    <row r="178" spans="151:151">
+      <c r="EU178" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="183" spans="150:150">
-      <c r="ET183" t="s">
+    <row r="179" spans="151:151">
+      <c r="EU179" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="184" spans="150:150">
-      <c r="ET184" t="s">
+    <row r="180" spans="151:151">
+      <c r="EU180" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="185" spans="150:150">
-      <c r="ET185" t="s">
+    <row r="181" spans="151:151">
+      <c r="EU181" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="186" spans="150:150">
-      <c r="ET186" t="s">
+    <row r="182" spans="151:151">
+      <c r="EU182" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="187" spans="150:150">
-      <c r="ET187" t="s">
+    <row r="183" spans="151:151">
+      <c r="EU183" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="188" spans="150:150">
-      <c r="ET188" t="s">
+    <row r="184" spans="151:151">
+      <c r="EU184" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="189" spans="150:150">
-      <c r="ET189" t="s">
+    <row r="185" spans="151:151">
+      <c r="EU185" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="190" spans="150:150">
-      <c r="ET190" t="s">
+    <row r="186" spans="151:151">
+      <c r="EU186" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="191" spans="150:150">
-      <c r="ET191" t="s">
+    <row r="187" spans="151:151">
+      <c r="EU187" t="s">
         <v>881</v>
       </c>
     </row>
-    <row r="192" spans="150:150">
-      <c r="ET192" t="s">
+    <row r="188" spans="151:151">
+      <c r="EU188" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="193" spans="150:150">
-      <c r="ET193" t="s">
+    <row r="189" spans="151:151">
+      <c r="EU189" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="194" spans="150:150">
-      <c r="ET194" t="s">
+    <row r="190" spans="151:151">
+      <c r="EU190" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="195" spans="150:150">
-      <c r="ET195" t="s">
+    <row r="191" spans="151:151">
+      <c r="EU191" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="196" spans="150:150">
-      <c r="ET196" t="s">
+    <row r="192" spans="151:151">
+      <c r="EU192" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="197" spans="150:150">
-      <c r="ET197" t="s">
+    <row r="193" spans="151:151">
+      <c r="EU193" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="198" spans="150:150">
-      <c r="ET198" t="s">
+    <row r="194" spans="151:151">
+      <c r="EU194" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="199" spans="150:150">
-      <c r="ET199" t="s">
+    <row r="195" spans="151:151">
+      <c r="EU195" t="s">
         <v>889</v>
       </c>
     </row>
-    <row r="200" spans="150:150">
-      <c r="ET200" t="s">
+    <row r="196" spans="151:151">
+      <c r="EU196" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="201" spans="150:150">
-      <c r="ET201" t="s">
+    <row r="197" spans="151:151">
+      <c r="EU197" t="s">
         <v>891</v>
       </c>
     </row>
-    <row r="202" spans="150:150">
-      <c r="ET202" t="s">
+    <row r="198" spans="151:151">
+      <c r="EU198" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="203" spans="150:150">
-      <c r="ET203" t="s">
+    <row r="199" spans="151:151">
+      <c r="EU199" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="204" spans="150:150">
-      <c r="ET204" t="s">
+    <row r="200" spans="151:151">
+      <c r="EU200" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="205" spans="150:150">
-      <c r="ET205" t="s">
+    <row r="201" spans="151:151">
+      <c r="EU201" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="206" spans="150:150">
-      <c r="ET206" t="s">
+    <row r="202" spans="151:151">
+      <c r="EU202" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="207" spans="150:150">
-      <c r="ET207" t="s">
+    <row r="203" spans="151:151">
+      <c r="EU203" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="208" spans="150:150">
-      <c r="ET208" t="s">
+    <row r="204" spans="151:151">
+      <c r="EU204" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="209" spans="150:150">
-      <c r="ET209" t="s">
+    <row r="205" spans="151:151">
+      <c r="EU205" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="210" spans="150:150">
-      <c r="ET210" t="s">
+    <row r="206" spans="151:151">
+      <c r="EU206" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="211" spans="150:150">
-      <c r="ET211" t="s">
+    <row r="207" spans="151:151">
+      <c r="EU207" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="212" spans="150:150">
-      <c r="ET212" t="s">
+    <row r="208" spans="151:151">
+      <c r="EU208" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="213" spans="150:150">
-      <c r="ET213" t="s">
+    <row r="209" spans="151:151">
+      <c r="EU209" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="214" spans="150:150">
-      <c r="ET214" t="s">
+    <row r="210" spans="151:151">
+      <c r="EU210" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="215" spans="150:150">
-      <c r="ET215" t="s">
+    <row r="211" spans="151:151">
+      <c r="EU211" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="216" spans="150:150">
-      <c r="ET216" t="s">
+    <row r="212" spans="151:151">
+      <c r="EU212" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="217" spans="150:150">
-      <c r="ET217" t="s">
+    <row r="213" spans="151:151">
+      <c r="EU213" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="218" spans="150:150">
-      <c r="ET218" t="s">
+    <row r="214" spans="151:151">
+      <c r="EU214" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="219" spans="150:150">
-      <c r="ET219" t="s">
+    <row r="215" spans="151:151">
+      <c r="EU215" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="220" spans="150:150">
-      <c r="ET220" t="s">
+    <row r="216" spans="151:151">
+      <c r="EU216" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="221" spans="150:150">
-      <c r="ET221" t="s">
+    <row r="217" spans="151:151">
+      <c r="EU217" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="222" spans="150:150">
-      <c r="ET222" t="s">
+    <row r="218" spans="151:151">
+      <c r="EU218" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="223" spans="150:150">
-      <c r="ET223" t="s">
+    <row r="219" spans="151:151">
+      <c r="EU219" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="224" spans="150:150">
-      <c r="ET224" t="s">
+    <row r="220" spans="151:151">
+      <c r="EU220" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="225" spans="150:150">
-      <c r="ET225" t="s">
+    <row r="221" spans="151:151">
+      <c r="EU221" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="226" spans="150:150">
-      <c r="ET226" t="s">
+    <row r="222" spans="151:151">
+      <c r="EU222" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="227" spans="150:150">
-      <c r="ET227" t="s">
+    <row r="223" spans="151:151">
+      <c r="EU223" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="228" spans="150:150">
-      <c r="ET228" t="s">
+    <row r="224" spans="151:151">
+      <c r="EU224" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="229" spans="150:150">
-      <c r="ET229" t="s">
+    <row r="225" spans="151:151">
+      <c r="EU225" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="230" spans="150:150">
-      <c r="ET230" t="s">
+    <row r="226" spans="151:151">
+      <c r="EU226" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="231" spans="150:150">
-      <c r="ET231" t="s">
+    <row r="227" spans="151:151">
+      <c r="EU227" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="232" spans="150:150">
-      <c r="ET232" t="s">
+    <row r="228" spans="151:151">
+      <c r="EU228" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="233" spans="150:150">
-      <c r="ET233" t="s">
+    <row r="229" spans="151:151">
+      <c r="EU229" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="234" spans="150:150">
-      <c r="ET234" t="s">
+    <row r="230" spans="151:151">
+      <c r="EU230" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="235" spans="150:150">
-      <c r="ET235" t="s">
+    <row r="231" spans="151:151">
+      <c r="EU231" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="236" spans="150:150">
-      <c r="ET236" t="s">
+    <row r="232" spans="151:151">
+      <c r="EU232" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="237" spans="150:150">
-      <c r="ET237" t="s">
+    <row r="233" spans="151:151">
+      <c r="EU233" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="238" spans="150:150">
-      <c r="ET238" t="s">
+    <row r="234" spans="151:151">
+      <c r="EU234" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="239" spans="150:150">
-      <c r="ET239" t="s">
+    <row r="235" spans="151:151">
+      <c r="EU235" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="240" spans="150:150">
-      <c r="ET240" t="s">
+    <row r="236" spans="151:151">
+      <c r="EU236" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="241" spans="150:150">
-      <c r="ET241" t="s">
+    <row r="237" spans="151:151">
+      <c r="EU237" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="242" spans="150:150">
-      <c r="ET242" t="s">
+    <row r="238" spans="151:151">
+      <c r="EU238" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="243" spans="150:150">
-      <c r="ET243" t="s">
+    <row r="239" spans="151:151">
+      <c r="EU239" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="244" spans="150:150">
-      <c r="ET244" t="s">
+    <row r="240" spans="151:151">
+      <c r="EU240" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="245" spans="150:150">
-      <c r="ET245" t="s">
+    <row r="241" spans="151:151">
+      <c r="EU241" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="246" spans="150:150">
-      <c r="ET246" t="s">
+    <row r="242" spans="151:151">
+      <c r="EU242" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="247" spans="150:150">
-      <c r="ET247" t="s">
+    <row r="243" spans="151:151">
+      <c r="EU243" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="248" spans="150:150">
-      <c r="ET248" t="s">
+    <row r="244" spans="151:151">
+      <c r="EU244" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="249" spans="150:150">
-      <c r="ET249" t="s">
+    <row r="245" spans="151:151">
+      <c r="EU245" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="250" spans="150:150">
-      <c r="ET250" t="s">
+    <row r="246" spans="151:151">
+      <c r="EU246" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="251" spans="150:150">
-      <c r="ET251" t="s">
+    <row r="247" spans="151:151">
+      <c r="EU247" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="252" spans="150:150">
-      <c r="ET252" t="s">
+    <row r="248" spans="151:151">
+      <c r="EU248" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="253" spans="150:150">
-      <c r="ET253" t="s">
+    <row r="249" spans="151:151">
+      <c r="EU249" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="254" spans="150:150">
-      <c r="ET254" t="s">
+    <row r="250" spans="151:151">
+      <c r="EU250" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="255" spans="150:150">
-      <c r="ET255" t="s">
+    <row r="251" spans="151:151">
+      <c r="EU251" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="256" spans="150:150">
-      <c r="ET256" t="s">
+    <row r="252" spans="151:151">
+      <c r="EU252" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="257" spans="150:150">
-      <c r="ET257" t="s">
+    <row r="253" spans="151:151">
+      <c r="EU253" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="258" spans="150:150">
-      <c r="ET258" t="s">
+    <row r="254" spans="151:151">
+      <c r="EU254" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="259" spans="150:150">
-      <c r="ET259" t="s">
+    <row r="255" spans="151:151">
+      <c r="EU255" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="260" spans="150:150">
-      <c r="ET260" t="s">
+    <row r="256" spans="151:151">
+      <c r="EU256" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="261" spans="150:150">
-      <c r="ET261" t="s">
+    <row r="257" spans="151:151">
+      <c r="EU257" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="262" spans="150:150">
-      <c r="ET262" t="s">
+    <row r="258" spans="151:151">
+      <c r="EU258" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="263" spans="150:150">
-      <c r="ET263" t="s">
+    <row r="259" spans="151:151">
+      <c r="EU259" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="264" spans="150:150">
-      <c r="ET264" t="s">
+    <row r="260" spans="151:151">
+      <c r="EU260" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="265" spans="150:150">
-      <c r="ET265" t="s">
+    <row r="261" spans="151:151">
+      <c r="EU261" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="266" spans="150:150">
-      <c r="ET266" t="s">
+    <row r="262" spans="151:151">
+      <c r="EU262" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="267" spans="150:150">
-      <c r="ET267" t="s">
+    <row r="263" spans="151:151">
+      <c r="EU263" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="268" spans="150:150">
-      <c r="ET268" t="s">
+    <row r="264" spans="151:151">
+      <c r="EU264" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="269" spans="150:150">
-      <c r="ET269" t="s">
+    <row r="265" spans="151:151">
+      <c r="EU265" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="270" spans="150:150">
-      <c r="ET270" t="s">
+    <row r="266" spans="151:151">
+      <c r="EU266" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="271" spans="150:150">
-      <c r="ET271" t="s">
+    <row r="267" spans="151:151">
+      <c r="EU267" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="272" spans="150:150">
-      <c r="ET272" t="s">
+    <row r="268" spans="151:151">
+      <c r="EU268" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="273" spans="150:150">
-      <c r="ET273" t="s">
+    <row r="269" spans="151:151">
+      <c r="EU269" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="274" spans="150:150">
-      <c r="ET274" t="s">
+    <row r="270" spans="151:151">
+      <c r="EU270" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="275" spans="150:150">
-      <c r="ET275" t="s">
+    <row r="271" spans="151:151">
+      <c r="EU271" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="276" spans="150:150">
-      <c r="ET276" t="s">
+    <row r="272" spans="151:151">
+      <c r="EU272" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="277" spans="150:150">
-      <c r="ET277" t="s">
+    <row r="273" spans="151:151">
+      <c r="EU273" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="278" spans="150:150">
-      <c r="ET278" t="s">
+    <row r="274" spans="151:151">
+      <c r="EU274" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="279" spans="150:150">
-      <c r="ET279" t="s">
+    <row r="275" spans="151:151">
+      <c r="EU275" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="280" spans="150:150">
-      <c r="ET280" t="s">
+    <row r="276" spans="151:151">
+      <c r="EU276" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="281" spans="150:150">
-      <c r="ET281" t="s">
+    <row r="277" spans="151:151">
+      <c r="EU277" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="282" spans="150:150">
-      <c r="ET282" t="s">
+    <row r="278" spans="151:151">
+      <c r="EU278" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="283" spans="150:150">
-      <c r="ET283" t="s">
+    <row r="279" spans="151:151">
+      <c r="EU279" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="284" spans="150:150">
-      <c r="ET284" t="s">
+    <row r="280" spans="151:151">
+      <c r="EU280" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="285" spans="150:150">
-      <c r="ET285" t="s">
+    <row r="281" spans="151:151">
+      <c r="EU281" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="286" spans="150:150">
-      <c r="ET286" t="s">
+    <row r="282" spans="151:151">
+      <c r="EU282" t="s">
         <v>976</v>
       </c>
     </row>
-    <row r="287" spans="150:150">
-      <c r="ET287" t="s">
+    <row r="283" spans="151:151">
+      <c r="EU283" t="s">
         <v>977</v>
       </c>
     </row>
-    <row r="288" spans="150:150">
-      <c r="ET288" t="s">
+    <row r="284" spans="151:151">
+      <c r="EU284" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="289" spans="150:150">
-      <c r="ET289" t="s">
+    <row r="285" spans="151:151">
+      <c r="EU285" t="s">
         <v>979</v>
+      </c>
+    </row>
+    <row r="286" spans="151:151">
+      <c r="EU286" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="287" spans="151:151">
+      <c r="EU287" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="288" spans="151:151">
+      <c r="EU288" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="289" spans="151:151">
+      <c r="EU289" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="290" spans="151:151">
+      <c r="EU290" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="291" spans="151:151">
+      <c r="EU291" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="292" spans="151:151">
+      <c r="EU292" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="293" spans="151:151">
+      <c r="EU293" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="294" spans="151:151">
+      <c r="EU294" t="s">
+        <v>988</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000031/metadata_template_ERC000031.xlsx
+++ b/templates/ERC000031/metadata_template_ERC000031.xlsx
@@ -17,38 +17,38 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="buildingoccupancytype">'cv_sample'!$AW$1:$AW$21</definedName>
-    <definedName name="buildingsetting">'cv_sample'!$AV$1:$AV$4</definedName>
+    <definedName name="buildingoccupancytype">'cv_sample'!$AX$1:$AX$21</definedName>
+    <definedName name="buildingsetting">'cv_sample'!$AW$1:$AW$4</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="filtertype">'cv_sample'!$AR$1:$AR$7</definedName>
-    <definedName name="frequencyofcleaning">'cv_sample'!$FJ$1:$FJ$5</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$EU$1:$EU$294</definedName>
-    <definedName name="heatingandcoolingsystemtype">'cv_sample'!$AS$1:$AS$5</definedName>
-    <definedName name="indoorspace">'cv_sample'!$AQ$1:$AQ$8</definedName>
-    <definedName name="indoorsurface">'cv_sample'!$AP$1:$AP$8</definedName>
+    <definedName name="filtertype">'cv_sample'!$AS$1:$AS$7</definedName>
+    <definedName name="frequencyofcleaning">'cv_sample'!$FK$1:$FK$5</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$EV$1:$EV$294</definedName>
+    <definedName name="heatingandcoolingsystemtype">'cv_sample'!$AT$1:$AT$5</definedName>
+    <definedName name="indoorspace">'cv_sample'!$AR$1:$AR$8</definedName>
+    <definedName name="indoorsurface">'cv_sample'!$AQ$1:$AQ$8</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="lighttype">'cv_sample'!$AU$1:$AU$3</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
+    <definedName name="lighttype">'cv_sample'!$AV$1:$AV$3</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$I$1:$I$5</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$W$1:$W$3</definedName>
-    <definedName name="spacetypicalstate">'cv_sample'!$AX$1:$AX$2</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$K$1:$K$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$X$1:$X$3</definedName>
+    <definedName name="spacetypicalstate">'cv_sample'!$AY$1:$AY$2</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="substructuretype">'cv_sample'!$AT$1:$AT$3</definedName>
-    <definedName name="surfaceaircontaminant">'cv_sample'!$AO$1:$AO$8</definedName>
-    <definedName name="surfacematerial">'cv_sample'!$AN$1:$AN$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$G$1:$G$30</definedName>
-    <definedName name="ventilationtype">'cv_sample'!$BB$1:$BB$3</definedName>
+    <definedName name="substructuretype">'cv_sample'!$AU$1:$AU$3</definedName>
+    <definedName name="surfaceaircontaminant">'cv_sample'!$AP$1:$AP$8</definedName>
+    <definedName name="surfacematerial">'cv_sample'!$AO$1:$AO$15</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$H$1:$H$30</definedName>
+    <definedName name="ventilationtype">'cv_sample'!$BC$1:$BC$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="1132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="1134">
   <si>
     <t>alias</t>
   </si>
@@ -864,6 +864,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -4967,13 +4973,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:HK2"/>
+  <dimension ref="A1:HL2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:219">
+    <row r="1" spans="1:220">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4993,16 +4999,16 @@
         <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>326</v>
@@ -5041,7 +5047,7 @@
         <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>355</v>
@@ -5092,37 +5098,37 @@
         <v>385</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AY1" s="1" t="s">
         <v>492</v>
@@ -5134,7 +5140,7 @@
         <v>496</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="BC1" s="1" t="s">
         <v>503</v>
@@ -5425,7 +5431,7 @@
         <v>693</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>989</v>
+        <v>695</v>
       </c>
       <c r="EV1" s="1" t="s">
         <v>991</v>
@@ -5470,7 +5476,7 @@
         <v>1017</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="FK1" s="1" t="s">
         <v>1026</v>
@@ -5631,8 +5637,11 @@
       <c r="HK1" s="1" t="s">
         <v>1130</v>
       </c>
-    </row>
-    <row r="2" spans="1:219" ht="150" customHeight="1">
+      <c r="HL1" s="1" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:220" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -5652,16 +5661,16 @@
         <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>327</v>
@@ -5700,7 +5709,7 @@
         <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>356</v>
@@ -5751,37 +5760,37 @@
         <v>386</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AY2" s="2" t="s">
         <v>493</v>
@@ -5793,7 +5802,7 @@
         <v>497</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="BC2" s="2" t="s">
         <v>504</v>
@@ -6084,7 +6093,7 @@
         <v>694</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>990</v>
+        <v>696</v>
       </c>
       <c r="EV2" s="2" t="s">
         <v>992</v>
@@ -6129,7 +6138,7 @@
         <v>1018</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="FK2" s="2" t="s">
         <v>1027</v>
@@ -6290,61 +6299,64 @@
       <c r="HK2" s="2" t="s">
         <v>1131</v>
       </c>
+      <c r="HL2" s="2" t="s">
+        <v>1133</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="18">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3:AN101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO3:AO101">
       <formula1>surfacematerial</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO3:AO101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP3:AP101">
       <formula1>surfaceaircontaminant</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP3:AP101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ3:AQ101">
       <formula1>indoorsurface</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ3:AQ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR3:AR101">
       <formula1>indoorspace</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR3:AR101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS3:AS101">
       <formula1>filtertype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS3:AS101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT3:AT101">
       <formula1>heatingandcoolingsystemtype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT3:AT101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU3:AU101">
       <formula1>substructuretype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU3:AU101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV101">
       <formula1>lighttype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW3:AW101">
       <formula1>buildingsetting</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW3:AW101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX3:AX101">
       <formula1>buildingoccupancytype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX3:AX101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY3:AY101">
       <formula1>spacetypicalstate</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB3:BB101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC3:BC101">
       <formula1>ventilationtype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EU3:EU101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EV3:EV101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FJ3:FJ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FK3:FK101">
       <formula1>frequencyofcleaning</formula1>
     </dataValidation>
   </dataValidations>
@@ -6354,1888 +6366,1888 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:FJ294"/>
+  <dimension ref="H1:FK294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="7:166">
-      <c r="G1" t="s">
-        <v>276</v>
-      </c>
+    <row r="1" spans="8:167">
       <c r="H1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J1" t="s">
-        <v>317</v>
-      </c>
-      <c r="W1" t="s">
-        <v>350</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>387</v>
+        <v>278</v>
+      </c>
+      <c r="I1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K1" t="s">
+        <v>319</v>
+      </c>
+      <c r="X1" t="s">
+        <v>352</v>
       </c>
       <c r="AO1" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="AP1" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="AQ1" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AR1" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="AS1" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="AT1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AU1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AV1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AW1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="AX1" t="s">
-        <v>488</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>498</v>
-      </c>
-      <c r="EU1" t="s">
-        <v>695</v>
-      </c>
-      <c r="FJ1" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="2" spans="7:166">
-      <c r="G2" t="s">
-        <v>277</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>490</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>500</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>697</v>
+      </c>
+      <c r="FK1" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="2" spans="8:167">
       <c r="H2" t="s">
-        <v>309</v>
-      </c>
-      <c r="J2" t="s">
-        <v>318</v>
-      </c>
-      <c r="W2" t="s">
-        <v>351</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>388</v>
+        <v>279</v>
+      </c>
+      <c r="I2" t="s">
+        <v>311</v>
+      </c>
+      <c r="K2" t="s">
+        <v>320</v>
+      </c>
+      <c r="X2" t="s">
+        <v>353</v>
       </c>
       <c r="AO2" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="AP2" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AQ2" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AR2" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="AS2" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="AT2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="AU2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AV2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AW2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="AX2" t="s">
-        <v>489</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>499</v>
-      </c>
-      <c r="EU2" t="s">
-        <v>696</v>
-      </c>
-      <c r="FJ2" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="3" spans="7:166">
-      <c r="G3" t="s">
-        <v>278</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>491</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>501</v>
+      </c>
+      <c r="EV2" t="s">
+        <v>698</v>
+      </c>
+      <c r="FK2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="3" spans="8:167">
       <c r="H3" t="s">
-        <v>310</v>
-      </c>
-      <c r="J3" t="s">
-        <v>319</v>
-      </c>
-      <c r="W3" t="s">
-        <v>352</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>389</v>
+        <v>280</v>
+      </c>
+      <c r="I3" t="s">
+        <v>312</v>
+      </c>
+      <c r="K3" t="s">
+        <v>321</v>
+      </c>
+      <c r="X3" t="s">
+        <v>354</v>
       </c>
       <c r="AO3" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="AP3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AQ3" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AR3" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="AS3" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="AT3" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="AU3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AV3" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AW3" t="s">
-        <v>468</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>500</v>
-      </c>
-      <c r="EU3" t="s">
-        <v>697</v>
-      </c>
-      <c r="FJ3" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="4" spans="7:166">
-      <c r="G4" t="s">
-        <v>279</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>470</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>502</v>
+      </c>
+      <c r="EV3" t="s">
+        <v>699</v>
+      </c>
+      <c r="FK3" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="4" spans="8:167">
       <c r="H4" t="s">
-        <v>311</v>
-      </c>
-      <c r="J4" t="s">
-        <v>320</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>390</v>
+        <v>281</v>
+      </c>
+      <c r="I4" t="s">
+        <v>313</v>
+      </c>
+      <c r="K4" t="s">
+        <v>322</v>
       </c>
       <c r="AO4" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="AP4" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AQ4" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AR4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="AS4" t="s">
-        <v>446</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>463</v>
+        <v>439</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>448</v>
       </c>
       <c r="AW4" t="s">
-        <v>469</v>
-      </c>
-      <c r="EU4" t="s">
-        <v>698</v>
-      </c>
-      <c r="FJ4" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="5" spans="7:166">
-      <c r="G5" t="s">
-        <v>280</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>471</v>
+      </c>
+      <c r="EV4" t="s">
+        <v>700</v>
+      </c>
+      <c r="FK4" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="5" spans="8:167">
       <c r="H5" t="s">
-        <v>312</v>
-      </c>
-      <c r="J5" t="s">
-        <v>321</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>391</v>
+        <v>282</v>
+      </c>
+      <c r="I5" t="s">
+        <v>314</v>
+      </c>
+      <c r="K5" t="s">
+        <v>323</v>
       </c>
       <c r="AO5" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="AP5" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="AQ5" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AR5" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="AS5" t="s">
-        <v>447</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>470</v>
-      </c>
-      <c r="EU5" t="s">
-        <v>699</v>
-      </c>
-      <c r="FJ5" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="6" spans="7:166">
-      <c r="G6" t="s">
-        <v>281</v>
-      </c>
-      <c r="J6" t="s">
-        <v>322</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>392</v>
+        <v>440</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>449</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>472</v>
+      </c>
+      <c r="EV5" t="s">
+        <v>701</v>
+      </c>
+      <c r="FK5" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="6" spans="8:167">
+      <c r="H6" t="s">
+        <v>283</v>
+      </c>
+      <c r="K6" t="s">
+        <v>324</v>
       </c>
       <c r="AO6" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="AP6" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="AQ6" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="AR6" t="s">
-        <v>439</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>471</v>
-      </c>
-      <c r="EU6" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="7" spans="7:166">
-      <c r="G7" t="s">
-        <v>282</v>
-      </c>
-      <c r="J7" t="s">
-        <v>323</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>393</v>
+        <v>431</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>441</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>473</v>
+      </c>
+      <c r="EV6" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="7" spans="8:167">
+      <c r="H7" t="s">
+        <v>284</v>
+      </c>
+      <c r="K7" t="s">
+        <v>325</v>
       </c>
       <c r="AO7" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="AP7" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="AQ7" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="AR7" t="s">
-        <v>440</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>472</v>
-      </c>
-      <c r="EU7" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="8" spans="7:166">
-      <c r="G8" t="s">
-        <v>283</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>394</v>
+        <v>432</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>442</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>474</v>
+      </c>
+      <c r="EV7" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="8" spans="8:167">
+      <c r="H8" t="s">
+        <v>285</v>
       </c>
       <c r="AO8" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="AP8" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="AQ8" t="s">
-        <v>431</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>473</v>
-      </c>
-      <c r="EU8" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="9" spans="7:166">
-      <c r="G9" t="s">
-        <v>284</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>395</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>474</v>
-      </c>
-      <c r="EU9" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="10" spans="7:166">
-      <c r="G10" t="s">
-        <v>285</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>396</v>
-      </c>
-      <c r="AW10" t="s">
+        <v>423</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>433</v>
+      </c>
+      <c r="AX8" t="s">
         <v>475</v>
       </c>
-      <c r="EU10" t="s">
+      <c r="EV8" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="11" spans="7:166">
-      <c r="G11" t="s">
+    <row r="9" spans="8:167">
+      <c r="H9" t="s">
         <v>286</v>
       </c>
-      <c r="AN11" t="s">
+      <c r="AO9" t="s">
         <v>397</v>
       </c>
-      <c r="AW11" t="s">
+      <c r="AX9" t="s">
         <v>476</v>
       </c>
-      <c r="EU11" t="s">
+      <c r="EV9" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="12" spans="7:166">
-      <c r="G12" t="s">
+    <row r="10" spans="8:167">
+      <c r="H10" t="s">
         <v>287</v>
       </c>
-      <c r="AN12" t="s">
+      <c r="AO10" t="s">
         <v>398</v>
       </c>
-      <c r="AW12" t="s">
-        <v>431</v>
-      </c>
-      <c r="EU12" t="s">
+      <c r="AX10" t="s">
+        <v>477</v>
+      </c>
+      <c r="EV10" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="13" spans="7:166">
-      <c r="G13" t="s">
+    <row r="11" spans="8:167">
+      <c r="H11" t="s">
         <v>288</v>
       </c>
-      <c r="AN13" t="s">
+      <c r="AO11" t="s">
         <v>399</v>
       </c>
-      <c r="AW13" t="s">
-        <v>477</v>
-      </c>
-      <c r="EU13" t="s">
+      <c r="AX11" t="s">
+        <v>478</v>
+      </c>
+      <c r="EV11" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="14" spans="7:166">
-      <c r="G14" t="s">
+    <row r="12" spans="8:167">
+      <c r="H12" t="s">
         <v>289</v>
       </c>
-      <c r="AN14" t="s">
+      <c r="AO12" t="s">
         <v>400</v>
       </c>
-      <c r="AW14" t="s">
-        <v>478</v>
-      </c>
-      <c r="EU14" t="s">
+      <c r="AX12" t="s">
+        <v>433</v>
+      </c>
+      <c r="EV12" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="15" spans="7:166">
-      <c r="G15" t="s">
+    <row r="13" spans="8:167">
+      <c r="H13" t="s">
         <v>290</v>
       </c>
-      <c r="AN15" t="s">
+      <c r="AO13" t="s">
         <v>401</v>
       </c>
-      <c r="AW15" t="s">
+      <c r="AX13" t="s">
         <v>479</v>
       </c>
-      <c r="EU15" t="s">
+      <c r="EV13" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="16" spans="7:166">
-      <c r="G16" t="s">
+    <row r="14" spans="8:167">
+      <c r="H14" t="s">
         <v>291</v>
       </c>
-      <c r="AW16" t="s">
+      <c r="AO14" t="s">
+        <v>402</v>
+      </c>
+      <c r="AX14" t="s">
         <v>480</v>
       </c>
-      <c r="EU16" t="s">
+      <c r="EV14" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="17" spans="7:151">
-      <c r="G17" t="s">
+    <row r="15" spans="8:167">
+      <c r="H15" t="s">
         <v>292</v>
       </c>
-      <c r="AW17" t="s">
+      <c r="AO15" t="s">
+        <v>403</v>
+      </c>
+      <c r="AX15" t="s">
         <v>481</v>
       </c>
-      <c r="EU17" t="s">
+      <c r="EV15" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="18" spans="7:151">
-      <c r="G18" t="s">
+    <row r="16" spans="8:167">
+      <c r="H16" t="s">
         <v>293</v>
       </c>
-      <c r="AW18" t="s">
+      <c r="AX16" t="s">
         <v>482</v>
       </c>
-      <c r="EU18" t="s">
+      <c r="EV16" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="19" spans="7:151">
-      <c r="G19" t="s">
+    <row r="17" spans="8:152">
+      <c r="H17" t="s">
         <v>294</v>
       </c>
-      <c r="AW19" t="s">
+      <c r="AX17" t="s">
         <v>483</v>
       </c>
-      <c r="EU19" t="s">
+      <c r="EV17" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="20" spans="7:151">
-      <c r="G20" t="s">
+    <row r="18" spans="8:152">
+      <c r="H18" t="s">
         <v>295</v>
       </c>
-      <c r="AW20" t="s">
+      <c r="AX18" t="s">
         <v>484</v>
       </c>
-      <c r="EU20" t="s">
+      <c r="EV18" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="21" spans="7:151">
-      <c r="G21" t="s">
+    <row r="19" spans="8:152">
+      <c r="H19" t="s">
         <v>296</v>
       </c>
-      <c r="AW21" t="s">
+      <c r="AX19" t="s">
         <v>485</v>
       </c>
-      <c r="EU21" t="s">
+      <c r="EV19" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="22" spans="7:151">
-      <c r="G22" t="s">
+    <row r="20" spans="8:152">
+      <c r="H20" t="s">
         <v>297</v>
       </c>
-      <c r="EU22" t="s">
+      <c r="AX20" t="s">
+        <v>486</v>
+      </c>
+      <c r="EV20" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="23" spans="7:151">
-      <c r="G23" t="s">
+    <row r="21" spans="8:152">
+      <c r="H21" t="s">
         <v>298</v>
       </c>
-      <c r="EU23" t="s">
+      <c r="AX21" t="s">
+        <v>487</v>
+      </c>
+      <c r="EV21" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="24" spans="7:151">
-      <c r="G24" t="s">
+    <row r="22" spans="8:152">
+      <c r="H22" t="s">
         <v>299</v>
       </c>
-      <c r="EU24" t="s">
+      <c r="EV22" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="25" spans="7:151">
-      <c r="G25" t="s">
+    <row r="23" spans="8:152">
+      <c r="H23" t="s">
         <v>300</v>
       </c>
-      <c r="EU25" t="s">
+      <c r="EV23" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="26" spans="7:151">
-      <c r="G26" t="s">
+    <row r="24" spans="8:152">
+      <c r="H24" t="s">
         <v>301</v>
       </c>
-      <c r="EU26" t="s">
+      <c r="EV24" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="27" spans="7:151">
-      <c r="G27" t="s">
+    <row r="25" spans="8:152">
+      <c r="H25" t="s">
         <v>302</v>
       </c>
-      <c r="EU27" t="s">
+      <c r="EV25" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="28" spans="7:151">
-      <c r="G28" t="s">
+    <row r="26" spans="8:152">
+      <c r="H26" t="s">
         <v>303</v>
       </c>
-      <c r="EU28" t="s">
+      <c r="EV26" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="29" spans="7:151">
-      <c r="G29" t="s">
+    <row r="27" spans="8:152">
+      <c r="H27" t="s">
         <v>304</v>
       </c>
-      <c r="EU29" t="s">
+      <c r="EV27" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="30" spans="7:151">
-      <c r="G30" t="s">
+    <row r="28" spans="8:152">
+      <c r="H28" t="s">
         <v>305</v>
       </c>
-      <c r="EU30" t="s">
+      <c r="EV28" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="31" spans="7:151">
-      <c r="EU31" t="s">
+    <row r="29" spans="8:152">
+      <c r="H29" t="s">
+        <v>306</v>
+      </c>
+      <c r="EV29" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="32" spans="7:151">
-      <c r="EU32" t="s">
+    <row r="30" spans="8:152">
+      <c r="H30" t="s">
+        <v>307</v>
+      </c>
+      <c r="EV30" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="33" spans="151:151">
-      <c r="EU33" t="s">
+    <row r="31" spans="8:152">
+      <c r="EV31" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="34" spans="151:151">
-      <c r="EU34" t="s">
+    <row r="32" spans="8:152">
+      <c r="EV32" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="35" spans="151:151">
-      <c r="EU35" t="s">
+    <row r="33" spans="152:152">
+      <c r="EV33" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="36" spans="151:151">
-      <c r="EU36" t="s">
+    <row r="34" spans="152:152">
+      <c r="EV34" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="37" spans="151:151">
-      <c r="EU37" t="s">
+    <row r="35" spans="152:152">
+      <c r="EV35" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="38" spans="151:151">
-      <c r="EU38" t="s">
+    <row r="36" spans="152:152">
+      <c r="EV36" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="39" spans="151:151">
-      <c r="EU39" t="s">
+    <row r="37" spans="152:152">
+      <c r="EV37" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="40" spans="151:151">
-      <c r="EU40" t="s">
+    <row r="38" spans="152:152">
+      <c r="EV38" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="41" spans="151:151">
-      <c r="EU41" t="s">
+    <row r="39" spans="152:152">
+      <c r="EV39" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="42" spans="151:151">
-      <c r="EU42" t="s">
+    <row r="40" spans="152:152">
+      <c r="EV40" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="43" spans="151:151">
-      <c r="EU43" t="s">
+    <row r="41" spans="152:152">
+      <c r="EV41" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="44" spans="151:151">
-      <c r="EU44" t="s">
+    <row r="42" spans="152:152">
+      <c r="EV42" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="45" spans="151:151">
-      <c r="EU45" t="s">
+    <row r="43" spans="152:152">
+      <c r="EV43" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="46" spans="151:151">
-      <c r="EU46" t="s">
+    <row r="44" spans="152:152">
+      <c r="EV44" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="47" spans="151:151">
-      <c r="EU47" t="s">
+    <row r="45" spans="152:152">
+      <c r="EV45" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="48" spans="151:151">
-      <c r="EU48" t="s">
+    <row r="46" spans="152:152">
+      <c r="EV46" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="49" spans="151:151">
-      <c r="EU49" t="s">
+    <row r="47" spans="152:152">
+      <c r="EV47" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="50" spans="151:151">
-      <c r="EU50" t="s">
+    <row r="48" spans="152:152">
+      <c r="EV48" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="51" spans="151:151">
-      <c r="EU51" t="s">
+    <row r="49" spans="152:152">
+      <c r="EV49" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="52" spans="151:151">
-      <c r="EU52" t="s">
+    <row r="50" spans="152:152">
+      <c r="EV50" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="53" spans="151:151">
-      <c r="EU53" t="s">
+    <row r="51" spans="152:152">
+      <c r="EV51" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="54" spans="151:151">
-      <c r="EU54" t="s">
+    <row r="52" spans="152:152">
+      <c r="EV52" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="55" spans="151:151">
-      <c r="EU55" t="s">
+    <row r="53" spans="152:152">
+      <c r="EV53" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="56" spans="151:151">
-      <c r="EU56" t="s">
+    <row r="54" spans="152:152">
+      <c r="EV54" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="57" spans="151:151">
-      <c r="EU57" t="s">
+    <row r="55" spans="152:152">
+      <c r="EV55" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="58" spans="151:151">
-      <c r="EU58" t="s">
+    <row r="56" spans="152:152">
+      <c r="EV56" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="59" spans="151:151">
-      <c r="EU59" t="s">
+    <row r="57" spans="152:152">
+      <c r="EV57" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="60" spans="151:151">
-      <c r="EU60" t="s">
+    <row r="58" spans="152:152">
+      <c r="EV58" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="61" spans="151:151">
-      <c r="EU61" t="s">
+    <row r="59" spans="152:152">
+      <c r="EV59" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="62" spans="151:151">
-      <c r="EU62" t="s">
+    <row r="60" spans="152:152">
+      <c r="EV60" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="63" spans="151:151">
-      <c r="EU63" t="s">
+    <row r="61" spans="152:152">
+      <c r="EV61" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="64" spans="151:151">
-      <c r="EU64" t="s">
+    <row r="62" spans="152:152">
+      <c r="EV62" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="65" spans="151:151">
-      <c r="EU65" t="s">
+    <row r="63" spans="152:152">
+      <c r="EV63" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="66" spans="151:151">
-      <c r="EU66" t="s">
+    <row r="64" spans="152:152">
+      <c r="EV64" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="67" spans="151:151">
-      <c r="EU67" t="s">
+    <row r="65" spans="152:152">
+      <c r="EV65" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="68" spans="151:151">
-      <c r="EU68" t="s">
+    <row r="66" spans="152:152">
+      <c r="EV66" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="69" spans="151:151">
-      <c r="EU69" t="s">
+    <row r="67" spans="152:152">
+      <c r="EV67" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="70" spans="151:151">
-      <c r="EU70" t="s">
+    <row r="68" spans="152:152">
+      <c r="EV68" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="71" spans="151:151">
-      <c r="EU71" t="s">
+    <row r="69" spans="152:152">
+      <c r="EV69" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="72" spans="151:151">
-      <c r="EU72" t="s">
+    <row r="70" spans="152:152">
+      <c r="EV70" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="73" spans="151:151">
-      <c r="EU73" t="s">
+    <row r="71" spans="152:152">
+      <c r="EV71" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="74" spans="151:151">
-      <c r="EU74" t="s">
+    <row r="72" spans="152:152">
+      <c r="EV72" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="75" spans="151:151">
-      <c r="EU75" t="s">
+    <row r="73" spans="152:152">
+      <c r="EV73" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="76" spans="151:151">
-      <c r="EU76" t="s">
+    <row r="74" spans="152:152">
+      <c r="EV74" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="77" spans="151:151">
-      <c r="EU77" t="s">
+    <row r="75" spans="152:152">
+      <c r="EV75" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="78" spans="151:151">
-      <c r="EU78" t="s">
+    <row r="76" spans="152:152">
+      <c r="EV76" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="79" spans="151:151">
-      <c r="EU79" t="s">
+    <row r="77" spans="152:152">
+      <c r="EV77" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="80" spans="151:151">
-      <c r="EU80" t="s">
+    <row r="78" spans="152:152">
+      <c r="EV78" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="81" spans="151:151">
-      <c r="EU81" t="s">
+    <row r="79" spans="152:152">
+      <c r="EV79" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="82" spans="151:151">
-      <c r="EU82" t="s">
+    <row r="80" spans="152:152">
+      <c r="EV80" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="83" spans="151:151">
-      <c r="EU83" t="s">
+    <row r="81" spans="152:152">
+      <c r="EV81" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="84" spans="151:151">
-      <c r="EU84" t="s">
+    <row r="82" spans="152:152">
+      <c r="EV82" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="85" spans="151:151">
-      <c r="EU85" t="s">
+    <row r="83" spans="152:152">
+      <c r="EV83" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="86" spans="151:151">
-      <c r="EU86" t="s">
+    <row r="84" spans="152:152">
+      <c r="EV84" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="87" spans="151:151">
-      <c r="EU87" t="s">
+    <row r="85" spans="152:152">
+      <c r="EV85" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="88" spans="151:151">
-      <c r="EU88" t="s">
+    <row r="86" spans="152:152">
+      <c r="EV86" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="89" spans="151:151">
-      <c r="EU89" t="s">
+    <row r="87" spans="152:152">
+      <c r="EV87" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="90" spans="151:151">
-      <c r="EU90" t="s">
+    <row r="88" spans="152:152">
+      <c r="EV88" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="91" spans="151:151">
-      <c r="EU91" t="s">
+    <row r="89" spans="152:152">
+      <c r="EV89" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="92" spans="151:151">
-      <c r="EU92" t="s">
+    <row r="90" spans="152:152">
+      <c r="EV90" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="93" spans="151:151">
-      <c r="EU93" t="s">
+    <row r="91" spans="152:152">
+      <c r="EV91" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="94" spans="151:151">
-      <c r="EU94" t="s">
+    <row r="92" spans="152:152">
+      <c r="EV92" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="95" spans="151:151">
-      <c r="EU95" t="s">
+    <row r="93" spans="152:152">
+      <c r="EV93" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="96" spans="151:151">
-      <c r="EU96" t="s">
+    <row r="94" spans="152:152">
+      <c r="EV94" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="97" spans="151:151">
-      <c r="EU97" t="s">
+    <row r="95" spans="152:152">
+      <c r="EV95" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="98" spans="151:151">
-      <c r="EU98" t="s">
+    <row r="96" spans="152:152">
+      <c r="EV96" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="99" spans="151:151">
-      <c r="EU99" t="s">
+    <row r="97" spans="152:152">
+      <c r="EV97" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="100" spans="151:151">
-      <c r="EU100" t="s">
+    <row r="98" spans="152:152">
+      <c r="EV98" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="101" spans="151:151">
-      <c r="EU101" t="s">
+    <row r="99" spans="152:152">
+      <c r="EV99" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="102" spans="151:151">
-      <c r="EU102" t="s">
+    <row r="100" spans="152:152">
+      <c r="EV100" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="103" spans="151:151">
-      <c r="EU103" t="s">
+    <row r="101" spans="152:152">
+      <c r="EV101" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="104" spans="151:151">
-      <c r="EU104" t="s">
+    <row r="102" spans="152:152">
+      <c r="EV102" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="105" spans="151:151">
-      <c r="EU105" t="s">
+    <row r="103" spans="152:152">
+      <c r="EV103" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="106" spans="151:151">
-      <c r="EU106" t="s">
+    <row r="104" spans="152:152">
+      <c r="EV104" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="107" spans="151:151">
-      <c r="EU107" t="s">
+    <row r="105" spans="152:152">
+      <c r="EV105" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="108" spans="151:151">
-      <c r="EU108" t="s">
+    <row r="106" spans="152:152">
+      <c r="EV106" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="109" spans="151:151">
-      <c r="EU109" t="s">
+    <row r="107" spans="152:152">
+      <c r="EV107" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="110" spans="151:151">
-      <c r="EU110" t="s">
+    <row r="108" spans="152:152">
+      <c r="EV108" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="111" spans="151:151">
-      <c r="EU111" t="s">
+    <row r="109" spans="152:152">
+      <c r="EV109" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="112" spans="151:151">
-      <c r="EU112" t="s">
+    <row r="110" spans="152:152">
+      <c r="EV110" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="113" spans="151:151">
-      <c r="EU113" t="s">
+    <row r="111" spans="152:152">
+      <c r="EV111" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="114" spans="151:151">
-      <c r="EU114" t="s">
+    <row r="112" spans="152:152">
+      <c r="EV112" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="115" spans="151:151">
-      <c r="EU115" t="s">
+    <row r="113" spans="152:152">
+      <c r="EV113" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="116" spans="151:151">
-      <c r="EU116" t="s">
+    <row r="114" spans="152:152">
+      <c r="EV114" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="117" spans="151:151">
-      <c r="EU117" t="s">
+    <row r="115" spans="152:152">
+      <c r="EV115" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="118" spans="151:151">
-      <c r="EU118" t="s">
+    <row r="116" spans="152:152">
+      <c r="EV116" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="119" spans="151:151">
-      <c r="EU119" t="s">
+    <row r="117" spans="152:152">
+      <c r="EV117" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="120" spans="151:151">
-      <c r="EU120" t="s">
+    <row r="118" spans="152:152">
+      <c r="EV118" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="121" spans="151:151">
-      <c r="EU121" t="s">
+    <row r="119" spans="152:152">
+      <c r="EV119" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="122" spans="151:151">
-      <c r="EU122" t="s">
+    <row r="120" spans="152:152">
+      <c r="EV120" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="123" spans="151:151">
-      <c r="EU123" t="s">
+    <row r="121" spans="152:152">
+      <c r="EV121" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="124" spans="151:151">
-      <c r="EU124" t="s">
+    <row r="122" spans="152:152">
+      <c r="EV122" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="125" spans="151:151">
-      <c r="EU125" t="s">
+    <row r="123" spans="152:152">
+      <c r="EV123" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="126" spans="151:151">
-      <c r="EU126" t="s">
+    <row r="124" spans="152:152">
+      <c r="EV124" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="127" spans="151:151">
-      <c r="EU127" t="s">
+    <row r="125" spans="152:152">
+      <c r="EV125" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="128" spans="151:151">
-      <c r="EU128" t="s">
+    <row r="126" spans="152:152">
+      <c r="EV126" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="129" spans="151:151">
-      <c r="EU129" t="s">
+    <row r="127" spans="152:152">
+      <c r="EV127" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="130" spans="151:151">
-      <c r="EU130" t="s">
+    <row r="128" spans="152:152">
+      <c r="EV128" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="131" spans="151:151">
-      <c r="EU131" t="s">
+    <row r="129" spans="152:152">
+      <c r="EV129" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="132" spans="151:151">
-      <c r="EU132" t="s">
+    <row r="130" spans="152:152">
+      <c r="EV130" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="133" spans="151:151">
-      <c r="EU133" t="s">
+    <row r="131" spans="152:152">
+      <c r="EV131" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="134" spans="151:151">
-      <c r="EU134" t="s">
+    <row r="132" spans="152:152">
+      <c r="EV132" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="135" spans="151:151">
-      <c r="EU135" t="s">
+    <row r="133" spans="152:152">
+      <c r="EV133" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="136" spans="151:151">
-      <c r="EU136" t="s">
+    <row r="134" spans="152:152">
+      <c r="EV134" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="137" spans="151:151">
-      <c r="EU137" t="s">
+    <row r="135" spans="152:152">
+      <c r="EV135" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="138" spans="151:151">
-      <c r="EU138" t="s">
+    <row r="136" spans="152:152">
+      <c r="EV136" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="139" spans="151:151">
-      <c r="EU139" t="s">
+    <row r="137" spans="152:152">
+      <c r="EV137" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="140" spans="151:151">
-      <c r="EU140" t="s">
+    <row r="138" spans="152:152">
+      <c r="EV138" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="141" spans="151:151">
-      <c r="EU141" t="s">
+    <row r="139" spans="152:152">
+      <c r="EV139" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="142" spans="151:151">
-      <c r="EU142" t="s">
+    <row r="140" spans="152:152">
+      <c r="EV140" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="143" spans="151:151">
-      <c r="EU143" t="s">
+    <row r="141" spans="152:152">
+      <c r="EV141" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="144" spans="151:151">
-      <c r="EU144" t="s">
+    <row r="142" spans="152:152">
+      <c r="EV142" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="145" spans="151:151">
-      <c r="EU145" t="s">
+    <row r="143" spans="152:152">
+      <c r="EV143" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="146" spans="151:151">
-      <c r="EU146" t="s">
+    <row r="144" spans="152:152">
+      <c r="EV144" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="147" spans="151:151">
-      <c r="EU147" t="s">
+    <row r="145" spans="152:152">
+      <c r="EV145" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="148" spans="151:151">
-      <c r="EU148" t="s">
+    <row r="146" spans="152:152">
+      <c r="EV146" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="149" spans="151:151">
-      <c r="EU149" t="s">
+    <row r="147" spans="152:152">
+      <c r="EV147" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="150" spans="151:151">
-      <c r="EU150" t="s">
+    <row r="148" spans="152:152">
+      <c r="EV148" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="151" spans="151:151">
-      <c r="EU151" t="s">
+    <row r="149" spans="152:152">
+      <c r="EV149" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="152" spans="151:151">
-      <c r="EU152" t="s">
+    <row r="150" spans="152:152">
+      <c r="EV150" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="153" spans="151:151">
-      <c r="EU153" t="s">
+    <row r="151" spans="152:152">
+      <c r="EV151" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="154" spans="151:151">
-      <c r="EU154" t="s">
+    <row r="152" spans="152:152">
+      <c r="EV152" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="155" spans="151:151">
-      <c r="EU155" t="s">
+    <row r="153" spans="152:152">
+      <c r="EV153" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="156" spans="151:151">
-      <c r="EU156" t="s">
+    <row r="154" spans="152:152">
+      <c r="EV154" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="157" spans="151:151">
-      <c r="EU157" t="s">
+    <row r="155" spans="152:152">
+      <c r="EV155" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="158" spans="151:151">
-      <c r="EU158" t="s">
+    <row r="156" spans="152:152">
+      <c r="EV156" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="159" spans="151:151">
-      <c r="EU159" t="s">
+    <row r="157" spans="152:152">
+      <c r="EV157" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="160" spans="151:151">
-      <c r="EU160" t="s">
+    <row r="158" spans="152:152">
+      <c r="EV158" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="161" spans="151:151">
-      <c r="EU161" t="s">
+    <row r="159" spans="152:152">
+      <c r="EV159" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="162" spans="151:151">
-      <c r="EU162" t="s">
+    <row r="160" spans="152:152">
+      <c r="EV160" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="163" spans="151:151">
-      <c r="EU163" t="s">
+    <row r="161" spans="152:152">
+      <c r="EV161" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="164" spans="151:151">
-      <c r="EU164" t="s">
+    <row r="162" spans="152:152">
+      <c r="EV162" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="165" spans="151:151">
-      <c r="EU165" t="s">
+    <row r="163" spans="152:152">
+      <c r="EV163" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="166" spans="151:151">
-      <c r="EU166" t="s">
+    <row r="164" spans="152:152">
+      <c r="EV164" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="167" spans="151:151">
-      <c r="EU167" t="s">
+    <row r="165" spans="152:152">
+      <c r="EV165" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="168" spans="151:151">
-      <c r="EU168" t="s">
+    <row r="166" spans="152:152">
+      <c r="EV166" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="169" spans="151:151">
-      <c r="EU169" t="s">
+    <row r="167" spans="152:152">
+      <c r="EV167" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="170" spans="151:151">
-      <c r="EU170" t="s">
+    <row r="168" spans="152:152">
+      <c r="EV168" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="171" spans="151:151">
-      <c r="EU171" t="s">
+    <row r="169" spans="152:152">
+      <c r="EV169" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="172" spans="151:151">
-      <c r="EU172" t="s">
+    <row r="170" spans="152:152">
+      <c r="EV170" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="173" spans="151:151">
-      <c r="EU173" t="s">
+    <row r="171" spans="152:152">
+      <c r="EV171" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="174" spans="151:151">
-      <c r="EU174" t="s">
+    <row r="172" spans="152:152">
+      <c r="EV172" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="175" spans="151:151">
-      <c r="EU175" t="s">
+    <row r="173" spans="152:152">
+      <c r="EV173" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="176" spans="151:151">
-      <c r="EU176" t="s">
+    <row r="174" spans="152:152">
+      <c r="EV174" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="177" spans="151:151">
-      <c r="EU177" t="s">
+    <row r="175" spans="152:152">
+      <c r="EV175" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="178" spans="151:151">
-      <c r="EU178" t="s">
+    <row r="176" spans="152:152">
+      <c r="EV176" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="179" spans="151:151">
-      <c r="EU179" t="s">
+    <row r="177" spans="152:152">
+      <c r="EV177" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="180" spans="151:151">
-      <c r="EU180" t="s">
+    <row r="178" spans="152:152">
+      <c r="EV178" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="181" spans="151:151">
-      <c r="EU181" t="s">
+    <row r="179" spans="152:152">
+      <c r="EV179" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="182" spans="151:151">
-      <c r="EU182" t="s">
+    <row r="180" spans="152:152">
+      <c r="EV180" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="183" spans="151:151">
-      <c r="EU183" t="s">
+    <row r="181" spans="152:152">
+      <c r="EV181" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="184" spans="151:151">
-      <c r="EU184" t="s">
+    <row r="182" spans="152:152">
+      <c r="EV182" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="185" spans="151:151">
-      <c r="EU185" t="s">
+    <row r="183" spans="152:152">
+      <c r="EV183" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="186" spans="151:151">
-      <c r="EU186" t="s">
+    <row r="184" spans="152:152">
+      <c r="EV184" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="187" spans="151:151">
-      <c r="EU187" t="s">
+    <row r="185" spans="152:152">
+      <c r="EV185" t="s">
         <v>881</v>
       </c>
     </row>
-    <row r="188" spans="151:151">
-      <c r="EU188" t="s">
+    <row r="186" spans="152:152">
+      <c r="EV186" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="189" spans="151:151">
-      <c r="EU189" t="s">
+    <row r="187" spans="152:152">
+      <c r="EV187" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="190" spans="151:151">
-      <c r="EU190" t="s">
+    <row r="188" spans="152:152">
+      <c r="EV188" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="191" spans="151:151">
-      <c r="EU191" t="s">
+    <row r="189" spans="152:152">
+      <c r="EV189" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="192" spans="151:151">
-      <c r="EU192" t="s">
+    <row r="190" spans="152:152">
+      <c r="EV190" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="193" spans="151:151">
-      <c r="EU193" t="s">
+    <row r="191" spans="152:152">
+      <c r="EV191" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="194" spans="151:151">
-      <c r="EU194" t="s">
+    <row r="192" spans="152:152">
+      <c r="EV192" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="195" spans="151:151">
-      <c r="EU195" t="s">
+    <row r="193" spans="152:152">
+      <c r="EV193" t="s">
         <v>889</v>
       </c>
     </row>
-    <row r="196" spans="151:151">
-      <c r="EU196" t="s">
+    <row r="194" spans="152:152">
+      <c r="EV194" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="197" spans="151:151">
-      <c r="EU197" t="s">
+    <row r="195" spans="152:152">
+      <c r="EV195" t="s">
         <v>891</v>
       </c>
     </row>
-    <row r="198" spans="151:151">
-      <c r="EU198" t="s">
+    <row r="196" spans="152:152">
+      <c r="EV196" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="199" spans="151:151">
-      <c r="EU199" t="s">
+    <row r="197" spans="152:152">
+      <c r="EV197" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="200" spans="151:151">
-      <c r="EU200" t="s">
+    <row r="198" spans="152:152">
+      <c r="EV198" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="201" spans="151:151">
-      <c r="EU201" t="s">
+    <row r="199" spans="152:152">
+      <c r="EV199" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="202" spans="151:151">
-      <c r="EU202" t="s">
+    <row r="200" spans="152:152">
+      <c r="EV200" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="203" spans="151:151">
-      <c r="EU203" t="s">
+    <row r="201" spans="152:152">
+      <c r="EV201" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="204" spans="151:151">
-      <c r="EU204" t="s">
+    <row r="202" spans="152:152">
+      <c r="EV202" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="205" spans="151:151">
-      <c r="EU205" t="s">
+    <row r="203" spans="152:152">
+      <c r="EV203" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="206" spans="151:151">
-      <c r="EU206" t="s">
+    <row r="204" spans="152:152">
+      <c r="EV204" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="207" spans="151:151">
-      <c r="EU207" t="s">
+    <row r="205" spans="152:152">
+      <c r="EV205" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="208" spans="151:151">
-      <c r="EU208" t="s">
+    <row r="206" spans="152:152">
+      <c r="EV206" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="209" spans="151:151">
-      <c r="EU209" t="s">
+    <row r="207" spans="152:152">
+      <c r="EV207" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="210" spans="151:151">
-      <c r="EU210" t="s">
+    <row r="208" spans="152:152">
+      <c r="EV208" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="211" spans="151:151">
-      <c r="EU211" t="s">
+    <row r="209" spans="152:152">
+      <c r="EV209" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="212" spans="151:151">
-      <c r="EU212" t="s">
+    <row r="210" spans="152:152">
+      <c r="EV210" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="213" spans="151:151">
-      <c r="EU213" t="s">
+    <row r="211" spans="152:152">
+      <c r="EV211" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="214" spans="151:151">
-      <c r="EU214" t="s">
+    <row r="212" spans="152:152">
+      <c r="EV212" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="215" spans="151:151">
-      <c r="EU215" t="s">
+    <row r="213" spans="152:152">
+      <c r="EV213" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="216" spans="151:151">
-      <c r="EU216" t="s">
+    <row r="214" spans="152:152">
+      <c r="EV214" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="217" spans="151:151">
-      <c r="EU217" t="s">
+    <row r="215" spans="152:152">
+      <c r="EV215" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="218" spans="151:151">
-      <c r="EU218" t="s">
+    <row r="216" spans="152:152">
+      <c r="EV216" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="219" spans="151:151">
-      <c r="EU219" t="s">
+    <row r="217" spans="152:152">
+      <c r="EV217" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="220" spans="151:151">
-      <c r="EU220" t="s">
+    <row r="218" spans="152:152">
+      <c r="EV218" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="221" spans="151:151">
-      <c r="EU221" t="s">
+    <row r="219" spans="152:152">
+      <c r="EV219" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="222" spans="151:151">
-      <c r="EU222" t="s">
+    <row r="220" spans="152:152">
+      <c r="EV220" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="223" spans="151:151">
-      <c r="EU223" t="s">
+    <row r="221" spans="152:152">
+      <c r="EV221" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="224" spans="151:151">
-      <c r="EU224" t="s">
+    <row r="222" spans="152:152">
+      <c r="EV222" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="225" spans="151:151">
-      <c r="EU225" t="s">
+    <row r="223" spans="152:152">
+      <c r="EV223" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="226" spans="151:151">
-      <c r="EU226" t="s">
+    <row r="224" spans="152:152">
+      <c r="EV224" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="227" spans="151:151">
-      <c r="EU227" t="s">
+    <row r="225" spans="152:152">
+      <c r="EV225" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="228" spans="151:151">
-      <c r="EU228" t="s">
+    <row r="226" spans="152:152">
+      <c r="EV226" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="229" spans="151:151">
-      <c r="EU229" t="s">
+    <row r="227" spans="152:152">
+      <c r="EV227" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="230" spans="151:151">
-      <c r="EU230" t="s">
+    <row r="228" spans="152:152">
+      <c r="EV228" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="231" spans="151:151">
-      <c r="EU231" t="s">
+    <row r="229" spans="152:152">
+      <c r="EV229" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="232" spans="151:151">
-      <c r="EU232" t="s">
+    <row r="230" spans="152:152">
+      <c r="EV230" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="233" spans="151:151">
-      <c r="EU233" t="s">
+    <row r="231" spans="152:152">
+      <c r="EV231" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="234" spans="151:151">
-      <c r="EU234" t="s">
+    <row r="232" spans="152:152">
+      <c r="EV232" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="235" spans="151:151">
-      <c r="EU235" t="s">
+    <row r="233" spans="152:152">
+      <c r="EV233" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="236" spans="151:151">
-      <c r="EU236" t="s">
+    <row r="234" spans="152:152">
+      <c r="EV234" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="237" spans="151:151">
-      <c r="EU237" t="s">
+    <row r="235" spans="152:152">
+      <c r="EV235" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="238" spans="151:151">
-      <c r="EU238" t="s">
+    <row r="236" spans="152:152">
+      <c r="EV236" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="239" spans="151:151">
-      <c r="EU239" t="s">
+    <row r="237" spans="152:152">
+      <c r="EV237" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="240" spans="151:151">
-      <c r="EU240" t="s">
+    <row r="238" spans="152:152">
+      <c r="EV238" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="241" spans="151:151">
-      <c r="EU241" t="s">
+    <row r="239" spans="152:152">
+      <c r="EV239" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="242" spans="151:151">
-      <c r="EU242" t="s">
+    <row r="240" spans="152:152">
+      <c r="EV240" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="243" spans="151:151">
-      <c r="EU243" t="s">
+    <row r="241" spans="152:152">
+      <c r="EV241" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="244" spans="151:151">
-      <c r="EU244" t="s">
+    <row r="242" spans="152:152">
+      <c r="EV242" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="245" spans="151:151">
-      <c r="EU245" t="s">
+    <row r="243" spans="152:152">
+      <c r="EV243" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="246" spans="151:151">
-      <c r="EU246" t="s">
+    <row r="244" spans="152:152">
+      <c r="EV244" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="247" spans="151:151">
-      <c r="EU247" t="s">
+    <row r="245" spans="152:152">
+      <c r="EV245" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="248" spans="151:151">
-      <c r="EU248" t="s">
+    <row r="246" spans="152:152">
+      <c r="EV246" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="249" spans="151:151">
-      <c r="EU249" t="s">
+    <row r="247" spans="152:152">
+      <c r="EV247" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="250" spans="151:151">
-      <c r="EU250" t="s">
+    <row r="248" spans="152:152">
+      <c r="EV248" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="251" spans="151:151">
-      <c r="EU251" t="s">
+    <row r="249" spans="152:152">
+      <c r="EV249" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="252" spans="151:151">
-      <c r="EU252" t="s">
+    <row r="250" spans="152:152">
+      <c r="EV250" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="253" spans="151:151">
-      <c r="EU253" t="s">
+    <row r="251" spans="152:152">
+      <c r="EV251" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="254" spans="151:151">
-      <c r="EU254" t="s">
+    <row r="252" spans="152:152">
+      <c r="EV252" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="255" spans="151:151">
-      <c r="EU255" t="s">
+    <row r="253" spans="152:152">
+      <c r="EV253" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="256" spans="151:151">
-      <c r="EU256" t="s">
+    <row r="254" spans="152:152">
+      <c r="EV254" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="257" spans="151:151">
-      <c r="EU257" t="s">
+    <row r="255" spans="152:152">
+      <c r="EV255" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="258" spans="151:151">
-      <c r="EU258" t="s">
+    <row r="256" spans="152:152">
+      <c r="EV256" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="259" spans="151:151">
-      <c r="EU259" t="s">
+    <row r="257" spans="152:152">
+      <c r="EV257" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="260" spans="151:151">
-      <c r="EU260" t="s">
+    <row r="258" spans="152:152">
+      <c r="EV258" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="261" spans="151:151">
-      <c r="EU261" t="s">
+    <row r="259" spans="152:152">
+      <c r="EV259" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="262" spans="151:151">
-      <c r="EU262" t="s">
+    <row r="260" spans="152:152">
+      <c r="EV260" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="263" spans="151:151">
-      <c r="EU263" t="s">
+    <row r="261" spans="152:152">
+      <c r="EV261" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="264" spans="151:151">
-      <c r="EU264" t="s">
+    <row r="262" spans="152:152">
+      <c r="EV262" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="265" spans="151:151">
-      <c r="EU265" t="s">
+    <row r="263" spans="152:152">
+      <c r="EV263" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="266" spans="151:151">
-      <c r="EU266" t="s">
+    <row r="264" spans="152:152">
+      <c r="EV264" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="267" spans="151:151">
-      <c r="EU267" t="s">
+    <row r="265" spans="152:152">
+      <c r="EV265" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="268" spans="151:151">
-      <c r="EU268" t="s">
+    <row r="266" spans="152:152">
+      <c r="EV266" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="269" spans="151:151">
-      <c r="EU269" t="s">
+    <row r="267" spans="152:152">
+      <c r="EV267" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="270" spans="151:151">
-      <c r="EU270" t="s">
+    <row r="268" spans="152:152">
+      <c r="EV268" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="271" spans="151:151">
-      <c r="EU271" t="s">
+    <row r="269" spans="152:152">
+      <c r="EV269" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="272" spans="151:151">
-      <c r="EU272" t="s">
+    <row r="270" spans="152:152">
+      <c r="EV270" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="273" spans="151:151">
-      <c r="EU273" t="s">
+    <row r="271" spans="152:152">
+      <c r="EV271" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="274" spans="151:151">
-      <c r="EU274" t="s">
+    <row r="272" spans="152:152">
+      <c r="EV272" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="275" spans="151:151">
-      <c r="EU275" t="s">
+    <row r="273" spans="152:152">
+      <c r="EV273" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="276" spans="151:151">
-      <c r="EU276" t="s">
+    <row r="274" spans="152:152">
+      <c r="EV274" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="277" spans="151:151">
-      <c r="EU277" t="s">
+    <row r="275" spans="152:152">
+      <c r="EV275" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="278" spans="151:151">
-      <c r="EU278" t="s">
+    <row r="276" spans="152:152">
+      <c r="EV276" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="279" spans="151:151">
-      <c r="EU279" t="s">
+    <row r="277" spans="152:152">
+      <c r="EV277" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="280" spans="151:151">
-      <c r="EU280" t="s">
+    <row r="278" spans="152:152">
+      <c r="EV278" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="281" spans="151:151">
-      <c r="EU281" t="s">
+    <row r="279" spans="152:152">
+      <c r="EV279" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="282" spans="151:151">
-      <c r="EU282" t="s">
+    <row r="280" spans="152:152">
+      <c r="EV280" t="s">
         <v>976</v>
       </c>
     </row>
-    <row r="283" spans="151:151">
-      <c r="EU283" t="s">
+    <row r="281" spans="152:152">
+      <c r="EV281" t="s">
         <v>977</v>
       </c>
     </row>
-    <row r="284" spans="151:151">
-      <c r="EU284" t="s">
+    <row r="282" spans="152:152">
+      <c r="EV282" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="285" spans="151:151">
-      <c r="EU285" t="s">
+    <row r="283" spans="152:152">
+      <c r="EV283" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="286" spans="151:151">
-      <c r="EU286" t="s">
+    <row r="284" spans="152:152">
+      <c r="EV284" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="287" spans="151:151">
-      <c r="EU287" t="s">
+    <row r="285" spans="152:152">
+      <c r="EV285" t="s">
         <v>981</v>
       </c>
     </row>
-    <row r="288" spans="151:151">
-      <c r="EU288" t="s">
+    <row r="286" spans="152:152">
+      <c r="EV286" t="s">
         <v>982</v>
       </c>
     </row>
-    <row r="289" spans="151:151">
-      <c r="EU289" t="s">
+    <row r="287" spans="152:152">
+      <c r="EV287" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="290" spans="151:151">
-      <c r="EU290" t="s">
+    <row r="288" spans="152:152">
+      <c r="EV288" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="291" spans="151:151">
-      <c r="EU291" t="s">
+    <row r="289" spans="152:152">
+      <c r="EV289" t="s">
         <v>985</v>
       </c>
     </row>
-    <row r="292" spans="151:151">
-      <c r="EU292" t="s">
+    <row r="290" spans="152:152">
+      <c r="EV290" t="s">
         <v>986</v>
       </c>
     </row>
-    <row r="293" spans="151:151">
-      <c r="EU293" t="s">
+    <row r="291" spans="152:152">
+      <c r="EV291" t="s">
         <v>987</v>
       </c>
     </row>
-    <row r="294" spans="151:151">
-      <c r="EU294" t="s">
+    <row r="292" spans="152:152">
+      <c r="EV292" t="s">
         <v>988</v>
+      </c>
+    </row>
+    <row r="293" spans="152:152">
+      <c r="EV293" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="294" spans="152:152">
+      <c r="EV294" t="s">
+        <v>990</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000031/metadata_template_ERC000031.xlsx
+++ b/templates/ERC000031/metadata_template_ERC000031.xlsx
@@ -22,17 +22,17 @@
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="filtertype">'cv_sample'!$AS$1:$AS$7</definedName>
     <definedName name="frequencyofcleaning">'cv_sample'!$FK$1:$FK$5</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$EV$1:$EV$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$EV$1:$EV$294</definedName>
     <definedName name="heatingandcoolingsystemtype">'cv_sample'!$AT$1:$AT$5</definedName>
     <definedName name="indoorspace">'cv_sample'!$AR$1:$AR$8</definedName>
     <definedName name="indoorsurface">'cv_sample'!$AQ$1:$AQ$8</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="lighttype">'cv_sample'!$AV$1:$AV$3</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$I$1:$I$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$K$1:$K$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$X$1:$X$3</definedName>
     <definedName name="spacetypicalstate">'cv_sample'!$AY$1:$AY$2</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="1134">
   <si>
     <t>alias</t>
   </si>
@@ -464,6 +464,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -554,6 +557,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -2348,9 +2354,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -2369,6 +2372,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -2570,6 +2576,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -2579,9 +2588,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -2621,7 +2627,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -2690,6 +2696,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -2765,6 +2774,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2786,6 +2798,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2831,6 +2846,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2843,6 +2861,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2852,9 +2873,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2879,6 +2897,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2939,10 +2960,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3955,10 +3976,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3999,10 +4020,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4029,7 +4050,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4046,7 +4067,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -4063,7 +4084,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -4080,7 +4101,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -4097,7 +4118,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -4114,7 +4135,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -4131,7 +4152,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -4148,7 +4169,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -4165,7 +4186,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -4182,7 +4203,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -4196,7 +4217,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -4210,7 +4231,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -4224,7 +4245,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -4238,7 +4259,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -4252,7 +4273,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -4266,7 +4287,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -4280,7 +4301,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -4294,7 +4315,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -4304,8 +4325,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -4316,7 +4340,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -4327,7 +4351,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -4338,7 +4362,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -4349,7 +4373,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -4360,7 +4384,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -4371,7 +4395,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -4382,7 +4406,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -4393,7 +4417,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -4404,7 +4428,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -4415,7 +4439,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -4426,7 +4450,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -4437,7 +4461,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -4448,7 +4472,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -4456,7 +4480,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -4464,7 +4488,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -4472,7 +4496,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -4480,7 +4504,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -4488,7 +4512,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -4496,7 +4520,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -4504,7 +4528,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -4512,7 +4536,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -4520,7 +4544,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -4528,236 +4552,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4779,27 +4808,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4819,122 +4848,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4958,1320 +4987,1320 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="2" spans="1:220" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
     </row>
   </sheetData>
@@ -6337,1863 +6366,1888 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H1:FK289"/>
+  <dimension ref="H1:FK294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="8:167">
       <c r="H1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="X1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AP1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AQ1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AR1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AS1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AT1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AU1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AV1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AW1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AX1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AY1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="BC1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="EV1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="FK1" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="2" spans="8:167">
       <c r="H2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="X2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AO2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AP2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AQ2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AR2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AS2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AT2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AU2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AV2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AW2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AX2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AY2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="BC2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="EV2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="FK2" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="3" spans="8:167">
       <c r="H3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="X3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AP3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AQ3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AR3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AS3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AT3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AU3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AV3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AW3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AX3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="BC3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="EV3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="FK3" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="4" spans="8:167">
       <c r="H4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AO4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AQ4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AR4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AS4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AT4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AW4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AX4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="EV4" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="FK4" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="5" spans="8:167">
       <c r="H5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AO5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AQ5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AR5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AS5" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AT5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AX5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="EV5" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="FK5" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="6" spans="8:167">
       <c r="H6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AO6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AQ6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AR6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AS6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AX6" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="EV6" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="7" spans="8:167">
       <c r="H7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AQ7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AR7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AS7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AX7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="EV7" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8" spans="8:167">
       <c r="H8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AP8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AQ8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AX8" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="EV8" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="9" spans="8:167">
       <c r="H9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AX9" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="EV9" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="10" spans="8:167">
       <c r="H10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AO10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AX10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="EV10" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="8:167">
       <c r="H11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AO11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AX11" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="EV11" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" spans="8:167">
       <c r="H12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO12" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AX12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="EV12" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="13" spans="8:167">
       <c r="H13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO13" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AX13" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="EV13" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="14" spans="8:167">
       <c r="H14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AX14" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="EV14" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="15" spans="8:167">
       <c r="H15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AX15" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="EV15" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="16" spans="8:167">
       <c r="H16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AX16" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="EV16" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="17" spans="8:152">
       <c r="H17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AX17" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="EV17" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18" spans="8:152">
       <c r="H18" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AX18" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="EV18" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="19" spans="8:152">
       <c r="H19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AX19" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="EV19" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="20" spans="8:152">
       <c r="H20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AX20" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="EV20" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="21" spans="8:152">
       <c r="H21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AX21" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="EV21" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="22" spans="8:152">
       <c r="H22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="EV22" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="23" spans="8:152">
       <c r="H23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="EV23" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="24" spans="8:152">
       <c r="H24" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="EV24" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="25" spans="8:152">
       <c r="H25" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="EV25" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="26" spans="8:152">
       <c r="H26" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="EV26" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="27" spans="8:152">
       <c r="H27" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="EV27" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="28" spans="8:152">
       <c r="H28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="EV28" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="29" spans="8:152">
       <c r="H29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="EV29" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="30" spans="8:152">
       <c r="H30" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="EV30" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="31" spans="8:152">
       <c r="EV31" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="32" spans="8:152">
       <c r="EV32" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="33" spans="152:152">
       <c r="EV33" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="34" spans="152:152">
       <c r="EV34" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="35" spans="152:152">
       <c r="EV35" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="36" spans="152:152">
       <c r="EV36" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="37" spans="152:152">
       <c r="EV37" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="38" spans="152:152">
       <c r="EV38" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="39" spans="152:152">
       <c r="EV39" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="40" spans="152:152">
       <c r="EV40" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="41" spans="152:152">
       <c r="EV41" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="42" spans="152:152">
       <c r="EV42" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="43" spans="152:152">
       <c r="EV43" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="44" spans="152:152">
       <c r="EV44" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="45" spans="152:152">
       <c r="EV45" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="46" spans="152:152">
       <c r="EV46" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="47" spans="152:152">
       <c r="EV47" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="48" spans="152:152">
       <c r="EV48" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="49" spans="152:152">
       <c r="EV49" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="50" spans="152:152">
       <c r="EV50" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="51" spans="152:152">
       <c r="EV51" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="52" spans="152:152">
       <c r="EV52" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="53" spans="152:152">
       <c r="EV53" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="54" spans="152:152">
       <c r="EV54" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="55" spans="152:152">
       <c r="EV55" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="56" spans="152:152">
       <c r="EV56" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="57" spans="152:152">
       <c r="EV57" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="58" spans="152:152">
       <c r="EV58" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="59" spans="152:152">
       <c r="EV59" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="60" spans="152:152">
       <c r="EV60" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="61" spans="152:152">
       <c r="EV61" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="62" spans="152:152">
       <c r="EV62" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="63" spans="152:152">
       <c r="EV63" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="64" spans="152:152">
       <c r="EV64" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="65" spans="152:152">
       <c r="EV65" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="66" spans="152:152">
       <c r="EV66" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="67" spans="152:152">
       <c r="EV67" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="68" spans="152:152">
       <c r="EV68" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="69" spans="152:152">
       <c r="EV69" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="70" spans="152:152">
       <c r="EV70" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="71" spans="152:152">
       <c r="EV71" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="72" spans="152:152">
       <c r="EV72" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="73" spans="152:152">
       <c r="EV73" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="74" spans="152:152">
       <c r="EV74" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="75" spans="152:152">
       <c r="EV75" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="76" spans="152:152">
       <c r="EV76" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="77" spans="152:152">
       <c r="EV77" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="78" spans="152:152">
       <c r="EV78" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="79" spans="152:152">
       <c r="EV79" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
     </row>
     <row r="80" spans="152:152">
       <c r="EV80" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="81" spans="152:152">
       <c r="EV81" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="82" spans="152:152">
       <c r="EV82" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="83" spans="152:152">
       <c r="EV83" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
     </row>
     <row r="84" spans="152:152">
       <c r="EV84" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="85" spans="152:152">
       <c r="EV85" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="86" spans="152:152">
       <c r="EV86" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="87" spans="152:152">
       <c r="EV87" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="88" spans="152:152">
       <c r="EV88" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="89" spans="152:152">
       <c r="EV89" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="90" spans="152:152">
       <c r="EV90" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="91" spans="152:152">
       <c r="EV91" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="92" spans="152:152">
       <c r="EV92" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="93" spans="152:152">
       <c r="EV93" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="94" spans="152:152">
       <c r="EV94" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="95" spans="152:152">
       <c r="EV95" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="96" spans="152:152">
       <c r="EV96" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="97" spans="152:152">
       <c r="EV97" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="98" spans="152:152">
       <c r="EV98" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="99" spans="152:152">
       <c r="EV99" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="100" spans="152:152">
       <c r="EV100" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="101" spans="152:152">
       <c r="EV101" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
     </row>
     <row r="102" spans="152:152">
       <c r="EV102" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="103" spans="152:152">
       <c r="EV103" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="104" spans="152:152">
       <c r="EV104" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="105" spans="152:152">
       <c r="EV105" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="106" spans="152:152">
       <c r="EV106" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="107" spans="152:152">
       <c r="EV107" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="108" spans="152:152">
       <c r="EV108" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="109" spans="152:152">
       <c r="EV109" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="110" spans="152:152">
       <c r="EV110" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="111" spans="152:152">
       <c r="EV111" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="112" spans="152:152">
       <c r="EV112" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="113" spans="152:152">
       <c r="EV113" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="114" spans="152:152">
       <c r="EV114" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="115" spans="152:152">
       <c r="EV115" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="116" spans="152:152">
       <c r="EV116" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="117" spans="152:152">
       <c r="EV117" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="118" spans="152:152">
       <c r="EV118" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="119" spans="152:152">
       <c r="EV119" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="120" spans="152:152">
       <c r="EV120" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="121" spans="152:152">
       <c r="EV121" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="122" spans="152:152">
       <c r="EV122" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="123" spans="152:152">
       <c r="EV123" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="124" spans="152:152">
       <c r="EV124" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="125" spans="152:152">
       <c r="EV125" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="126" spans="152:152">
       <c r="EV126" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="127" spans="152:152">
       <c r="EV127" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="128" spans="152:152">
       <c r="EV128" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="129" spans="152:152">
       <c r="EV129" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="130" spans="152:152">
       <c r="EV130" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="131" spans="152:152">
       <c r="EV131" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="132" spans="152:152">
       <c r="EV132" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="133" spans="152:152">
       <c r="EV133" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="134" spans="152:152">
       <c r="EV134" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="135" spans="152:152">
       <c r="EV135" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="136" spans="152:152">
       <c r="EV136" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="137" spans="152:152">
       <c r="EV137" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="138" spans="152:152">
       <c r="EV138" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="139" spans="152:152">
       <c r="EV139" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="140" spans="152:152">
       <c r="EV140" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="141" spans="152:152">
       <c r="EV141" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="142" spans="152:152">
       <c r="EV142" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="143" spans="152:152">
       <c r="EV143" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="144" spans="152:152">
       <c r="EV144" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="145" spans="152:152">
       <c r="EV145" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="146" spans="152:152">
       <c r="EV146" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="147" spans="152:152">
       <c r="EV147" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="148" spans="152:152">
       <c r="EV148" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="149" spans="152:152">
       <c r="EV149" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="150" spans="152:152">
       <c r="EV150" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="151" spans="152:152">
       <c r="EV151" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="152" spans="152:152">
       <c r="EV152" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="153" spans="152:152">
       <c r="EV153" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="154" spans="152:152">
       <c r="EV154" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="155" spans="152:152">
       <c r="EV155" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="156" spans="152:152">
       <c r="EV156" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="157" spans="152:152">
       <c r="EV157" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="158" spans="152:152">
       <c r="EV158" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="159" spans="152:152">
       <c r="EV159" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="160" spans="152:152">
       <c r="EV160" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="161" spans="152:152">
       <c r="EV161" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="162" spans="152:152">
       <c r="EV162" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="163" spans="152:152">
       <c r="EV163" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="164" spans="152:152">
       <c r="EV164" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="165" spans="152:152">
       <c r="EV165" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="166" spans="152:152">
       <c r="EV166" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="167" spans="152:152">
       <c r="EV167" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="168" spans="152:152">
       <c r="EV168" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="169" spans="152:152">
       <c r="EV169" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="170" spans="152:152">
       <c r="EV170" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="171" spans="152:152">
       <c r="EV171" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="172" spans="152:152">
       <c r="EV172" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="173" spans="152:152">
       <c r="EV173" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="174" spans="152:152">
       <c r="EV174" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="175" spans="152:152">
       <c r="EV175" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="176" spans="152:152">
       <c r="EV176" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="177" spans="152:152">
       <c r="EV177" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="178" spans="152:152">
       <c r="EV178" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="179" spans="152:152">
       <c r="EV179" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="180" spans="152:152">
       <c r="EV180" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="181" spans="152:152">
       <c r="EV181" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="182" spans="152:152">
       <c r="EV182" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="183" spans="152:152">
       <c r="EV183" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="184" spans="152:152">
       <c r="EV184" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="185" spans="152:152">
       <c r="EV185" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="186" spans="152:152">
       <c r="EV186" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="187" spans="152:152">
       <c r="EV187" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="188" spans="152:152">
       <c r="EV188" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="189" spans="152:152">
       <c r="EV189" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="190" spans="152:152">
       <c r="EV190" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="191" spans="152:152">
       <c r="EV191" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="192" spans="152:152">
       <c r="EV192" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="193" spans="152:152">
       <c r="EV193" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="194" spans="152:152">
       <c r="EV194" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="195" spans="152:152">
       <c r="EV195" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="196" spans="152:152">
       <c r="EV196" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="197" spans="152:152">
       <c r="EV197" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="198" spans="152:152">
       <c r="EV198" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="199" spans="152:152">
       <c r="EV199" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="200" spans="152:152">
       <c r="EV200" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="201" spans="152:152">
       <c r="EV201" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="202" spans="152:152">
       <c r="EV202" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="203" spans="152:152">
       <c r="EV203" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="204" spans="152:152">
       <c r="EV204" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="205" spans="152:152">
       <c r="EV205" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="206" spans="152:152">
       <c r="EV206" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="207" spans="152:152">
       <c r="EV207" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="208" spans="152:152">
       <c r="EV208" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="209" spans="152:152">
       <c r="EV209" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="210" spans="152:152">
       <c r="EV210" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="211" spans="152:152">
       <c r="EV211" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="212" spans="152:152">
       <c r="EV212" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="213" spans="152:152">
       <c r="EV213" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="214" spans="152:152">
       <c r="EV214" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="215" spans="152:152">
       <c r="EV215" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="216" spans="152:152">
       <c r="EV216" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="217" spans="152:152">
       <c r="EV217" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="218" spans="152:152">
       <c r="EV218" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="219" spans="152:152">
       <c r="EV219" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="220" spans="152:152">
       <c r="EV220" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="221" spans="152:152">
       <c r="EV221" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="222" spans="152:152">
       <c r="EV222" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="223" spans="152:152">
       <c r="EV223" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="224" spans="152:152">
       <c r="EV224" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="225" spans="152:152">
       <c r="EV225" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="226" spans="152:152">
       <c r="EV226" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="227" spans="152:152">
       <c r="EV227" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
     </row>
     <row r="228" spans="152:152">
       <c r="EV228" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="229" spans="152:152">
       <c r="EV229" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="230" spans="152:152">
       <c r="EV230" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="231" spans="152:152">
       <c r="EV231" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
     </row>
     <row r="232" spans="152:152">
       <c r="EV232" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="233" spans="152:152">
       <c r="EV233" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="234" spans="152:152">
       <c r="EV234" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="235" spans="152:152">
       <c r="EV235" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="236" spans="152:152">
       <c r="EV236" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="237" spans="152:152">
       <c r="EV237" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="238" spans="152:152">
       <c r="EV238" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="239" spans="152:152">
       <c r="EV239" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="240" spans="152:152">
       <c r="EV240" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="241" spans="152:152">
       <c r="EV241" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="242" spans="152:152">
       <c r="EV242" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="243" spans="152:152">
       <c r="EV243" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
     <row r="244" spans="152:152">
       <c r="EV244" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="245" spans="152:152">
       <c r="EV245" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
     </row>
     <row r="246" spans="152:152">
       <c r="EV246" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="247" spans="152:152">
       <c r="EV247" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
     </row>
     <row r="248" spans="152:152">
       <c r="EV248" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="249" spans="152:152">
       <c r="EV249" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="250" spans="152:152">
       <c r="EV250" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="251" spans="152:152">
       <c r="EV251" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="252" spans="152:152">
       <c r="EV252" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="253" spans="152:152">
       <c r="EV253" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="254" spans="152:152">
       <c r="EV254" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="255" spans="152:152">
       <c r="EV255" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="256" spans="152:152">
       <c r="EV256" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="257" spans="152:152">
       <c r="EV257" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="258" spans="152:152">
       <c r="EV258" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="259" spans="152:152">
       <c r="EV259" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="260" spans="152:152">
       <c r="EV260" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="261" spans="152:152">
       <c r="EV261" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="262" spans="152:152">
       <c r="EV262" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="263" spans="152:152">
       <c r="EV263" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
     <row r="264" spans="152:152">
       <c r="EV264" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="265" spans="152:152">
       <c r="EV265" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="266" spans="152:152">
       <c r="EV266" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="267" spans="152:152">
       <c r="EV267" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
     <row r="268" spans="152:152">
       <c r="EV268" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="269" spans="152:152">
       <c r="EV269" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="270" spans="152:152">
       <c r="EV270" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="271" spans="152:152">
       <c r="EV271" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="272" spans="152:152">
       <c r="EV272" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="273" spans="152:152">
       <c r="EV273" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="274" spans="152:152">
       <c r="EV274" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="275" spans="152:152">
       <c r="EV275" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
     </row>
     <row r="276" spans="152:152">
       <c r="EV276" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="277" spans="152:152">
       <c r="EV277" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="278" spans="152:152">
       <c r="EV278" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="279" spans="152:152">
       <c r="EV279" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="280" spans="152:152">
       <c r="EV280" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="281" spans="152:152">
       <c r="EV281" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="282" spans="152:152">
       <c r="EV282" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="283" spans="152:152">
       <c r="EV283" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
     </row>
     <row r="284" spans="152:152">
       <c r="EV284" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="285" spans="152:152">
       <c r="EV285" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="286" spans="152:152">
       <c r="EV286" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="287" spans="152:152">
       <c r="EV287" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
     </row>
     <row r="288" spans="152:152">
       <c r="EV288" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="289" spans="152:152">
       <c r="EV289" t="s">
-        <v>983</v>
+        <v>985</v>
+      </c>
+    </row>
+    <row r="290" spans="152:152">
+      <c r="EV290" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="291" spans="152:152">
+      <c r="EV291" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="292" spans="152:152">
+      <c r="EV292" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="293" spans="152:152">
+      <c r="EV293" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="294" spans="152:152">
+      <c r="EV294" t="s">
+        <v>990</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000031/metadata_template_ERC000031.xlsx
+++ b/templates/ERC000031/metadata_template_ERC000031.xlsx
@@ -1670,7 +1670,7 @@
     <t>door material</t>
   </si>
   <si>
-    <t>(Optional) The material the door is composed of (Units: kg s−3)</t>
+    <t>(Optional) The material the door is composed of</t>
   </si>
   <si>
     <t>adjacent rooms</t>
@@ -1688,7 +1688,7 @@
     <t>ceiling signs of water/mold</t>
   </si>
   <si>
-    <t>(Optional) Signs of the presence of mold or mildew on the ceiling (Units: J/°C)</t>
+    <t>(Optional) Signs of the presence of mold or mildew on the ceiling</t>
   </si>
   <si>
     <t>window status</t>
@@ -1700,25 +1700,25 @@
     <t>door location</t>
   </si>
   <si>
-    <t>(Optional) The relative location of the door in the room (Units: year)</t>
+    <t>(Optional) The relative location of the door in the room</t>
   </si>
   <si>
     <t>window signs of water/mold</t>
   </si>
   <si>
-    <t>(Optional) Signs of the presence of mold or mildew on the window. (Units: year)</t>
+    <t>(Optional) Signs of the presence of mold or mildew on the window.</t>
   </si>
   <si>
     <t>window type</t>
   </si>
   <si>
-    <t>(Optional) The type of windows (Units: ppm)</t>
+    <t>(Optional) The type of windows</t>
   </si>
   <si>
     <t>window material</t>
   </si>
   <si>
-    <t>(Optional) The type of material used to finish a window (Units: g/m3)</t>
+    <t>(Optional) The type of material used to finish a window</t>
   </si>
   <si>
     <t>window horizontal position</t>
@@ -1730,7 +1730,7 @@
     <t>room condition</t>
   </si>
   <si>
-    <t>(Optional) The condition of the room at the time of sampling (Units: mm)</t>
+    <t>(Optional) The condition of the room at the time of sampling</t>
   </si>
   <si>
     <t>window area/size</t>
@@ -1742,7 +1742,7 @@
     <t>sampling floor</t>
   </si>
   <si>
-    <t>(Optional) The floor of the building, where the sampling room is located (Units: °C)</t>
+    <t>(Optional) The floor of the building, where the sampling room is located</t>
   </si>
   <si>
     <t>room count</t>
@@ -1754,19 +1754,19 @@
     <t>average daily occupancy</t>
   </si>
   <si>
-    <t>(Optional) Daily average occupancy of room. indicate the number of person(s) daily occupying the sampling room. (Units: °C)</t>
+    <t>(Optional) Daily average occupancy of room. indicate the number of person(s) daily occupying the sampling room.</t>
   </si>
   <si>
     <t>floor condition</t>
   </si>
   <si>
-    <t>(Optional) The physical condition of the floor at the time of sampling; photos or video preferred; use drawings to indicate location of damaged areas (Units: °C)</t>
+    <t>(Optional) The physical condition of the floor at the time of sampling; photos or video preferred; use drawings to indicate location of damaged areas</t>
   </si>
   <si>
     <t>door type, wood</t>
   </si>
   <si>
-    <t>(Optional) The type of wood door (Units: °C)</t>
+    <t>(Optional) The type of wood door</t>
   </si>
   <si>
     <t>door condition</t>
@@ -1796,13 +1796,13 @@
     <t>ceiling structure</t>
   </si>
   <si>
-    <t>(Optional) The construction format of the ceiling (Units: m)</t>
+    <t>(Optional) The construction format of the ceiling</t>
   </si>
   <si>
     <t>wall texture</t>
   </si>
   <si>
-    <t>(Optional) The feel, appearance, or consistency of a wall surface (Units: m)</t>
+    <t>(Optional) The feel, appearance, or consistency of a wall surface</t>
   </si>
   <si>
     <t>floor thermal mass</t>
@@ -1814,67 +1814,67 @@
     <t>room air exchange rate</t>
   </si>
   <si>
-    <t>(Optional) The rate at which outside air replaces indoor air in a given space (Units: year)</t>
+    <t>(Optional) The rate at which outside air replaces indoor air in a given space</t>
   </si>
   <si>
     <t>bathroom count</t>
   </si>
   <si>
-    <t>(Optional) The number of bathrooms in the building (Units: year)</t>
+    <t>(Optional) The number of bathrooms in the building</t>
   </si>
   <si>
     <t>shading device signs of water/mold</t>
   </si>
   <si>
-    <t>(Optional) Signs of the presence of mold or mildew on the shading device (Units: year)</t>
+    <t>(Optional) Signs of the presence of mold or mildew on the shading device</t>
   </si>
   <si>
     <t>window covering</t>
   </si>
   <si>
-    <t>(Optional) The type of window covering (Units: year)</t>
+    <t>(Optional) The type of window covering</t>
   </si>
   <si>
     <t>ceiling texture</t>
   </si>
   <si>
-    <t>(Optional) The feel, appearance, or consistency of a ceiling surface (Units: year)</t>
+    <t>(Optional) The feel, appearance, or consistency of a ceiling surface</t>
   </si>
   <si>
     <t>maximum occupancy</t>
   </si>
   <si>
-    <t>(Optional) The maximum amount of people allowed in the indoor environment (Units: year)</t>
+    <t>(Optional) The maximum amount of people allowed in the indoor environment</t>
   </si>
   <si>
     <t>gender of restroom</t>
   </si>
   <si>
-    <t>(Optional) The gender type of the restroom (Units: year)</t>
+    <t>(Optional) The gender type of the restroom</t>
   </si>
   <si>
     <t>ceiling condition</t>
   </si>
   <si>
-    <t>(Optional) The physical condition of the ceiling at the time of sampling; photos or video preferred; use drawings to indicate location of damaged areas (Units: year)</t>
+    <t>(Optional) The physical condition of the ceiling at the time of sampling; photos or video preferred; use drawings to indicate location of damaged areas</t>
   </si>
   <si>
     <t>floor structure</t>
   </si>
   <si>
-    <t>(Optional) Refers to the structural elements and subfloor upon which the finish flooring is installed (Units: year)</t>
+    <t>(Optional) Refers to the structural elements and subfloor upon which the finish flooring is installed</t>
   </si>
   <si>
     <t>rooms that share a wall with sampling room</t>
   </si>
   <si>
-    <t>(Optional) List of room(s) (room number, room name) sharing a wall with the sampling room (Units: year)</t>
+    <t>(Optional) List of room(s) (room number, room name) sharing a wall with the sampling room</t>
   </si>
   <si>
     <t>wall finish material</t>
   </si>
   <si>
-    <t>(Optional) The material utilized to finish the outer most layer of the wall (Units: year)</t>
+    <t>(Optional) The material utilized to finish the outer most layer of the wall</t>
   </si>
   <si>
     <t>room occupancy</t>
@@ -1886,25 +1886,25 @@
     <t>room location in building</t>
   </si>
   <si>
-    <t>(Optional) The position of the room within the building (Units: year)</t>
+    <t>(Optional) The position of the room within the building</t>
   </si>
   <si>
     <t>floor finish material</t>
   </si>
   <si>
-    <t>(Optional) The floor covering type; the finished surface that is walked on (Units: year)</t>
+    <t>(Optional) The floor covering type; the finished surface that is walked on</t>
   </si>
   <si>
     <t>room window count</t>
   </si>
   <si>
-    <t>(Optional) Number of windows in the room (Units: year)</t>
+    <t>(Optional) Number of windows in the room</t>
   </si>
   <si>
     <t>sampling room id or name</t>
   </si>
   <si>
-    <t>(Optional) Explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other). (Units: year)</t>
+    <t>(Optional) Explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other).</t>
   </si>
   <si>
     <t>height carpet fiber mat</t>
@@ -1922,25 +1922,25 @@
     <t>heating system delivery method</t>
   </si>
   <si>
-    <t>(Optional) The method by which the heat is delivered through the system (Units: m2)</t>
+    <t>(Optional) The method by which the heat is delivered through the system</t>
   </si>
   <si>
     <t>room sampling position</t>
   </si>
   <si>
-    <t>(Optional) The horizontal sampling position in the room relative to architectural elements (Units: m2)</t>
+    <t>(Optional) The horizontal sampling position in the room relative to architectural elements</t>
   </si>
   <si>
     <t>room moisture damage or mold history</t>
   </si>
   <si>
-    <t>(Optional) The history of moisture damage or mold in the past 12 months. number of events of moisture damage or mold observed (Units: °C)</t>
+    <t>(Optional) The history of moisture damage or mold in the past 12 months. number of events of moisture damage or mold observed</t>
   </si>
   <si>
     <t>door signs of water/mold</t>
   </si>
   <si>
-    <t>(Optional) Signs of the presence of mold or mildew on a door (Units: minute)</t>
+    <t>(Optional) Signs of the presence of mold or mildew on a door</t>
   </si>
   <si>
     <t>room net area</t>
@@ -1958,19 +1958,19 @@
     <t>rooms that share a door with sampling room</t>
   </si>
   <si>
-    <t>(Optional) List of room(s) (room number, room name) sharing a door with the sampling room (Units: year)</t>
+    <t>(Optional) List of room(s) (room number, room name) sharing a door with the sampling room</t>
   </si>
   <si>
     <t>orientations of exterior window</t>
   </si>
   <si>
-    <t>(Optional) The compass direction the exterior window of the room is facing (Units: year)</t>
+    <t>(Optional) The compass direction the exterior window of the room is facing</t>
   </si>
   <si>
     <t>wall location</t>
   </si>
   <si>
-    <t>(Optional) The relative location of the wall within the room (Units: °C)</t>
+    <t>(Optional) The relative location of the wall within the room</t>
   </si>
   <si>
     <t>room volume</t>
@@ -1982,91 +1982,91 @@
     <t>door type, composite</t>
   </si>
   <si>
-    <t>(Optional) The composite type of the door (Units: m2)</t>
+    <t>(Optional) The composite type of the door</t>
   </si>
   <si>
     <t>bedroom count</t>
   </si>
   <si>
-    <t>(Optional) The number of bedrooms in the building (Units: m2)</t>
+    <t>(Optional) The number of bedrooms in the building</t>
   </si>
   <si>
     <t>wall construction type</t>
   </si>
   <si>
-    <t>(Optional) The building class of the wall defined by the composition of the building elements and fire-resistance rating. (Units: m2)</t>
+    <t>(Optional) The building class of the wall defined by the composition of the building elements and fire-resistance rating.</t>
   </si>
   <si>
     <t>wall signs of water/mold</t>
   </si>
   <si>
-    <t>(Optional) Signs of the presence of mold or mildew on a wall (Units: m2)</t>
+    <t>(Optional) Signs of the presence of mold or mildew on a wall</t>
   </si>
   <si>
     <t>window condition</t>
   </si>
   <si>
-    <t>(Optional) The physical condition of the window at the time of sampling (Units: m2)</t>
+    <t>(Optional) The physical condition of the window at the time of sampling</t>
   </si>
   <si>
     <t>escalator count</t>
   </si>
   <si>
-    <t>(Optional) The number of escalators within the built structure (Units: m2)</t>
+    <t>(Optional) The number of escalators within the built structure</t>
   </si>
   <si>
     <t>cooling system identifier</t>
   </si>
   <si>
-    <t>(Optional) The cooling system identifier (Units: °C)</t>
+    <t>(Optional) The cooling system identifier</t>
   </si>
   <si>
     <t>quadrant position</t>
   </si>
   <si>
-    <t>(Optional) The quadrant position of the sampling room within the building (Units: °C)</t>
+    <t>(Optional) The quadrant position of the sampling room within the building</t>
   </si>
   <si>
     <t>number of pets</t>
   </si>
   <si>
-    <t>(Optional) The number of pets residing in the sampled space (Units: °C)</t>
+    <t>(Optional) The number of pets residing in the sampled space</t>
   </si>
   <si>
     <t>window vertical position</t>
   </si>
   <si>
-    <t>(Optional) The vertical position of the window on the wall (Units: °C)</t>
+    <t>(Optional) The vertical position of the window on the wall</t>
   </si>
   <si>
     <t>fireplace type</t>
   </si>
   <si>
-    <t>(Optional) A firebox with chimney (Units: °C)</t>
+    <t>(Optional) A firebox with chimney</t>
   </si>
   <si>
     <t>heating delivery locations</t>
   </si>
   <si>
-    <t>(Optional) The location of heat delivery within the room (Units: °C)</t>
+    <t>(Optional) The location of heat delivery within the room</t>
   </si>
   <si>
     <t>ceiling finish material</t>
   </si>
   <si>
-    <t>(Optional) The type of material used to finish a ceiling (Units: °C)</t>
+    <t>(Optional) The type of material used to finish a ceiling</t>
   </si>
   <si>
     <t>door type</t>
   </si>
   <si>
-    <t>(Optional) The type of door material (Units: °C)</t>
+    <t>(Optional) The type of door material</t>
   </si>
   <si>
     <t>number of houseplants</t>
   </si>
   <si>
-    <t>(Optional) The number of plant(s) in the sampling space (Units: °C)</t>
+    <t>(Optional) The number of plant(s) in the sampling space</t>
   </si>
   <si>
     <t>floor age</t>
@@ -2078,7 +2078,7 @@
     <t>rooms connected by a doorway</t>
   </si>
   <si>
-    <t>(Optional) List of rooms connected to the sampling room by a doorway (Units: year)</t>
+    <t>(Optional) List of rooms connected to the sampling room by a doorway</t>
   </si>
   <si>
     <t>specifications</t>
@@ -2096,7 +2096,7 @@
     <t>window open frequency</t>
   </si>
   <si>
-    <t>(Optional) The number of times windows are opened per week (Units: m)</t>
+    <t>(Optional) The number of times windows are opened per week</t>
   </si>
   <si>
     <t>room dimensions</t>
@@ -2138,7 +2138,7 @@
     <t>handidness</t>
   </si>
   <si>
-    <t>(Optional) The handidness of the individual sampled (Units: year)</t>
+    <t>(Optional) The handidness of the individual sampled</t>
   </si>
   <si>
     <t>Afghanistan</t>
@@ -3104,7 +3104,7 @@
     <t>number of residents</t>
   </si>
   <si>
-    <t>(Optional) The number of individuals currently occupying in the sampling location (Units: m)</t>
+    <t>(Optional) The number of individuals currently occupying in the sampling location</t>
   </si>
   <si>
     <t>average dew point</t>
@@ -3149,7 +3149,7 @@
     <t>seasonal use</t>
   </si>
   <si>
-    <t>(Optional) The seasons the space is occupied (Units: year)</t>
+    <t>(Optional) The seasons the space is occupied</t>
   </si>
   <si>
     <t>season</t>
@@ -3311,7 +3311,7 @@
     <t>sampling day weather</t>
   </si>
   <si>
-    <t>(Optional) The weather on the sampling day (Units: g/m3)</t>
+    <t>(Optional) The weather on the sampling day</t>
   </si>
   <si>
     <t>amount of light</t>
@@ -3323,7 +3323,7 @@
     <t>train line</t>
   </si>
   <si>
-    <t>(Optional) The subway line name (Units: °C)</t>
+    <t>(Optional) The subway line name</t>
   </si>
   <si>
     <t>outside relative humidity</t>
@@ -3359,43 +3359,43 @@
     <t>built structure type</t>
   </si>
   <si>
-    <t>(Optional) A physical structure that is a body or assemblage of bodies in space to form a system capable of supporting loads (Units: m)</t>
+    <t>(Optional) A physical structure that is a body or assemblage of bodies in space to form a system capable of supporting loads</t>
   </si>
   <si>
     <t>exterior door count</t>
   </si>
   <si>
-    <t>(Optional) The number of exterior doors in the built structure (Units: °C)</t>
+    <t>(Optional) The number of exterior doors in the built structure</t>
   </si>
   <si>
     <t>design, construction, and operation documents</t>
   </si>
   <si>
-    <t>(Optional) The building design, construction and operation documents (Units: year)</t>
+    <t>(Optional) The building design, construction and operation documents</t>
   </si>
   <si>
     <t>shading device condition</t>
   </si>
   <si>
-    <t>(Optional) The physical condition of the shading device at the time of sampling (Units: year)</t>
+    <t>(Optional) The physical condition of the shading device at the time of sampling</t>
   </si>
   <si>
     <t>occupancy documentation</t>
   </si>
   <si>
-    <t>(Optional) The type of documentation of occupancy (Units: year)</t>
+    <t>(Optional) The type of documentation of occupancy</t>
   </si>
   <si>
     <t>floor count</t>
   </si>
   <si>
-    <t>(Optional) The number of floors in the building, including basements and mechanical penthouse (Units: year)</t>
+    <t>(Optional) The number of floors in the building, including basements and mechanical penthouse</t>
   </si>
   <si>
     <t>shading device material</t>
   </si>
   <si>
-    <t>(Optional) The material the shading device is composed of (Units: year)</t>
+    <t>(Optional) The material the shading device is composed of</t>
   </si>
   <si>
     <t>built structure age</t>
@@ -3407,13 +3407,13 @@
     <t>hallway/corridor count</t>
   </si>
   <si>
-    <t>(Optional) The total count of hallways and corridors in the built structure (Units: g/m3)</t>
+    <t>(Optional) The total count of hallways and corridors in the built structure</t>
   </si>
   <si>
     <t>architectural structure</t>
   </si>
   <si>
-    <t>(Optional) An architectural structure is a human-made, free-standing, immobile outdoor construction (Units: m2)</t>
+    <t>(Optional) An architectural structure is a human-made, free-standing, immobile outdoor construction</t>
   </si>
   <si>
     <t>shading device type</t>
@@ -3425,13 +3425,13 @@
     <t>shading device location</t>
   </si>
   <si>
-    <t>(Optional) The location of the shading device in relation to the built structure (Units: °C)</t>
+    <t>(Optional) The location of the shading device in relation to the built structure</t>
   </si>
   <si>
     <t>drawings</t>
   </si>
   <si>
-    <t>(Optional) The buildings architectural drawings; if design is chosen, indicate phase-conceptual, schematic, design development, and construction documents (Units: year)</t>
+    <t>(Optional) The buildings architectural drawings; if design is chosen, indicate phase-conceptual, schematic, design development, and construction documents</t>
   </si>
   <si>
     <t>address</t>

--- a/templates/ERC000031/metadata_template_ERC000031.xlsx
+++ b/templates/ERC000031/metadata_template_ERC000031.xlsx
@@ -24,7 +24,7 @@
     <definedName name="frequencyofcleaning">'cv_sample'!$FK$1:$FK$5</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$EV$1:$EV$294</definedName>
     <definedName name="heatingandcoolingsystemtype">'cv_sample'!$AT$1:$AT$5</definedName>
-    <definedName name="indoorspace">'cv_sample'!$AR$1:$AR$8</definedName>
+    <definedName name="indoorspace">'cv_sample'!$AR$1:$AR$12</definedName>
     <definedName name="indoorsurface">'cv_sample'!$AQ$1:$AQ$8</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
@@ -34,12 +34,13 @@
     <definedName name="observedbioticrelationship">'cv_sample'!$I$1:$I$5</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$K$1:$K$7</definedName>
+    <definedName name="roomtype">'cv_sample'!$BL$1:$BL$27</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$X$1:$X$3</definedName>
     <definedName name="spacetypicalstate">'cv_sample'!$AY$1:$AY$2</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
     <definedName name="substructuretype">'cv_sample'!$AU$1:$AU$3</definedName>
     <definedName name="surfaceaircontaminant">'cv_sample'!$AP$1:$AP$8</definedName>
-    <definedName name="surfacematerial">'cv_sample'!$AO$1:$AO$15</definedName>
+    <definedName name="surfacematerial">'cv_sample'!$AO$1:$AO$16</definedName>
     <definedName name="trophiclevel">'cv_sample'!$H$1:$H$30</definedName>
     <definedName name="ventilationtype">'cv_sample'!$BC$1:$BC$3</definedName>
   </definedNames>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="1163">
   <si>
     <t>alias</t>
   </si>
@@ -1223,10 +1224,13 @@
     <t>carpet</t>
   </si>
   <si>
+    <t>concrete</t>
+  </si>
+  <si>
     <t>cinder blocks</t>
   </si>
   <si>
-    <t>concrete</t>
+    <t>epoxy resin</t>
   </si>
   <si>
     <t>glass</t>
@@ -1334,6 +1338,9 @@
     <t>bedroom</t>
   </si>
   <si>
+    <t>cleanroom</t>
+  </si>
+  <si>
     <t>elevator</t>
   </si>
   <si>
@@ -1352,6 +1359,15 @@
     <t>office</t>
   </si>
   <si>
+    <t xml:space="preserve"> space analog</t>
+  </si>
+  <si>
+    <t>space habitat</t>
+  </si>
+  <si>
+    <t>space station</t>
+  </si>
+  <si>
     <t>indoor space</t>
   </si>
   <si>
@@ -1613,6 +1629,78 @@
     <t>(Optional) Distance between doors (meters) in the hallway between the sampling room and adjacent rooms</t>
   </si>
   <si>
+    <t>attic</t>
+  </si>
+  <si>
+    <t>auditorium</t>
+  </si>
+  <si>
+    <t>bathoom</t>
+  </si>
+  <si>
+    <t>cafe</t>
+  </si>
+  <si>
+    <t>cleanroom ISO 1</t>
+  </si>
+  <si>
+    <t>cleanroom ISO 5</t>
+  </si>
+  <si>
+    <t>cleanroom ISO 7</t>
+  </si>
+  <si>
+    <t>cleanroom ISO 8</t>
+  </si>
+  <si>
+    <t>closet</t>
+  </si>
+  <si>
+    <t>conference room</t>
+  </si>
+  <si>
+    <t>data center</t>
+  </si>
+  <si>
+    <t>gymnasium</t>
+  </si>
+  <si>
+    <t>laboratory_dry</t>
+  </si>
+  <si>
+    <t>laboratory_wet</t>
+  </si>
+  <si>
+    <t>lobby</t>
+  </si>
+  <si>
+    <t>lockers</t>
+  </si>
+  <si>
+    <t>mail room</t>
+  </si>
+  <si>
+    <t>mechanical or electrical room</t>
+  </si>
+  <si>
+    <t>natatorium</t>
+  </si>
+  <si>
+    <t>open office</t>
+  </si>
+  <si>
+    <t>private office</t>
+  </si>
+  <si>
+    <t>restroom</t>
+  </si>
+  <si>
+    <t>stairwell</t>
+  </si>
+  <si>
+    <t>warehouse</t>
+  </si>
+  <si>
     <t>room type</t>
   </si>
   <si>
@@ -2126,7 +2214,7 @@
     <t>organism count</t>
   </si>
   <si>
-    <t>(Mandatory) Total cell count of any organism (or group of organisms) per gram, volume or area of sample, should include name of organism followed by count. the method that was used for the enumeration (e.g. qpcr, atp, mpn, etc.) should also be provided. (example: total prokaryotes; 3.5e7 cells per ml; qpcr)</t>
+    <t>(Optional) Total cell count of any organism (or group of organisms) per gram, volume or area of sample, should include name of organism followed by count. the method that was used for the enumeration (e.g. qpcr, atp, mpn, etc.) should also be provided. (example: total prokaryotes; 3.5e7 cells per ml; qpcr)</t>
   </si>
   <si>
     <t>mechanical structure</t>
@@ -3062,7 +3150,7 @@
     <t>air temperature</t>
   </si>
   <si>
-    <t>(Mandatory) Temperature of the air at time of sampling (Units: ºC)</t>
+    <t>(Recommended) Temperature of the air at time of sampling (Units: ºC)</t>
   </si>
   <si>
     <t>surface temperature</t>
@@ -3137,7 +3225,7 @@
     <t>carbon dioxide</t>
   </si>
   <si>
-    <t>(Mandatory) Carbon dioxide (gas) amount or concentration at the time of sampling (Units: µmol/L)</t>
+    <t>(Recommended) Carbon dioxide (gas) amount or concentration at the time of sampling (Units: µmol/L)</t>
   </si>
   <si>
     <t>source material identifiers</t>
@@ -5101,544 +5189,544 @@
         <v>387</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>521</v>
+        <v>550</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>523</v>
+        <v>552</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>527</v>
+        <v>556</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>529</v>
+        <v>558</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>531</v>
+        <v>560</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>533</v>
+        <v>562</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>535</v>
+        <v>564</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>537</v>
+        <v>566</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>539</v>
+        <v>568</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>541</v>
+        <v>570</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>545</v>
+        <v>574</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>547</v>
+        <v>576</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>549</v>
+        <v>578</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>551</v>
+        <v>580</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>553</v>
+        <v>582</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>555</v>
+        <v>584</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>557</v>
+        <v>586</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>559</v>
+        <v>588</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>561</v>
+        <v>590</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>563</v>
+        <v>592</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>567</v>
+        <v>596</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>569</v>
+        <v>598</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>571</v>
+        <v>600</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>573</v>
+        <v>602</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>575</v>
+        <v>604</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>577</v>
+        <v>606</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>579</v>
+        <v>608</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>581</v>
+        <v>610</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>583</v>
+        <v>612</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>585</v>
+        <v>614</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>589</v>
+        <v>618</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>593</v>
+        <v>622</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>595</v>
+        <v>624</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>599</v>
+        <v>628</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>601</v>
+        <v>630</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>603</v>
+        <v>632</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>605</v>
+        <v>634</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>607</v>
+        <v>636</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>609</v>
+        <v>638</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>611</v>
+        <v>640</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>615</v>
+        <v>644</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>617</v>
+        <v>646</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>619</v>
+        <v>648</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>621</v>
+        <v>650</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>623</v>
+        <v>652</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>625</v>
+        <v>654</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>627</v>
+        <v>656</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>629</v>
+        <v>658</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>635</v>
+        <v>664</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>637</v>
+        <v>666</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>639</v>
+        <v>668</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>641</v>
+        <v>670</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>643</v>
+        <v>672</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>645</v>
+        <v>674</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>647</v>
+        <v>676</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>649</v>
+        <v>678</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>651</v>
+        <v>680</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>653</v>
+        <v>682</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>655</v>
+        <v>684</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>657</v>
+        <v>686</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>659</v>
+        <v>688</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>661</v>
+        <v>690</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>663</v>
+        <v>692</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>665</v>
+        <v>694</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>667</v>
+        <v>696</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>669</v>
+        <v>698</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>671</v>
+        <v>700</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>673</v>
+        <v>702</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>675</v>
+        <v>704</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>679</v>
+        <v>708</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>681</v>
+        <v>710</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>683</v>
+        <v>712</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>685</v>
+        <v>714</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>687</v>
+        <v>716</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>689</v>
+        <v>718</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>691</v>
+        <v>720</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>693</v>
+        <v>722</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>991</v>
+        <v>1020</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>993</v>
+        <v>1022</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>995</v>
+        <v>1024</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>997</v>
+        <v>1026</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>999</v>
+        <v>1028</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>1001</v>
+        <v>1030</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>1003</v>
+        <v>1032</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>1005</v>
+        <v>1034</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1007</v>
+        <v>1036</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1009</v>
+        <v>1038</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1011</v>
+        <v>1040</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1013</v>
+        <v>1042</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1015</v>
+        <v>1044</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1017</v>
+        <v>1046</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1019</v>
+        <v>1048</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1026</v>
+        <v>1055</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1028</v>
+        <v>1057</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1030</v>
+        <v>1059</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1032</v>
+        <v>1061</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1034</v>
+        <v>1063</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1036</v>
+        <v>1065</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1038</v>
+        <v>1067</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1040</v>
+        <v>1069</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1042</v>
+        <v>1071</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1044</v>
+        <v>1073</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1046</v>
+        <v>1075</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1048</v>
+        <v>1077</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1050</v>
+        <v>1079</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1052</v>
+        <v>1081</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1054</v>
+        <v>1083</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1056</v>
+        <v>1085</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1058</v>
+        <v>1087</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1060</v>
+        <v>1089</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1062</v>
+        <v>1091</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1064</v>
+        <v>1093</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1066</v>
+        <v>1095</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1068</v>
+        <v>1097</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1070</v>
+        <v>1099</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1072</v>
+        <v>1101</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1074</v>
+        <v>1103</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1076</v>
+        <v>1105</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1078</v>
+        <v>1107</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1080</v>
+        <v>1109</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1082</v>
+        <v>1111</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1084</v>
+        <v>1113</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1086</v>
+        <v>1115</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1088</v>
+        <v>1117</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1090</v>
+        <v>1119</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1092</v>
+        <v>1121</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1094</v>
+        <v>1123</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1096</v>
+        <v>1125</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1098</v>
+        <v>1127</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1100</v>
+        <v>1129</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1102</v>
+        <v>1131</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1104</v>
+        <v>1133</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1106</v>
+        <v>1135</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1108</v>
+        <v>1137</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1110</v>
+        <v>1139</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1112</v>
+        <v>1141</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1114</v>
+        <v>1143</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1116</v>
+        <v>1145</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1118</v>
+        <v>1147</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1120</v>
+        <v>1149</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1122</v>
+        <v>1151</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1124</v>
+        <v>1153</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1126</v>
+        <v>1155</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1128</v>
+        <v>1157</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1130</v>
+        <v>1159</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1132</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="2" spans="1:220" ht="150" customHeight="1">
@@ -5763,548 +5851,548 @@
         <v>388</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>524</v>
+        <v>553</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>528</v>
+        <v>557</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>530</v>
+        <v>559</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>532</v>
+        <v>561</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>534</v>
+        <v>563</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>536</v>
+        <v>565</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>538</v>
+        <v>567</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>540</v>
+        <v>569</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>542</v>
+        <v>571</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>544</v>
+        <v>573</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>546</v>
+        <v>575</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>548</v>
+        <v>577</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>550</v>
+        <v>579</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>552</v>
+        <v>581</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>554</v>
+        <v>583</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>556</v>
+        <v>585</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>558</v>
+        <v>587</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>560</v>
+        <v>589</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>562</v>
+        <v>591</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>564</v>
+        <v>593</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>566</v>
+        <v>595</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>568</v>
+        <v>597</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>570</v>
+        <v>599</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>572</v>
+        <v>601</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>574</v>
+        <v>603</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>578</v>
+        <v>607</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>580</v>
+        <v>609</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>582</v>
+        <v>611</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>584</v>
+        <v>613</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>586</v>
+        <v>615</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>590</v>
+        <v>619</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>592</v>
+        <v>621</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>594</v>
+        <v>623</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>600</v>
+        <v>629</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>602</v>
+        <v>631</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>604</v>
+        <v>633</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>606</v>
+        <v>635</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>608</v>
+        <v>637</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>610</v>
+        <v>639</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>612</v>
+        <v>641</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>614</v>
+        <v>643</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>616</v>
+        <v>645</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>618</v>
+        <v>647</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>620</v>
+        <v>649</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>622</v>
+        <v>651</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>624</v>
+        <v>653</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>626</v>
+        <v>655</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>630</v>
+        <v>659</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>632</v>
+        <v>661</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>634</v>
+        <v>663</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>636</v>
+        <v>665</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>638</v>
+        <v>667</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>640</v>
+        <v>669</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>642</v>
+        <v>671</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>644</v>
+        <v>673</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>646</v>
+        <v>675</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>648</v>
+        <v>677</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>650</v>
+        <v>679</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>652</v>
+        <v>681</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>654</v>
+        <v>683</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>656</v>
+        <v>685</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>658</v>
+        <v>687</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>660</v>
+        <v>689</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>662</v>
+        <v>691</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>664</v>
+        <v>693</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>666</v>
+        <v>695</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>668</v>
+        <v>697</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>670</v>
+        <v>699</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>672</v>
+        <v>701</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>674</v>
+        <v>703</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>676</v>
+        <v>705</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>678</v>
+        <v>707</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>680</v>
+        <v>709</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>682</v>
+        <v>711</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>684</v>
+        <v>713</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>686</v>
+        <v>715</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>688</v>
+        <v>717</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>690</v>
+        <v>719</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>692</v>
+        <v>721</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>694</v>
+        <v>723</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>696</v>
+        <v>725</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>992</v>
+        <v>1021</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>994</v>
+        <v>1023</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>996</v>
+        <v>1025</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>998</v>
+        <v>1027</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>1000</v>
+        <v>1029</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>1002</v>
+        <v>1031</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>1004</v>
+        <v>1033</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>1006</v>
+        <v>1035</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1008</v>
+        <v>1037</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1010</v>
+        <v>1039</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1012</v>
+        <v>1041</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1014</v>
+        <v>1043</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1016</v>
+        <v>1045</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1018</v>
+        <v>1047</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1020</v>
+        <v>1049</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1027</v>
+        <v>1056</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1029</v>
+        <v>1058</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1031</v>
+        <v>1060</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1033</v>
+        <v>1062</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1035</v>
+        <v>1064</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1037</v>
+        <v>1066</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1039</v>
+        <v>1068</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1041</v>
+        <v>1070</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1043</v>
+        <v>1072</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1045</v>
+        <v>1074</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1047</v>
+        <v>1076</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1049</v>
+        <v>1078</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1051</v>
+        <v>1080</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1053</v>
+        <v>1082</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1055</v>
+        <v>1084</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1057</v>
+        <v>1086</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1059</v>
+        <v>1088</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1061</v>
+        <v>1090</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1063</v>
+        <v>1092</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1065</v>
+        <v>1094</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1067</v>
+        <v>1096</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1069</v>
+        <v>1098</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1071</v>
+        <v>1100</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1073</v>
+        <v>1102</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1075</v>
+        <v>1104</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1077</v>
+        <v>1106</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1079</v>
+        <v>1108</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1081</v>
+        <v>1110</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1083</v>
+        <v>1112</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1085</v>
+        <v>1114</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1087</v>
+        <v>1116</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1089</v>
+        <v>1118</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1091</v>
+        <v>1120</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1093</v>
+        <v>1122</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1095</v>
+        <v>1124</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1097</v>
+        <v>1126</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1099</v>
+        <v>1128</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1101</v>
+        <v>1130</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1103</v>
+        <v>1132</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1105</v>
+        <v>1134</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1107</v>
+        <v>1136</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1109</v>
+        <v>1138</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1111</v>
+        <v>1140</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1113</v>
+        <v>1142</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1115</v>
+        <v>1144</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1117</v>
+        <v>1146</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1119</v>
+        <v>1148</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1121</v>
+        <v>1150</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1123</v>
+        <v>1152</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1125</v>
+        <v>1154</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1127</v>
+        <v>1156</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1129</v>
+        <v>1158</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1131</v>
+        <v>1160</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1133</v>
+        <v>1162</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="18">
+  <dataValidations count="19">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
@@ -6353,6 +6441,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC3:BC101">
       <formula1>ventilationtype</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL3:BL101">
+      <formula1>roomtype</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EV3:EV101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
@@ -6386,43 +6477,46 @@
         <v>389</v>
       </c>
       <c r="AP1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AR1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AS1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AT1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AU1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AV1" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AW1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AX1" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="AY1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="BC1" t="s">
-        <v>500</v>
+        <v>505</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>526</v>
       </c>
       <c r="EV1" t="s">
-        <v>697</v>
+        <v>726</v>
       </c>
       <c r="FK1" t="s">
-        <v>1021</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="2" spans="8:167">
@@ -6442,43 +6536,46 @@
         <v>390</v>
       </c>
       <c r="AP2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AQ2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AS2" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AT2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="AU2" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AV2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AW2" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AX2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AY2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="BC2" t="s">
-        <v>501</v>
+        <v>506</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>527</v>
       </c>
       <c r="EV2" t="s">
-        <v>698</v>
+        <v>727</v>
       </c>
       <c r="FK2" t="s">
-        <v>1022</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="3" spans="8:167">
@@ -6498,40 +6595,43 @@
         <v>391</v>
       </c>
       <c r="AP3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AQ3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AR3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AS3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AT3" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AU3" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AV3" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AW3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AX3" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="BC3" t="s">
-        <v>502</v>
+        <v>507</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>528</v>
       </c>
       <c r="EV3" t="s">
-        <v>699</v>
+        <v>728</v>
       </c>
       <c r="FK3" t="s">
-        <v>1023</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="4" spans="8:167">
@@ -6548,31 +6648,34 @@
         <v>392</v>
       </c>
       <c r="AP4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AQ4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AR4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AS4" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AT4" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AW4" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AX4" t="s">
-        <v>471</v>
+        <v>476</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>529</v>
       </c>
       <c r="EV4" t="s">
-        <v>700</v>
+        <v>729</v>
       </c>
       <c r="FK4" t="s">
-        <v>1024</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="5" spans="8:167">
@@ -6589,28 +6692,31 @@
         <v>393</v>
       </c>
       <c r="AP5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AQ5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AS5" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AT5" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AX5" t="s">
-        <v>472</v>
+        <v>477</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>530</v>
       </c>
       <c r="EV5" t="s">
-        <v>701</v>
+        <v>730</v>
       </c>
       <c r="FK5" t="s">
-        <v>1025</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="6" spans="8:167">
@@ -6624,22 +6730,25 @@
         <v>394</v>
       </c>
       <c r="AP6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AQ6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AR6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AS6" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AX6" t="s">
-        <v>473</v>
+        <v>478</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>531</v>
       </c>
       <c r="EV6" t="s">
-        <v>702</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7" spans="8:167">
@@ -6653,22 +6762,25 @@
         <v>395</v>
       </c>
       <c r="AP7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AQ7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AR7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AS7" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AX7" t="s">
-        <v>474</v>
+        <v>479</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>532</v>
       </c>
       <c r="EV7" t="s">
-        <v>703</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8" spans="8:167">
@@ -6679,19 +6791,22 @@
         <v>396</v>
       </c>
       <c r="AP8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AR8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AX8" t="s">
-        <v>475</v>
+        <v>480</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>533</v>
       </c>
       <c r="EV8" t="s">
-        <v>704</v>
+        <v>733</v>
       </c>
     </row>
     <row r="9" spans="8:167">
@@ -6701,11 +6816,17 @@
       <c r="AO9" t="s">
         <v>397</v>
       </c>
+      <c r="AR9" t="s">
+        <v>435</v>
+      </c>
       <c r="AX9" t="s">
-        <v>476</v>
+        <v>481</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>534</v>
       </c>
       <c r="EV9" t="s">
-        <v>705</v>
+        <v>734</v>
       </c>
     </row>
     <row r="10" spans="8:167">
@@ -6715,11 +6836,17 @@
       <c r="AO10" t="s">
         <v>398</v>
       </c>
+      <c r="AR10" t="s">
+        <v>436</v>
+      </c>
       <c r="AX10" t="s">
-        <v>477</v>
+        <v>482</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>535</v>
       </c>
       <c r="EV10" t="s">
-        <v>706</v>
+        <v>735</v>
       </c>
     </row>
     <row r="11" spans="8:167">
@@ -6729,11 +6856,17 @@
       <c r="AO11" t="s">
         <v>399</v>
       </c>
+      <c r="AR11" t="s">
+        <v>437</v>
+      </c>
       <c r="AX11" t="s">
-        <v>478</v>
+        <v>483</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>536</v>
       </c>
       <c r="EV11" t="s">
-        <v>707</v>
+        <v>736</v>
       </c>
     </row>
     <row r="12" spans="8:167">
@@ -6743,11 +6876,17 @@
       <c r="AO12" t="s">
         <v>400</v>
       </c>
+      <c r="AR12" t="s">
+        <v>438</v>
+      </c>
       <c r="AX12" t="s">
-        <v>433</v>
+        <v>435</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>430</v>
       </c>
       <c r="EV12" t="s">
-        <v>708</v>
+        <v>737</v>
       </c>
     </row>
     <row r="13" spans="8:167">
@@ -6758,10 +6897,13 @@
         <v>401</v>
       </c>
       <c r="AX13" t="s">
-        <v>479</v>
+        <v>484</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>537</v>
       </c>
       <c r="EV13" t="s">
-        <v>709</v>
+        <v>738</v>
       </c>
     </row>
     <row r="14" spans="8:167">
@@ -6772,10 +6914,13 @@
         <v>402</v>
       </c>
       <c r="AX14" t="s">
-        <v>480</v>
+        <v>485</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>432</v>
       </c>
       <c r="EV14" t="s">
-        <v>710</v>
+        <v>739</v>
       </c>
     </row>
     <row r="15" spans="8:167">
@@ -6786,21 +6931,30 @@
         <v>403</v>
       </c>
       <c r="AX15" t="s">
-        <v>481</v>
+        <v>486</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>433</v>
       </c>
       <c r="EV15" t="s">
-        <v>711</v>
+        <v>740</v>
       </c>
     </row>
     <row r="16" spans="8:167">
       <c r="H16" t="s">
         <v>293</v>
       </c>
+      <c r="AO16" t="s">
+        <v>404</v>
+      </c>
       <c r="AX16" t="s">
-        <v>482</v>
+        <v>487</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>538</v>
       </c>
       <c r="EV16" t="s">
-        <v>712</v>
+        <v>741</v>
       </c>
     </row>
     <row r="17" spans="8:152">
@@ -6808,10 +6962,13 @@
         <v>294</v>
       </c>
       <c r="AX17" t="s">
-        <v>483</v>
+        <v>488</v>
+      </c>
+      <c r="BL17" t="s">
+        <v>539</v>
       </c>
       <c r="EV17" t="s">
-        <v>713</v>
+        <v>742</v>
       </c>
     </row>
     <row r="18" spans="8:152">
@@ -6819,10 +6976,13 @@
         <v>295</v>
       </c>
       <c r="AX18" t="s">
-        <v>484</v>
+        <v>489</v>
+      </c>
+      <c r="BL18" t="s">
+        <v>540</v>
       </c>
       <c r="EV18" t="s">
-        <v>714</v>
+        <v>743</v>
       </c>
     </row>
     <row r="19" spans="8:152">
@@ -6830,10 +6990,13 @@
         <v>296</v>
       </c>
       <c r="AX19" t="s">
-        <v>485</v>
+        <v>490</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>541</v>
       </c>
       <c r="EV19" t="s">
-        <v>715</v>
+        <v>744</v>
       </c>
     </row>
     <row r="20" spans="8:152">
@@ -6841,10 +7004,13 @@
         <v>297</v>
       </c>
       <c r="AX20" t="s">
-        <v>486</v>
+        <v>491</v>
+      </c>
+      <c r="BL20" t="s">
+        <v>542</v>
       </c>
       <c r="EV20" t="s">
-        <v>716</v>
+        <v>745</v>
       </c>
     </row>
     <row r="21" spans="8:152">
@@ -6852,58 +7018,79 @@
         <v>298</v>
       </c>
       <c r="AX21" t="s">
-        <v>487</v>
+        <v>492</v>
+      </c>
+      <c r="BL21" t="s">
+        <v>543</v>
       </c>
       <c r="EV21" t="s">
-        <v>717</v>
+        <v>746</v>
       </c>
     </row>
     <row r="22" spans="8:152">
       <c r="H22" t="s">
         <v>299</v>
       </c>
+      <c r="BL22" t="s">
+        <v>544</v>
+      </c>
       <c r="EV22" t="s">
-        <v>718</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="8:152">
       <c r="H23" t="s">
         <v>300</v>
       </c>
+      <c r="BL23" t="s">
+        <v>545</v>
+      </c>
       <c r="EV23" t="s">
-        <v>719</v>
+        <v>748</v>
       </c>
     </row>
     <row r="24" spans="8:152">
       <c r="H24" t="s">
         <v>301</v>
       </c>
+      <c r="BL24" t="s">
+        <v>546</v>
+      </c>
       <c r="EV24" t="s">
-        <v>720</v>
+        <v>749</v>
       </c>
     </row>
     <row r="25" spans="8:152">
       <c r="H25" t="s">
         <v>302</v>
       </c>
+      <c r="BL25" t="s">
+        <v>547</v>
+      </c>
       <c r="EV25" t="s">
-        <v>721</v>
+        <v>750</v>
       </c>
     </row>
     <row r="26" spans="8:152">
       <c r="H26" t="s">
         <v>303</v>
       </c>
+      <c r="BL26" t="s">
+        <v>548</v>
+      </c>
       <c r="EV26" t="s">
-        <v>722</v>
+        <v>751</v>
       </c>
     </row>
     <row r="27" spans="8:152">
       <c r="H27" t="s">
         <v>304</v>
       </c>
+      <c r="BL27" t="s">
+        <v>549</v>
+      </c>
       <c r="EV27" t="s">
-        <v>723</v>
+        <v>752</v>
       </c>
     </row>
     <row r="28" spans="8:152">
@@ -6911,7 +7098,7 @@
         <v>305</v>
       </c>
       <c r="EV28" t="s">
-        <v>724</v>
+        <v>753</v>
       </c>
     </row>
     <row r="29" spans="8:152">
@@ -6919,7 +7106,7 @@
         <v>306</v>
       </c>
       <c r="EV29" t="s">
-        <v>725</v>
+        <v>754</v>
       </c>
     </row>
     <row r="30" spans="8:152">
@@ -6927,1327 +7114,1327 @@
         <v>307</v>
       </c>
       <c r="EV30" t="s">
-        <v>726</v>
+        <v>755</v>
       </c>
     </row>
     <row r="31" spans="8:152">
       <c r="EV31" t="s">
-        <v>727</v>
+        <v>756</v>
       </c>
     </row>
     <row r="32" spans="8:152">
       <c r="EV32" t="s">
-        <v>728</v>
+        <v>757</v>
       </c>
     </row>
     <row r="33" spans="152:152">
       <c r="EV33" t="s">
-        <v>729</v>
+        <v>758</v>
       </c>
     </row>
     <row r="34" spans="152:152">
       <c r="EV34" t="s">
-        <v>730</v>
+        <v>759</v>
       </c>
     </row>
     <row r="35" spans="152:152">
       <c r="EV35" t="s">
-        <v>731</v>
+        <v>760</v>
       </c>
     </row>
     <row r="36" spans="152:152">
       <c r="EV36" t="s">
-        <v>732</v>
+        <v>761</v>
       </c>
     </row>
     <row r="37" spans="152:152">
       <c r="EV37" t="s">
-        <v>733</v>
+        <v>762</v>
       </c>
     </row>
     <row r="38" spans="152:152">
       <c r="EV38" t="s">
-        <v>734</v>
+        <v>763</v>
       </c>
     </row>
     <row r="39" spans="152:152">
       <c r="EV39" t="s">
-        <v>735</v>
+        <v>764</v>
       </c>
     </row>
     <row r="40" spans="152:152">
       <c r="EV40" t="s">
-        <v>736</v>
+        <v>765</v>
       </c>
     </row>
     <row r="41" spans="152:152">
       <c r="EV41" t="s">
-        <v>737</v>
+        <v>766</v>
       </c>
     </row>
     <row r="42" spans="152:152">
       <c r="EV42" t="s">
-        <v>738</v>
+        <v>767</v>
       </c>
     </row>
     <row r="43" spans="152:152">
       <c r="EV43" t="s">
-        <v>739</v>
+        <v>768</v>
       </c>
     </row>
     <row r="44" spans="152:152">
       <c r="EV44" t="s">
-        <v>740</v>
+        <v>769</v>
       </c>
     </row>
     <row r="45" spans="152:152">
       <c r="EV45" t="s">
-        <v>741</v>
+        <v>770</v>
       </c>
     </row>
     <row r="46" spans="152:152">
       <c r="EV46" t="s">
-        <v>742</v>
+        <v>771</v>
       </c>
     </row>
     <row r="47" spans="152:152">
       <c r="EV47" t="s">
-        <v>743</v>
+        <v>772</v>
       </c>
     </row>
     <row r="48" spans="152:152">
       <c r="EV48" t="s">
-        <v>744</v>
+        <v>773</v>
       </c>
     </row>
     <row r="49" spans="152:152">
       <c r="EV49" t="s">
-        <v>745</v>
+        <v>774</v>
       </c>
     </row>
     <row r="50" spans="152:152">
       <c r="EV50" t="s">
-        <v>746</v>
+        <v>775</v>
       </c>
     </row>
     <row r="51" spans="152:152">
       <c r="EV51" t="s">
-        <v>747</v>
+        <v>776</v>
       </c>
     </row>
     <row r="52" spans="152:152">
       <c r="EV52" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
     </row>
     <row r="53" spans="152:152">
       <c r="EV53" t="s">
-        <v>749</v>
+        <v>778</v>
       </c>
     </row>
     <row r="54" spans="152:152">
       <c r="EV54" t="s">
-        <v>750</v>
+        <v>779</v>
       </c>
     </row>
     <row r="55" spans="152:152">
       <c r="EV55" t="s">
-        <v>751</v>
+        <v>780</v>
       </c>
     </row>
     <row r="56" spans="152:152">
       <c r="EV56" t="s">
-        <v>752</v>
+        <v>781</v>
       </c>
     </row>
     <row r="57" spans="152:152">
       <c r="EV57" t="s">
-        <v>753</v>
+        <v>782</v>
       </c>
     </row>
     <row r="58" spans="152:152">
       <c r="EV58" t="s">
-        <v>754</v>
+        <v>783</v>
       </c>
     </row>
     <row r="59" spans="152:152">
       <c r="EV59" t="s">
-        <v>755</v>
+        <v>784</v>
       </c>
     </row>
     <row r="60" spans="152:152">
       <c r="EV60" t="s">
-        <v>756</v>
+        <v>785</v>
       </c>
     </row>
     <row r="61" spans="152:152">
       <c r="EV61" t="s">
-        <v>757</v>
+        <v>786</v>
       </c>
     </row>
     <row r="62" spans="152:152">
       <c r="EV62" t="s">
-        <v>758</v>
+        <v>787</v>
       </c>
     </row>
     <row r="63" spans="152:152">
       <c r="EV63" t="s">
-        <v>759</v>
+        <v>788</v>
       </c>
     </row>
     <row r="64" spans="152:152">
       <c r="EV64" t="s">
-        <v>760</v>
+        <v>789</v>
       </c>
     </row>
     <row r="65" spans="152:152">
       <c r="EV65" t="s">
-        <v>761</v>
+        <v>790</v>
       </c>
     </row>
     <row r="66" spans="152:152">
       <c r="EV66" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
     </row>
     <row r="67" spans="152:152">
       <c r="EV67" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
     </row>
     <row r="68" spans="152:152">
       <c r="EV68" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
     </row>
     <row r="69" spans="152:152">
       <c r="EV69" t="s">
-        <v>765</v>
+        <v>794</v>
       </c>
     </row>
     <row r="70" spans="152:152">
       <c r="EV70" t="s">
-        <v>766</v>
+        <v>795</v>
       </c>
     </row>
     <row r="71" spans="152:152">
       <c r="EV71" t="s">
-        <v>767</v>
+        <v>796</v>
       </c>
     </row>
     <row r="72" spans="152:152">
       <c r="EV72" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
     </row>
     <row r="73" spans="152:152">
       <c r="EV73" t="s">
-        <v>769</v>
+        <v>798</v>
       </c>
     </row>
     <row r="74" spans="152:152">
       <c r="EV74" t="s">
-        <v>770</v>
+        <v>799</v>
       </c>
     </row>
     <row r="75" spans="152:152">
       <c r="EV75" t="s">
-        <v>771</v>
+        <v>800</v>
       </c>
     </row>
     <row r="76" spans="152:152">
       <c r="EV76" t="s">
-        <v>772</v>
+        <v>801</v>
       </c>
     </row>
     <row r="77" spans="152:152">
       <c r="EV77" t="s">
-        <v>773</v>
+        <v>802</v>
       </c>
     </row>
     <row r="78" spans="152:152">
       <c r="EV78" t="s">
-        <v>774</v>
+        <v>803</v>
       </c>
     </row>
     <row r="79" spans="152:152">
       <c r="EV79" t="s">
-        <v>775</v>
+        <v>804</v>
       </c>
     </row>
     <row r="80" spans="152:152">
       <c r="EV80" t="s">
-        <v>776</v>
+        <v>805</v>
       </c>
     </row>
     <row r="81" spans="152:152">
       <c r="EV81" t="s">
-        <v>777</v>
+        <v>806</v>
       </c>
     </row>
     <row r="82" spans="152:152">
       <c r="EV82" t="s">
-        <v>778</v>
+        <v>807</v>
       </c>
     </row>
     <row r="83" spans="152:152">
       <c r="EV83" t="s">
-        <v>779</v>
+        <v>808</v>
       </c>
     </row>
     <row r="84" spans="152:152">
       <c r="EV84" t="s">
-        <v>780</v>
+        <v>809</v>
       </c>
     </row>
     <row r="85" spans="152:152">
       <c r="EV85" t="s">
-        <v>781</v>
+        <v>810</v>
       </c>
     </row>
     <row r="86" spans="152:152">
       <c r="EV86" t="s">
-        <v>782</v>
+        <v>811</v>
       </c>
     </row>
     <row r="87" spans="152:152">
       <c r="EV87" t="s">
-        <v>783</v>
+        <v>812</v>
       </c>
     </row>
     <row r="88" spans="152:152">
       <c r="EV88" t="s">
-        <v>784</v>
+        <v>813</v>
       </c>
     </row>
     <row r="89" spans="152:152">
       <c r="EV89" t="s">
-        <v>785</v>
+        <v>814</v>
       </c>
     </row>
     <row r="90" spans="152:152">
       <c r="EV90" t="s">
-        <v>786</v>
+        <v>815</v>
       </c>
     </row>
     <row r="91" spans="152:152">
       <c r="EV91" t="s">
-        <v>787</v>
+        <v>816</v>
       </c>
     </row>
     <row r="92" spans="152:152">
       <c r="EV92" t="s">
-        <v>788</v>
+        <v>817</v>
       </c>
     </row>
     <row r="93" spans="152:152">
       <c r="EV93" t="s">
-        <v>789</v>
+        <v>818</v>
       </c>
     </row>
     <row r="94" spans="152:152">
       <c r="EV94" t="s">
-        <v>790</v>
+        <v>819</v>
       </c>
     </row>
     <row r="95" spans="152:152">
       <c r="EV95" t="s">
-        <v>791</v>
+        <v>820</v>
       </c>
     </row>
     <row r="96" spans="152:152">
       <c r="EV96" t="s">
-        <v>792</v>
+        <v>821</v>
       </c>
     </row>
     <row r="97" spans="152:152">
       <c r="EV97" t="s">
-        <v>793</v>
+        <v>822</v>
       </c>
     </row>
     <row r="98" spans="152:152">
       <c r="EV98" t="s">
-        <v>794</v>
+        <v>823</v>
       </c>
     </row>
     <row r="99" spans="152:152">
       <c r="EV99" t="s">
-        <v>795</v>
+        <v>824</v>
       </c>
     </row>
     <row r="100" spans="152:152">
       <c r="EV100" t="s">
-        <v>796</v>
+        <v>825</v>
       </c>
     </row>
     <row r="101" spans="152:152">
       <c r="EV101" t="s">
-        <v>797</v>
+        <v>826</v>
       </c>
     </row>
     <row r="102" spans="152:152">
       <c r="EV102" t="s">
-        <v>798</v>
+        <v>827</v>
       </c>
     </row>
     <row r="103" spans="152:152">
       <c r="EV103" t="s">
-        <v>799</v>
+        <v>828</v>
       </c>
     </row>
     <row r="104" spans="152:152">
       <c r="EV104" t="s">
-        <v>800</v>
+        <v>829</v>
       </c>
     </row>
     <row r="105" spans="152:152">
       <c r="EV105" t="s">
-        <v>801</v>
+        <v>830</v>
       </c>
     </row>
     <row r="106" spans="152:152">
       <c r="EV106" t="s">
-        <v>802</v>
+        <v>831</v>
       </c>
     </row>
     <row r="107" spans="152:152">
       <c r="EV107" t="s">
-        <v>803</v>
+        <v>832</v>
       </c>
     </row>
     <row r="108" spans="152:152">
       <c r="EV108" t="s">
-        <v>804</v>
+        <v>833</v>
       </c>
     </row>
     <row r="109" spans="152:152">
       <c r="EV109" t="s">
-        <v>805</v>
+        <v>834</v>
       </c>
     </row>
     <row r="110" spans="152:152">
       <c r="EV110" t="s">
-        <v>806</v>
+        <v>835</v>
       </c>
     </row>
     <row r="111" spans="152:152">
       <c r="EV111" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
     </row>
     <row r="112" spans="152:152">
       <c r="EV112" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="113" spans="152:152">
       <c r="EV113" t="s">
-        <v>809</v>
+        <v>838</v>
       </c>
     </row>
     <row r="114" spans="152:152">
       <c r="EV114" t="s">
-        <v>810</v>
+        <v>839</v>
       </c>
     </row>
     <row r="115" spans="152:152">
       <c r="EV115" t="s">
-        <v>811</v>
+        <v>840</v>
       </c>
     </row>
     <row r="116" spans="152:152">
       <c r="EV116" t="s">
-        <v>812</v>
+        <v>841</v>
       </c>
     </row>
     <row r="117" spans="152:152">
       <c r="EV117" t="s">
-        <v>813</v>
+        <v>842</v>
       </c>
     </row>
     <row r="118" spans="152:152">
       <c r="EV118" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
     </row>
     <row r="119" spans="152:152">
       <c r="EV119" t="s">
-        <v>815</v>
+        <v>844</v>
       </c>
     </row>
     <row r="120" spans="152:152">
       <c r="EV120" t="s">
-        <v>816</v>
+        <v>845</v>
       </c>
     </row>
     <row r="121" spans="152:152">
       <c r="EV121" t="s">
-        <v>817</v>
+        <v>846</v>
       </c>
     </row>
     <row r="122" spans="152:152">
       <c r="EV122" t="s">
-        <v>818</v>
+        <v>847</v>
       </c>
     </row>
     <row r="123" spans="152:152">
       <c r="EV123" t="s">
-        <v>819</v>
+        <v>848</v>
       </c>
     </row>
     <row r="124" spans="152:152">
       <c r="EV124" t="s">
-        <v>820</v>
+        <v>849</v>
       </c>
     </row>
     <row r="125" spans="152:152">
       <c r="EV125" t="s">
-        <v>821</v>
+        <v>850</v>
       </c>
     </row>
     <row r="126" spans="152:152">
       <c r="EV126" t="s">
-        <v>822</v>
+        <v>851</v>
       </c>
     </row>
     <row r="127" spans="152:152">
       <c r="EV127" t="s">
-        <v>823</v>
+        <v>852</v>
       </c>
     </row>
     <row r="128" spans="152:152">
       <c r="EV128" t="s">
-        <v>824</v>
+        <v>853</v>
       </c>
     </row>
     <row r="129" spans="152:152">
       <c r="EV129" t="s">
-        <v>825</v>
+        <v>854</v>
       </c>
     </row>
     <row r="130" spans="152:152">
       <c r="EV130" t="s">
-        <v>826</v>
+        <v>855</v>
       </c>
     </row>
     <row r="131" spans="152:152">
       <c r="EV131" t="s">
-        <v>827</v>
+        <v>856</v>
       </c>
     </row>
     <row r="132" spans="152:152">
       <c r="EV132" t="s">
-        <v>828</v>
+        <v>857</v>
       </c>
     </row>
     <row r="133" spans="152:152">
       <c r="EV133" t="s">
-        <v>829</v>
+        <v>858</v>
       </c>
     </row>
     <row r="134" spans="152:152">
       <c r="EV134" t="s">
-        <v>830</v>
+        <v>859</v>
       </c>
     </row>
     <row r="135" spans="152:152">
       <c r="EV135" t="s">
-        <v>831</v>
+        <v>860</v>
       </c>
     </row>
     <row r="136" spans="152:152">
       <c r="EV136" t="s">
-        <v>832</v>
+        <v>861</v>
       </c>
     </row>
     <row r="137" spans="152:152">
       <c r="EV137" t="s">
-        <v>833</v>
+        <v>862</v>
       </c>
     </row>
     <row r="138" spans="152:152">
       <c r="EV138" t="s">
-        <v>834</v>
+        <v>863</v>
       </c>
     </row>
     <row r="139" spans="152:152">
       <c r="EV139" t="s">
-        <v>835</v>
+        <v>864</v>
       </c>
     </row>
     <row r="140" spans="152:152">
       <c r="EV140" t="s">
-        <v>836</v>
+        <v>865</v>
       </c>
     </row>
     <row r="141" spans="152:152">
       <c r="EV141" t="s">
-        <v>837</v>
+        <v>866</v>
       </c>
     </row>
     <row r="142" spans="152:152">
       <c r="EV142" t="s">
-        <v>838</v>
+        <v>867</v>
       </c>
     </row>
     <row r="143" spans="152:152">
       <c r="EV143" t="s">
-        <v>839</v>
+        <v>868</v>
       </c>
     </row>
     <row r="144" spans="152:152">
       <c r="EV144" t="s">
-        <v>840</v>
+        <v>869</v>
       </c>
     </row>
     <row r="145" spans="152:152">
       <c r="EV145" t="s">
-        <v>841</v>
+        <v>870</v>
       </c>
     </row>
     <row r="146" spans="152:152">
       <c r="EV146" t="s">
-        <v>842</v>
+        <v>871</v>
       </c>
     </row>
     <row r="147" spans="152:152">
       <c r="EV147" t="s">
-        <v>843</v>
+        <v>872</v>
       </c>
     </row>
     <row r="148" spans="152:152">
       <c r="EV148" t="s">
-        <v>844</v>
+        <v>873</v>
       </c>
     </row>
     <row r="149" spans="152:152">
       <c r="EV149" t="s">
-        <v>845</v>
+        <v>874</v>
       </c>
     </row>
     <row r="150" spans="152:152">
       <c r="EV150" t="s">
-        <v>846</v>
+        <v>875</v>
       </c>
     </row>
     <row r="151" spans="152:152">
       <c r="EV151" t="s">
-        <v>847</v>
+        <v>876</v>
       </c>
     </row>
     <row r="152" spans="152:152">
       <c r="EV152" t="s">
-        <v>848</v>
+        <v>877</v>
       </c>
     </row>
     <row r="153" spans="152:152">
       <c r="EV153" t="s">
-        <v>849</v>
+        <v>878</v>
       </c>
     </row>
     <row r="154" spans="152:152">
       <c r="EV154" t="s">
-        <v>850</v>
+        <v>879</v>
       </c>
     </row>
     <row r="155" spans="152:152">
       <c r="EV155" t="s">
-        <v>851</v>
+        <v>880</v>
       </c>
     </row>
     <row r="156" spans="152:152">
       <c r="EV156" t="s">
-        <v>852</v>
+        <v>881</v>
       </c>
     </row>
     <row r="157" spans="152:152">
       <c r="EV157" t="s">
-        <v>853</v>
+        <v>882</v>
       </c>
     </row>
     <row r="158" spans="152:152">
       <c r="EV158" t="s">
-        <v>854</v>
+        <v>883</v>
       </c>
     </row>
     <row r="159" spans="152:152">
       <c r="EV159" t="s">
-        <v>855</v>
+        <v>884</v>
       </c>
     </row>
     <row r="160" spans="152:152">
       <c r="EV160" t="s">
-        <v>856</v>
+        <v>885</v>
       </c>
     </row>
     <row r="161" spans="152:152">
       <c r="EV161" t="s">
-        <v>857</v>
+        <v>886</v>
       </c>
     </row>
     <row r="162" spans="152:152">
       <c r="EV162" t="s">
-        <v>858</v>
+        <v>887</v>
       </c>
     </row>
     <row r="163" spans="152:152">
       <c r="EV163" t="s">
-        <v>859</v>
+        <v>888</v>
       </c>
     </row>
     <row r="164" spans="152:152">
       <c r="EV164" t="s">
-        <v>860</v>
+        <v>889</v>
       </c>
     </row>
     <row r="165" spans="152:152">
       <c r="EV165" t="s">
-        <v>861</v>
+        <v>890</v>
       </c>
     </row>
     <row r="166" spans="152:152">
       <c r="EV166" t="s">
-        <v>862</v>
+        <v>891</v>
       </c>
     </row>
     <row r="167" spans="152:152">
       <c r="EV167" t="s">
-        <v>863</v>
+        <v>892</v>
       </c>
     </row>
     <row r="168" spans="152:152">
       <c r="EV168" t="s">
-        <v>864</v>
+        <v>893</v>
       </c>
     </row>
     <row r="169" spans="152:152">
       <c r="EV169" t="s">
-        <v>865</v>
+        <v>894</v>
       </c>
     </row>
     <row r="170" spans="152:152">
       <c r="EV170" t="s">
-        <v>866</v>
+        <v>895</v>
       </c>
     </row>
     <row r="171" spans="152:152">
       <c r="EV171" t="s">
-        <v>867</v>
+        <v>896</v>
       </c>
     </row>
     <row r="172" spans="152:152">
       <c r="EV172" t="s">
-        <v>868</v>
+        <v>897</v>
       </c>
     </row>
     <row r="173" spans="152:152">
       <c r="EV173" t="s">
-        <v>869</v>
+        <v>898</v>
       </c>
     </row>
     <row r="174" spans="152:152">
       <c r="EV174" t="s">
-        <v>870</v>
+        <v>899</v>
       </c>
     </row>
     <row r="175" spans="152:152">
       <c r="EV175" t="s">
-        <v>871</v>
+        <v>900</v>
       </c>
     </row>
     <row r="176" spans="152:152">
       <c r="EV176" t="s">
-        <v>872</v>
+        <v>901</v>
       </c>
     </row>
     <row r="177" spans="152:152">
       <c r="EV177" t="s">
-        <v>873</v>
+        <v>902</v>
       </c>
     </row>
     <row r="178" spans="152:152">
       <c r="EV178" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
     </row>
     <row r="179" spans="152:152">
       <c r="EV179" t="s">
-        <v>875</v>
+        <v>904</v>
       </c>
     </row>
     <row r="180" spans="152:152">
       <c r="EV180" t="s">
-        <v>876</v>
+        <v>905</v>
       </c>
     </row>
     <row r="181" spans="152:152">
       <c r="EV181" t="s">
-        <v>877</v>
+        <v>906</v>
       </c>
     </row>
     <row r="182" spans="152:152">
       <c r="EV182" t="s">
-        <v>878</v>
+        <v>907</v>
       </c>
     </row>
     <row r="183" spans="152:152">
       <c r="EV183" t="s">
-        <v>879</v>
+        <v>908</v>
       </c>
     </row>
     <row r="184" spans="152:152">
       <c r="EV184" t="s">
-        <v>880</v>
+        <v>909</v>
       </c>
     </row>
     <row r="185" spans="152:152">
       <c r="EV185" t="s">
-        <v>881</v>
+        <v>910</v>
       </c>
     </row>
     <row r="186" spans="152:152">
       <c r="EV186" t="s">
-        <v>882</v>
+        <v>911</v>
       </c>
     </row>
     <row r="187" spans="152:152">
       <c r="EV187" t="s">
-        <v>883</v>
+        <v>912</v>
       </c>
     </row>
     <row r="188" spans="152:152">
       <c r="EV188" t="s">
-        <v>884</v>
+        <v>913</v>
       </c>
     </row>
     <row r="189" spans="152:152">
       <c r="EV189" t="s">
-        <v>885</v>
+        <v>914</v>
       </c>
     </row>
     <row r="190" spans="152:152">
       <c r="EV190" t="s">
-        <v>886</v>
+        <v>915</v>
       </c>
     </row>
     <row r="191" spans="152:152">
       <c r="EV191" t="s">
-        <v>887</v>
+        <v>916</v>
       </c>
     </row>
     <row r="192" spans="152:152">
       <c r="EV192" t="s">
-        <v>888</v>
+        <v>917</v>
       </c>
     </row>
     <row r="193" spans="152:152">
       <c r="EV193" t="s">
-        <v>889</v>
+        <v>918</v>
       </c>
     </row>
     <row r="194" spans="152:152">
       <c r="EV194" t="s">
-        <v>890</v>
+        <v>919</v>
       </c>
     </row>
     <row r="195" spans="152:152">
       <c r="EV195" t="s">
-        <v>891</v>
+        <v>920</v>
       </c>
     </row>
     <row r="196" spans="152:152">
       <c r="EV196" t="s">
-        <v>892</v>
+        <v>921</v>
       </c>
     </row>
     <row r="197" spans="152:152">
       <c r="EV197" t="s">
-        <v>893</v>
+        <v>922</v>
       </c>
     </row>
     <row r="198" spans="152:152">
       <c r="EV198" t="s">
-        <v>894</v>
+        <v>923</v>
       </c>
     </row>
     <row r="199" spans="152:152">
       <c r="EV199" t="s">
-        <v>895</v>
+        <v>924</v>
       </c>
     </row>
     <row r="200" spans="152:152">
       <c r="EV200" t="s">
-        <v>896</v>
+        <v>925</v>
       </c>
     </row>
     <row r="201" spans="152:152">
       <c r="EV201" t="s">
-        <v>897</v>
+        <v>926</v>
       </c>
     </row>
     <row r="202" spans="152:152">
       <c r="EV202" t="s">
-        <v>898</v>
+        <v>927</v>
       </c>
     </row>
     <row r="203" spans="152:152">
       <c r="EV203" t="s">
-        <v>899</v>
+        <v>928</v>
       </c>
     </row>
     <row r="204" spans="152:152">
       <c r="EV204" t="s">
-        <v>900</v>
+        <v>929</v>
       </c>
     </row>
     <row r="205" spans="152:152">
       <c r="EV205" t="s">
-        <v>901</v>
+        <v>930</v>
       </c>
     </row>
     <row r="206" spans="152:152">
       <c r="EV206" t="s">
-        <v>902</v>
+        <v>931</v>
       </c>
     </row>
     <row r="207" spans="152:152">
       <c r="EV207" t="s">
-        <v>903</v>
+        <v>932</v>
       </c>
     </row>
     <row r="208" spans="152:152">
       <c r="EV208" t="s">
-        <v>904</v>
+        <v>933</v>
       </c>
     </row>
     <row r="209" spans="152:152">
       <c r="EV209" t="s">
-        <v>905</v>
+        <v>934</v>
       </c>
     </row>
     <row r="210" spans="152:152">
       <c r="EV210" t="s">
-        <v>906</v>
+        <v>935</v>
       </c>
     </row>
     <row r="211" spans="152:152">
       <c r="EV211" t="s">
-        <v>907</v>
+        <v>936</v>
       </c>
     </row>
     <row r="212" spans="152:152">
       <c r="EV212" t="s">
-        <v>908</v>
+        <v>937</v>
       </c>
     </row>
     <row r="213" spans="152:152">
       <c r="EV213" t="s">
-        <v>909</v>
+        <v>938</v>
       </c>
     </row>
     <row r="214" spans="152:152">
       <c r="EV214" t="s">
-        <v>910</v>
+        <v>939</v>
       </c>
     </row>
     <row r="215" spans="152:152">
       <c r="EV215" t="s">
-        <v>911</v>
+        <v>940</v>
       </c>
     </row>
     <row r="216" spans="152:152">
       <c r="EV216" t="s">
-        <v>912</v>
+        <v>941</v>
       </c>
     </row>
     <row r="217" spans="152:152">
       <c r="EV217" t="s">
-        <v>913</v>
+        <v>942</v>
       </c>
     </row>
     <row r="218" spans="152:152">
       <c r="EV218" t="s">
-        <v>914</v>
+        <v>943</v>
       </c>
     </row>
     <row r="219" spans="152:152">
       <c r="EV219" t="s">
-        <v>915</v>
+        <v>944</v>
       </c>
     </row>
     <row r="220" spans="152:152">
       <c r="EV220" t="s">
-        <v>916</v>
+        <v>945</v>
       </c>
     </row>
     <row r="221" spans="152:152">
       <c r="EV221" t="s">
-        <v>917</v>
+        <v>946</v>
       </c>
     </row>
     <row r="222" spans="152:152">
       <c r="EV222" t="s">
-        <v>918</v>
+        <v>947</v>
       </c>
     </row>
     <row r="223" spans="152:152">
       <c r="EV223" t="s">
-        <v>919</v>
+        <v>948</v>
       </c>
     </row>
     <row r="224" spans="152:152">
       <c r="EV224" t="s">
-        <v>920</v>
+        <v>949</v>
       </c>
     </row>
     <row r="225" spans="152:152">
       <c r="EV225" t="s">
-        <v>921</v>
+        <v>950</v>
       </c>
     </row>
     <row r="226" spans="152:152">
       <c r="EV226" t="s">
-        <v>922</v>
+        <v>951</v>
       </c>
     </row>
     <row r="227" spans="152:152">
       <c r="EV227" t="s">
-        <v>923</v>
+        <v>952</v>
       </c>
     </row>
     <row r="228" spans="152:152">
       <c r="EV228" t="s">
-        <v>924</v>
+        <v>953</v>
       </c>
     </row>
     <row r="229" spans="152:152">
       <c r="EV229" t="s">
-        <v>925</v>
+        <v>954</v>
       </c>
     </row>
     <row r="230" spans="152:152">
       <c r="EV230" t="s">
-        <v>926</v>
+        <v>955</v>
       </c>
     </row>
     <row r="231" spans="152:152">
       <c r="EV231" t="s">
-        <v>927</v>
+        <v>956</v>
       </c>
     </row>
     <row r="232" spans="152:152">
       <c r="EV232" t="s">
-        <v>928</v>
+        <v>957</v>
       </c>
     </row>
     <row r="233" spans="152:152">
       <c r="EV233" t="s">
-        <v>929</v>
+        <v>958</v>
       </c>
     </row>
     <row r="234" spans="152:152">
       <c r="EV234" t="s">
-        <v>930</v>
+        <v>959</v>
       </c>
     </row>
     <row r="235" spans="152:152">
       <c r="EV235" t="s">
-        <v>931</v>
+        <v>960</v>
       </c>
     </row>
     <row r="236" spans="152:152">
       <c r="EV236" t="s">
-        <v>932</v>
+        <v>961</v>
       </c>
     </row>
     <row r="237" spans="152:152">
       <c r="EV237" t="s">
-        <v>933</v>
+        <v>962</v>
       </c>
     </row>
     <row r="238" spans="152:152">
       <c r="EV238" t="s">
-        <v>934</v>
+        <v>963</v>
       </c>
     </row>
     <row r="239" spans="152:152">
       <c r="EV239" t="s">
-        <v>935</v>
+        <v>964</v>
       </c>
     </row>
     <row r="240" spans="152:152">
       <c r="EV240" t="s">
-        <v>936</v>
+        <v>965</v>
       </c>
     </row>
     <row r="241" spans="152:152">
       <c r="EV241" t="s">
-        <v>937</v>
+        <v>966</v>
       </c>
     </row>
     <row r="242" spans="152:152">
       <c r="EV242" t="s">
-        <v>938</v>
+        <v>967</v>
       </c>
     </row>
     <row r="243" spans="152:152">
       <c r="EV243" t="s">
-        <v>939</v>
+        <v>968</v>
       </c>
     </row>
     <row r="244" spans="152:152">
       <c r="EV244" t="s">
-        <v>940</v>
+        <v>969</v>
       </c>
     </row>
     <row r="245" spans="152:152">
       <c r="EV245" t="s">
-        <v>941</v>
+        <v>970</v>
       </c>
     </row>
     <row r="246" spans="152:152">
       <c r="EV246" t="s">
-        <v>942</v>
+        <v>971</v>
       </c>
     </row>
     <row r="247" spans="152:152">
       <c r="EV247" t="s">
-        <v>943</v>
+        <v>972</v>
       </c>
     </row>
     <row r="248" spans="152:152">
       <c r="EV248" t="s">
-        <v>944</v>
+        <v>973</v>
       </c>
     </row>
     <row r="249" spans="152:152">
       <c r="EV249" t="s">
-        <v>945</v>
+        <v>974</v>
       </c>
     </row>
     <row r="250" spans="152:152">
       <c r="EV250" t="s">
-        <v>946</v>
+        <v>975</v>
       </c>
     </row>
     <row r="251" spans="152:152">
       <c r="EV251" t="s">
-        <v>947</v>
+        <v>976</v>
       </c>
     </row>
     <row r="252" spans="152:152">
       <c r="EV252" t="s">
-        <v>948</v>
+        <v>977</v>
       </c>
     </row>
     <row r="253" spans="152:152">
       <c r="EV253" t="s">
-        <v>949</v>
+        <v>978</v>
       </c>
     </row>
     <row r="254" spans="152:152">
       <c r="EV254" t="s">
-        <v>950</v>
+        <v>979</v>
       </c>
     </row>
     <row r="255" spans="152:152">
       <c r="EV255" t="s">
-        <v>951</v>
+        <v>980</v>
       </c>
     </row>
     <row r="256" spans="152:152">
       <c r="EV256" t="s">
-        <v>952</v>
+        <v>981</v>
       </c>
     </row>
     <row r="257" spans="152:152">
       <c r="EV257" t="s">
-        <v>953</v>
+        <v>982</v>
       </c>
     </row>
     <row r="258" spans="152:152">
       <c r="EV258" t="s">
-        <v>954</v>
+        <v>983</v>
       </c>
     </row>
     <row r="259" spans="152:152">
       <c r="EV259" t="s">
-        <v>955</v>
+        <v>984</v>
       </c>
     </row>
     <row r="260" spans="152:152">
       <c r="EV260" t="s">
-        <v>956</v>
+        <v>985</v>
       </c>
     </row>
     <row r="261" spans="152:152">
       <c r="EV261" t="s">
-        <v>957</v>
+        <v>986</v>
       </c>
     </row>
     <row r="262" spans="152:152">
       <c r="EV262" t="s">
-        <v>958</v>
+        <v>987</v>
       </c>
     </row>
     <row r="263" spans="152:152">
       <c r="EV263" t="s">
-        <v>959</v>
+        <v>988</v>
       </c>
     </row>
     <row r="264" spans="152:152">
       <c r="EV264" t="s">
-        <v>960</v>
+        <v>989</v>
       </c>
     </row>
     <row r="265" spans="152:152">
       <c r="EV265" t="s">
-        <v>961</v>
+        <v>990</v>
       </c>
     </row>
     <row r="266" spans="152:152">
       <c r="EV266" t="s">
-        <v>962</v>
+        <v>991</v>
       </c>
     </row>
     <row r="267" spans="152:152">
       <c r="EV267" t="s">
-        <v>963</v>
+        <v>992</v>
       </c>
     </row>
     <row r="268" spans="152:152">
       <c r="EV268" t="s">
-        <v>964</v>
+        <v>993</v>
       </c>
     </row>
     <row r="269" spans="152:152">
       <c r="EV269" t="s">
-        <v>965</v>
+        <v>994</v>
       </c>
     </row>
     <row r="270" spans="152:152">
       <c r="EV270" t="s">
-        <v>966</v>
+        <v>995</v>
       </c>
     </row>
     <row r="271" spans="152:152">
       <c r="EV271" t="s">
-        <v>967</v>
+        <v>996</v>
       </c>
     </row>
     <row r="272" spans="152:152">
       <c r="EV272" t="s">
-        <v>968</v>
+        <v>997</v>
       </c>
     </row>
     <row r="273" spans="152:152">
       <c r="EV273" t="s">
-        <v>969</v>
+        <v>998</v>
       </c>
     </row>
     <row r="274" spans="152:152">
       <c r="EV274" t="s">
-        <v>970</v>
+        <v>999</v>
       </c>
     </row>
     <row r="275" spans="152:152">
       <c r="EV275" t="s">
-        <v>971</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="276" spans="152:152">
       <c r="EV276" t="s">
-        <v>972</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="277" spans="152:152">
       <c r="EV277" t="s">
-        <v>973</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="278" spans="152:152">
       <c r="EV278" t="s">
-        <v>974</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="279" spans="152:152">
       <c r="EV279" t="s">
-        <v>975</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="280" spans="152:152">
       <c r="EV280" t="s">
-        <v>976</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="281" spans="152:152">
       <c r="EV281" t="s">
-        <v>977</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="282" spans="152:152">
       <c r="EV282" t="s">
-        <v>978</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="283" spans="152:152">
       <c r="EV283" t="s">
-        <v>979</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="284" spans="152:152">
       <c r="EV284" t="s">
-        <v>980</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="285" spans="152:152">
       <c r="EV285" t="s">
-        <v>981</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="286" spans="152:152">
       <c r="EV286" t="s">
-        <v>982</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="287" spans="152:152">
       <c r="EV287" t="s">
-        <v>983</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="288" spans="152:152">
       <c r="EV288" t="s">
-        <v>984</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="289" spans="152:152">
       <c r="EV289" t="s">
-        <v>985</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="290" spans="152:152">
       <c r="EV290" t="s">
-        <v>986</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="291" spans="152:152">
       <c r="EV291" t="s">
-        <v>987</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="292" spans="152:152">
       <c r="EV292" t="s">
-        <v>988</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="293" spans="152:152">
       <c r="EV293" t="s">
-        <v>989</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="294" spans="152:152">
       <c r="EV294" t="s">
-        <v>990</v>
+        <v>1019</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000031/metadata_template_ERC000031.xlsx
+++ b/templates/ERC000031/metadata_template_ERC000031.xlsx
@@ -25,7 +25,7 @@
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$EV$1:$EV$294</definedName>
     <definedName name="heatingandcoolingsystemtype">'cv_sample'!$AT$1:$AT$5</definedName>
     <definedName name="indoorspace">'cv_sample'!$AR$1:$AR$12</definedName>
-    <definedName name="indoorsurface">'cv_sample'!$AQ$1:$AQ$8</definedName>
+    <definedName name="indoorsurface">'cv_sample'!$AQ$1:$AQ$9</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="1163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="1164">
   <si>
     <t>alias</t>
   </si>
@@ -1312,6 +1312,9 @@
   </si>
   <si>
     <t>door</t>
+  </si>
+  <si>
+    <t>floor</t>
   </si>
   <si>
     <t>shelving</t>
@@ -5195,538 +5198,538 @@
         <v>415</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="2" spans="1:220" ht="150" customHeight="1">
@@ -5857,538 +5860,538 @@
         <v>416</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
   </sheetData>
@@ -6483,40 +6486,40 @@
         <v>417</v>
       </c>
       <c r="AR1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AS1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AT1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AU1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AV1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AW1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AX1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AY1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="BC1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="BL1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="EV1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="FK1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="2" spans="8:167">
@@ -6542,40 +6545,40 @@
         <v>418</v>
       </c>
       <c r="AR2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AS2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AT2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AU2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AV2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AW2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AX2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AY2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="BC2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="BL2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="EV2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="FK2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="3" spans="8:167">
@@ -6601,37 +6604,37 @@
         <v>419</v>
       </c>
       <c r="AR3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AS3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AT3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AU3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AV3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AW3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AX3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="BC3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="BL3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="EV3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="FK3" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="4" spans="8:167">
@@ -6654,28 +6657,28 @@
         <v>420</v>
       </c>
       <c r="AR4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AS4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AT4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AW4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AX4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="BL4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="EV4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="FK4" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="5" spans="8:167">
@@ -6698,25 +6701,25 @@
         <v>421</v>
       </c>
       <c r="AR5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AS5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AT5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AX5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="BL5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="EV5" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="FK5" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="6" spans="8:167">
@@ -6736,19 +6739,19 @@
         <v>422</v>
       </c>
       <c r="AR6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AS6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AX6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="BL6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="EV6" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="7" spans="8:167">
@@ -6768,19 +6771,19 @@
         <v>423</v>
       </c>
       <c r="AR7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AS7" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AX7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="BL7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="EV7" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="8" spans="8:167">
@@ -6797,16 +6800,16 @@
         <v>424</v>
       </c>
       <c r="AR8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AX8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="BL8" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="EV8" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="9" spans="8:167">
@@ -6816,17 +6819,20 @@
       <c r="AO9" t="s">
         <v>397</v>
       </c>
+      <c r="AQ9" t="s">
+        <v>425</v>
+      </c>
       <c r="AR9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AX9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="BL9" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="EV9" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="10" spans="8:167">
@@ -6837,16 +6843,16 @@
         <v>398</v>
       </c>
       <c r="AR10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AX10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="BL10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="EV10" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="11" spans="8:167">
@@ -6857,16 +6863,16 @@
         <v>399</v>
       </c>
       <c r="AR11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AX11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="BL11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="EV11" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="12" spans="8:167">
@@ -6877,16 +6883,16 @@
         <v>400</v>
       </c>
       <c r="AR12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AX12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="BL12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="EV12" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="13" spans="8:167">
@@ -6897,13 +6903,13 @@
         <v>401</v>
       </c>
       <c r="AX13" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="BL13" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="EV13" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="14" spans="8:167">
@@ -6914,13 +6920,13 @@
         <v>402</v>
       </c>
       <c r="AX14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="BL14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="EV14" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="15" spans="8:167">
@@ -6931,13 +6937,13 @@
         <v>403</v>
       </c>
       <c r="AX15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="BL15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="EV15" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="16" spans="8:167">
@@ -6948,13 +6954,13 @@
         <v>404</v>
       </c>
       <c r="AX16" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="BL16" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="EV16" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="17" spans="8:152">
@@ -6962,13 +6968,13 @@
         <v>294</v>
       </c>
       <c r="AX17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="BL17" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="EV17" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="18" spans="8:152">
@@ -6976,13 +6982,13 @@
         <v>295</v>
       </c>
       <c r="AX18" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="BL18" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="EV18" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="19" spans="8:152">
@@ -6990,13 +6996,13 @@
         <v>296</v>
       </c>
       <c r="AX19" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="BL19" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="EV19" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="20" spans="8:152">
@@ -7004,13 +7010,13 @@
         <v>297</v>
       </c>
       <c r="AX20" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="BL20" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="EV20" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="21" spans="8:152">
@@ -7018,13 +7024,13 @@
         <v>298</v>
       </c>
       <c r="AX21" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="BL21" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="EV21" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22" spans="8:152">
@@ -7032,10 +7038,10 @@
         <v>299</v>
       </c>
       <c r="BL22" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="EV22" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="23" spans="8:152">
@@ -7043,10 +7049,10 @@
         <v>300</v>
       </c>
       <c r="BL23" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="EV23" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="24" spans="8:152">
@@ -7054,10 +7060,10 @@
         <v>301</v>
       </c>
       <c r="BL24" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="EV24" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="25" spans="8:152">
@@ -7065,10 +7071,10 @@
         <v>302</v>
       </c>
       <c r="BL25" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="EV25" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="26" spans="8:152">
@@ -7076,10 +7082,10 @@
         <v>303</v>
       </c>
       <c r="BL26" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="EV26" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="27" spans="8:152">
@@ -7087,10 +7093,10 @@
         <v>304</v>
       </c>
       <c r="BL27" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="EV27" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="28" spans="8:152">
@@ -7098,7 +7104,7 @@
         <v>305</v>
       </c>
       <c r="EV28" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="29" spans="8:152">
@@ -7106,7 +7112,7 @@
         <v>306</v>
       </c>
       <c r="EV29" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="30" spans="8:152">
@@ -7114,1327 +7120,1327 @@
         <v>307</v>
       </c>
       <c r="EV30" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="31" spans="8:152">
       <c r="EV31" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="32" spans="8:152">
       <c r="EV32" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="33" spans="152:152">
       <c r="EV33" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="34" spans="152:152">
       <c r="EV34" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="35" spans="152:152">
       <c r="EV35" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="36" spans="152:152">
       <c r="EV36" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="37" spans="152:152">
       <c r="EV37" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="38" spans="152:152">
       <c r="EV38" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="39" spans="152:152">
       <c r="EV39" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="40" spans="152:152">
       <c r="EV40" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="41" spans="152:152">
       <c r="EV41" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="42" spans="152:152">
       <c r="EV42" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="43" spans="152:152">
       <c r="EV43" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="44" spans="152:152">
       <c r="EV44" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="45" spans="152:152">
       <c r="EV45" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="46" spans="152:152">
       <c r="EV46" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="47" spans="152:152">
       <c r="EV47" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="48" spans="152:152">
       <c r="EV48" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="49" spans="152:152">
       <c r="EV49" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="50" spans="152:152">
       <c r="EV50" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="51" spans="152:152">
       <c r="EV51" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="52" spans="152:152">
       <c r="EV52" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="53" spans="152:152">
       <c r="EV53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="54" spans="152:152">
       <c r="EV54" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="55" spans="152:152">
       <c r="EV55" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="56" spans="152:152">
       <c r="EV56" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="57" spans="152:152">
       <c r="EV57" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="58" spans="152:152">
       <c r="EV58" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="59" spans="152:152">
       <c r="EV59" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="60" spans="152:152">
       <c r="EV60" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="61" spans="152:152">
       <c r="EV61" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="62" spans="152:152">
       <c r="EV62" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="63" spans="152:152">
       <c r="EV63" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="64" spans="152:152">
       <c r="EV64" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="65" spans="152:152">
       <c r="EV65" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="66" spans="152:152">
       <c r="EV66" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="67" spans="152:152">
       <c r="EV67" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="68" spans="152:152">
       <c r="EV68" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="69" spans="152:152">
       <c r="EV69" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="70" spans="152:152">
       <c r="EV70" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="71" spans="152:152">
       <c r="EV71" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="72" spans="152:152">
       <c r="EV72" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="73" spans="152:152">
       <c r="EV73" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="74" spans="152:152">
       <c r="EV74" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="75" spans="152:152">
       <c r="EV75" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="76" spans="152:152">
       <c r="EV76" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="77" spans="152:152">
       <c r="EV77" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="78" spans="152:152">
       <c r="EV78" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="79" spans="152:152">
       <c r="EV79" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="80" spans="152:152">
       <c r="EV80" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="81" spans="152:152">
       <c r="EV81" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="82" spans="152:152">
       <c r="EV82" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="83" spans="152:152">
       <c r="EV83" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="84" spans="152:152">
       <c r="EV84" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="85" spans="152:152">
       <c r="EV85" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="86" spans="152:152">
       <c r="EV86" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="87" spans="152:152">
       <c r="EV87" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="88" spans="152:152">
       <c r="EV88" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="89" spans="152:152">
       <c r="EV89" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="90" spans="152:152">
       <c r="EV90" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="91" spans="152:152">
       <c r="EV91" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="92" spans="152:152">
       <c r="EV92" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="93" spans="152:152">
       <c r="EV93" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="94" spans="152:152">
       <c r="EV94" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="95" spans="152:152">
       <c r="EV95" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="96" spans="152:152">
       <c r="EV96" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="97" spans="152:152">
       <c r="EV97" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="98" spans="152:152">
       <c r="EV98" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="99" spans="152:152">
       <c r="EV99" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="100" spans="152:152">
       <c r="EV100" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="101" spans="152:152">
       <c r="EV101" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="102" spans="152:152">
       <c r="EV102" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="103" spans="152:152">
       <c r="EV103" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="104" spans="152:152">
       <c r="EV104" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="105" spans="152:152">
       <c r="EV105" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="106" spans="152:152">
       <c r="EV106" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="107" spans="152:152">
       <c r="EV107" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="108" spans="152:152">
       <c r="EV108" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="109" spans="152:152">
       <c r="EV109" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="110" spans="152:152">
       <c r="EV110" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="111" spans="152:152">
       <c r="EV111" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="112" spans="152:152">
       <c r="EV112" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="113" spans="152:152">
       <c r="EV113" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="114" spans="152:152">
       <c r="EV114" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="115" spans="152:152">
       <c r="EV115" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="116" spans="152:152">
       <c r="EV116" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="117" spans="152:152">
       <c r="EV117" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="118" spans="152:152">
       <c r="EV118" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="119" spans="152:152">
       <c r="EV119" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="120" spans="152:152">
       <c r="EV120" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="121" spans="152:152">
       <c r="EV121" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="122" spans="152:152">
       <c r="EV122" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="123" spans="152:152">
       <c r="EV123" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="124" spans="152:152">
       <c r="EV124" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="125" spans="152:152">
       <c r="EV125" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="126" spans="152:152">
       <c r="EV126" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="127" spans="152:152">
       <c r="EV127" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="128" spans="152:152">
       <c r="EV128" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="129" spans="152:152">
       <c r="EV129" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="130" spans="152:152">
       <c r="EV130" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="131" spans="152:152">
       <c r="EV131" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="132" spans="152:152">
       <c r="EV132" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="133" spans="152:152">
       <c r="EV133" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="134" spans="152:152">
       <c r="EV134" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="135" spans="152:152">
       <c r="EV135" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="136" spans="152:152">
       <c r="EV136" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="137" spans="152:152">
       <c r="EV137" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="138" spans="152:152">
       <c r="EV138" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="139" spans="152:152">
       <c r="EV139" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="140" spans="152:152">
       <c r="EV140" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="141" spans="152:152">
       <c r="EV141" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="142" spans="152:152">
       <c r="EV142" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="143" spans="152:152">
       <c r="EV143" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="144" spans="152:152">
       <c r="EV144" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="145" spans="152:152">
       <c r="EV145" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="146" spans="152:152">
       <c r="EV146" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="147" spans="152:152">
       <c r="EV147" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="148" spans="152:152">
       <c r="EV148" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="149" spans="152:152">
       <c r="EV149" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="150" spans="152:152">
       <c r="EV150" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="151" spans="152:152">
       <c r="EV151" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="152" spans="152:152">
       <c r="EV152" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="153" spans="152:152">
       <c r="EV153" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="154" spans="152:152">
       <c r="EV154" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="155" spans="152:152">
       <c r="EV155" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="156" spans="152:152">
       <c r="EV156" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="157" spans="152:152">
       <c r="EV157" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="158" spans="152:152">
       <c r="EV158" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="159" spans="152:152">
       <c r="EV159" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="160" spans="152:152">
       <c r="EV160" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="161" spans="152:152">
       <c r="EV161" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="162" spans="152:152">
       <c r="EV162" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="163" spans="152:152">
       <c r="EV163" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="164" spans="152:152">
       <c r="EV164" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="165" spans="152:152">
       <c r="EV165" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="166" spans="152:152">
       <c r="EV166" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="167" spans="152:152">
       <c r="EV167" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="168" spans="152:152">
       <c r="EV168" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="169" spans="152:152">
       <c r="EV169" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="170" spans="152:152">
       <c r="EV170" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="171" spans="152:152">
       <c r="EV171" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="172" spans="152:152">
       <c r="EV172" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="173" spans="152:152">
       <c r="EV173" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="174" spans="152:152">
       <c r="EV174" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="175" spans="152:152">
       <c r="EV175" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="176" spans="152:152">
       <c r="EV176" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="177" spans="152:152">
       <c r="EV177" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="178" spans="152:152">
       <c r="EV178" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="179" spans="152:152">
       <c r="EV179" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="180" spans="152:152">
       <c r="EV180" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="181" spans="152:152">
       <c r="EV181" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="182" spans="152:152">
       <c r="EV182" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="183" spans="152:152">
       <c r="EV183" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="184" spans="152:152">
       <c r="EV184" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="185" spans="152:152">
       <c r="EV185" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="186" spans="152:152">
       <c r="EV186" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="187" spans="152:152">
       <c r="EV187" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="188" spans="152:152">
       <c r="EV188" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="189" spans="152:152">
       <c r="EV189" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="190" spans="152:152">
       <c r="EV190" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="191" spans="152:152">
       <c r="EV191" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="192" spans="152:152">
       <c r="EV192" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="193" spans="152:152">
       <c r="EV193" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="194" spans="152:152">
       <c r="EV194" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="195" spans="152:152">
       <c r="EV195" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="196" spans="152:152">
       <c r="EV196" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="197" spans="152:152">
       <c r="EV197" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="198" spans="152:152">
       <c r="EV198" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="199" spans="152:152">
       <c r="EV199" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="200" spans="152:152">
       <c r="EV200" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="201" spans="152:152">
       <c r="EV201" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="202" spans="152:152">
       <c r="EV202" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="203" spans="152:152">
       <c r="EV203" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="204" spans="152:152">
       <c r="EV204" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="205" spans="152:152">
       <c r="EV205" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="206" spans="152:152">
       <c r="EV206" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="207" spans="152:152">
       <c r="EV207" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="208" spans="152:152">
       <c r="EV208" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="209" spans="152:152">
       <c r="EV209" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="210" spans="152:152">
       <c r="EV210" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="211" spans="152:152">
       <c r="EV211" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="212" spans="152:152">
       <c r="EV212" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="213" spans="152:152">
       <c r="EV213" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="214" spans="152:152">
       <c r="EV214" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="215" spans="152:152">
       <c r="EV215" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="216" spans="152:152">
       <c r="EV216" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="217" spans="152:152">
       <c r="EV217" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="218" spans="152:152">
       <c r="EV218" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="219" spans="152:152">
       <c r="EV219" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="220" spans="152:152">
       <c r="EV220" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="221" spans="152:152">
       <c r="EV221" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="222" spans="152:152">
       <c r="EV222" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="223" spans="152:152">
       <c r="EV223" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="224" spans="152:152">
       <c r="EV224" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="225" spans="152:152">
       <c r="EV225" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="226" spans="152:152">
       <c r="EV226" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="227" spans="152:152">
       <c r="EV227" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="228" spans="152:152">
       <c r="EV228" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="229" spans="152:152">
       <c r="EV229" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="230" spans="152:152">
       <c r="EV230" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="231" spans="152:152">
       <c r="EV231" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="232" spans="152:152">
       <c r="EV232" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="233" spans="152:152">
       <c r="EV233" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="234" spans="152:152">
       <c r="EV234" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="235" spans="152:152">
       <c r="EV235" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="236" spans="152:152">
       <c r="EV236" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="237" spans="152:152">
       <c r="EV237" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="238" spans="152:152">
       <c r="EV238" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="239" spans="152:152">
       <c r="EV239" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="240" spans="152:152">
       <c r="EV240" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="241" spans="152:152">
       <c r="EV241" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="242" spans="152:152">
       <c r="EV242" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="243" spans="152:152">
       <c r="EV243" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="244" spans="152:152">
       <c r="EV244" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="245" spans="152:152">
       <c r="EV245" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="246" spans="152:152">
       <c r="EV246" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="247" spans="152:152">
       <c r="EV247" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="248" spans="152:152">
       <c r="EV248" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="249" spans="152:152">
       <c r="EV249" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="250" spans="152:152">
       <c r="EV250" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="251" spans="152:152">
       <c r="EV251" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="252" spans="152:152">
       <c r="EV252" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="253" spans="152:152">
       <c r="EV253" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="254" spans="152:152">
       <c r="EV254" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="255" spans="152:152">
       <c r="EV255" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="256" spans="152:152">
       <c r="EV256" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="257" spans="152:152">
       <c r="EV257" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="258" spans="152:152">
       <c r="EV258" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="259" spans="152:152">
       <c r="EV259" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="260" spans="152:152">
       <c r="EV260" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="261" spans="152:152">
       <c r="EV261" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="262" spans="152:152">
       <c r="EV262" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="263" spans="152:152">
       <c r="EV263" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="264" spans="152:152">
       <c r="EV264" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="265" spans="152:152">
       <c r="EV265" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="266" spans="152:152">
       <c r="EV266" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="267" spans="152:152">
       <c r="EV267" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="268" spans="152:152">
       <c r="EV268" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="269" spans="152:152">
       <c r="EV269" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="270" spans="152:152">
       <c r="EV270" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="271" spans="152:152">
       <c r="EV271" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="272" spans="152:152">
       <c r="EV272" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="273" spans="152:152">
       <c r="EV273" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="274" spans="152:152">
       <c r="EV274" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="275" spans="152:152">
       <c r="EV275" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="276" spans="152:152">
       <c r="EV276" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="277" spans="152:152">
       <c r="EV277" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="278" spans="152:152">
       <c r="EV278" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="279" spans="152:152">
       <c r="EV279" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="280" spans="152:152">
       <c r="EV280" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="281" spans="152:152">
       <c r="EV281" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="282" spans="152:152">
       <c r="EV282" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="283" spans="152:152">
       <c r="EV283" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="284" spans="152:152">
       <c r="EV284" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="285" spans="152:152">
       <c r="EV285" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="286" spans="152:152">
       <c r="EV286" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="287" spans="152:152">
       <c r="EV287" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="288" spans="152:152">
       <c r="EV288" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="289" spans="152:152">
       <c r="EV289" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="290" spans="152:152">
       <c r="EV290" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="291" spans="152:152">
       <c r="EV291" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="292" spans="152:152">
       <c r="EV292" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="293" spans="152:152">
       <c r="EV293" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="294" spans="152:152">
       <c r="EV294" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000031/metadata_template_ERC000031.xlsx
+++ b/templates/ERC000031/metadata_template_ERC000031.xlsx
@@ -26,7 +26,7 @@
     <definedName name="heatingandcoolingsystemtype">'cv_sample'!$AT$1:$AT$5</definedName>
     <definedName name="indoorspace">'cv_sample'!$AR$1:$AR$12</definedName>
     <definedName name="indoorsurface">'cv_sample'!$AQ$1:$AQ$9</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="1164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="1165">
   <si>
     <t>alias</t>
   </si>
@@ -745,6 +745,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -4070,7 +4073,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -4114,7 +4117,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -4141,7 +4144,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4878,6 +4881,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4899,27 +4907,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4939,122 +4947,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -5078,1320 +5086,1320 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="2" spans="1:220" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
   </sheetData>
@@ -6465,1982 +6473,1982 @@
   <sheetData>
     <row r="1" spans="8:167">
       <c r="H1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="X1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AQ1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AS1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AT1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AU1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AV1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AW1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AX1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AY1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="BC1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="BL1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="EV1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="FK1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="2" spans="8:167">
       <c r="H2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AQ2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AR2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AS2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AT2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AU2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AV2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AW2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AX2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AY2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="BC2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="BL2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="EV2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="FK2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="3" spans="8:167">
       <c r="H3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="X3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AQ3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AR3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AS3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AT3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AU3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AV3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AW3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AX3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="BC3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="BL3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="EV3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="FK3" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="4" spans="8:167">
       <c r="H4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AQ4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AS4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AT4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AW4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AX4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="BL4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="EV4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="FK4" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="5" spans="8:167">
       <c r="H5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AQ5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AR5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AS5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AT5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AX5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="BL5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="EV5" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="FK5" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="6" spans="8:167">
       <c r="H6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AQ6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AR6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AS6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AX6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="BL6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="EV6" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="7" spans="8:167">
       <c r="H7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AP7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AR7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AS7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AX7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="BL7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="EV7" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8" spans="8:167">
       <c r="H8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AP8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AR8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AX8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="BL8" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="EV8" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="9" spans="8:167">
       <c r="H9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AR9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AX9" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="BL9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="EV9" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" spans="8:167">
       <c r="H10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AR10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AX10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="BL10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="EV10" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="8:167">
       <c r="H11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AR11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AX11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="BL11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="EV11" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="12" spans="8:167">
       <c r="H12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AR12" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AX12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="BL12" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="EV12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="13" spans="8:167">
       <c r="H13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AX13" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="BL13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="EV13" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="14" spans="8:167">
       <c r="H14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AX14" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="BL14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="EV14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="15" spans="8:167">
       <c r="H15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AX15" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="BL15" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="EV15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="16" spans="8:167">
       <c r="H16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AX16" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="BL16" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="EV16" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="17" spans="8:152">
       <c r="H17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AX17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="BL17" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="EV17" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="18" spans="8:152">
       <c r="H18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AX18" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="BL18" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="EV18" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="19" spans="8:152">
       <c r="H19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AX19" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="BL19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="EV19" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="20" spans="8:152">
       <c r="H20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AX20" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="BL20" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="EV20" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="21" spans="8:152">
       <c r="H21" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AX21" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="BL21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="EV21" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="22" spans="8:152">
       <c r="H22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="BL22" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="EV22" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="23" spans="8:152">
       <c r="H23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="BL23" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="EV23" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24" spans="8:152">
       <c r="H24" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BL24" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="EV24" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="25" spans="8:152">
       <c r="H25" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BL25" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="EV25" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="26" spans="8:152">
       <c r="H26" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BL26" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="EV26" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="27" spans="8:152">
       <c r="H27" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="BL27" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="EV27" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="28" spans="8:152">
       <c r="H28" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="EV28" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="29" spans="8:152">
       <c r="H29" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="EV29" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="30" spans="8:152">
       <c r="H30" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="EV30" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="31" spans="8:152">
       <c r="EV31" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="32" spans="8:152">
       <c r="EV32" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="33" spans="152:152">
       <c r="EV33" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="34" spans="152:152">
       <c r="EV34" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="35" spans="152:152">
       <c r="EV35" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="36" spans="152:152">
       <c r="EV36" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="37" spans="152:152">
       <c r="EV37" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="38" spans="152:152">
       <c r="EV38" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="39" spans="152:152">
       <c r="EV39" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="40" spans="152:152">
       <c r="EV40" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="41" spans="152:152">
       <c r="EV41" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="42" spans="152:152">
       <c r="EV42" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="43" spans="152:152">
       <c r="EV43" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="44" spans="152:152">
       <c r="EV44" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="45" spans="152:152">
       <c r="EV45" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="46" spans="152:152">
       <c r="EV46" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="47" spans="152:152">
       <c r="EV47" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="48" spans="152:152">
       <c r="EV48" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="49" spans="152:152">
       <c r="EV49" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="50" spans="152:152">
       <c r="EV50" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="51" spans="152:152">
       <c r="EV51" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="52" spans="152:152">
       <c r="EV52" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="53" spans="152:152">
       <c r="EV53" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="54" spans="152:152">
       <c r="EV54" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="55" spans="152:152">
       <c r="EV55" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="56" spans="152:152">
       <c r="EV56" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="57" spans="152:152">
       <c r="EV57" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="58" spans="152:152">
       <c r="EV58" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="59" spans="152:152">
       <c r="EV59" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="60" spans="152:152">
       <c r="EV60" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="61" spans="152:152">
       <c r="EV61" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="62" spans="152:152">
       <c r="EV62" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="63" spans="152:152">
       <c r="EV63" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="64" spans="152:152">
       <c r="EV64" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="65" spans="152:152">
       <c r="EV65" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="66" spans="152:152">
       <c r="EV66" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="67" spans="152:152">
       <c r="EV67" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="68" spans="152:152">
       <c r="EV68" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="69" spans="152:152">
       <c r="EV69" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="70" spans="152:152">
       <c r="EV70" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="71" spans="152:152">
       <c r="EV71" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="72" spans="152:152">
       <c r="EV72" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="73" spans="152:152">
       <c r="EV73" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="74" spans="152:152">
       <c r="EV74" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="75" spans="152:152">
       <c r="EV75" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="76" spans="152:152">
       <c r="EV76" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="77" spans="152:152">
       <c r="EV77" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="78" spans="152:152">
       <c r="EV78" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="79" spans="152:152">
       <c r="EV79" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="80" spans="152:152">
       <c r="EV80" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="81" spans="152:152">
       <c r="EV81" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="82" spans="152:152">
       <c r="EV82" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="83" spans="152:152">
       <c r="EV83" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="84" spans="152:152">
       <c r="EV84" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="85" spans="152:152">
       <c r="EV85" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="86" spans="152:152">
       <c r="EV86" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="87" spans="152:152">
       <c r="EV87" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="88" spans="152:152">
       <c r="EV88" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="89" spans="152:152">
       <c r="EV89" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="90" spans="152:152">
       <c r="EV90" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="91" spans="152:152">
       <c r="EV91" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="92" spans="152:152">
       <c r="EV92" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="93" spans="152:152">
       <c r="EV93" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="94" spans="152:152">
       <c r="EV94" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="95" spans="152:152">
       <c r="EV95" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="96" spans="152:152">
       <c r="EV96" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="97" spans="152:152">
       <c r="EV97" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="98" spans="152:152">
       <c r="EV98" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="99" spans="152:152">
       <c r="EV99" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="100" spans="152:152">
       <c r="EV100" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="101" spans="152:152">
       <c r="EV101" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="102" spans="152:152">
       <c r="EV102" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="103" spans="152:152">
       <c r="EV103" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="104" spans="152:152">
       <c r="EV104" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="105" spans="152:152">
       <c r="EV105" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="106" spans="152:152">
       <c r="EV106" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="107" spans="152:152">
       <c r="EV107" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="108" spans="152:152">
       <c r="EV108" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="109" spans="152:152">
       <c r="EV109" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="110" spans="152:152">
       <c r="EV110" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="111" spans="152:152">
       <c r="EV111" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="112" spans="152:152">
       <c r="EV112" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="113" spans="152:152">
       <c r="EV113" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="114" spans="152:152">
       <c r="EV114" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="115" spans="152:152">
       <c r="EV115" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="116" spans="152:152">
       <c r="EV116" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="117" spans="152:152">
       <c r="EV117" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="118" spans="152:152">
       <c r="EV118" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="119" spans="152:152">
       <c r="EV119" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="120" spans="152:152">
       <c r="EV120" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="121" spans="152:152">
       <c r="EV121" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="122" spans="152:152">
       <c r="EV122" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="123" spans="152:152">
       <c r="EV123" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="124" spans="152:152">
       <c r="EV124" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="125" spans="152:152">
       <c r="EV125" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="126" spans="152:152">
       <c r="EV126" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="127" spans="152:152">
       <c r="EV127" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="128" spans="152:152">
       <c r="EV128" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="129" spans="152:152">
       <c r="EV129" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="130" spans="152:152">
       <c r="EV130" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="131" spans="152:152">
       <c r="EV131" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="132" spans="152:152">
       <c r="EV132" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="133" spans="152:152">
       <c r="EV133" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="134" spans="152:152">
       <c r="EV134" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="135" spans="152:152">
       <c r="EV135" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="136" spans="152:152">
       <c r="EV136" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="137" spans="152:152">
       <c r="EV137" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="138" spans="152:152">
       <c r="EV138" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="139" spans="152:152">
       <c r="EV139" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="140" spans="152:152">
       <c r="EV140" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="141" spans="152:152">
       <c r="EV141" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="142" spans="152:152">
       <c r="EV142" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="143" spans="152:152">
       <c r="EV143" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="144" spans="152:152">
       <c r="EV144" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="145" spans="152:152">
       <c r="EV145" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="146" spans="152:152">
       <c r="EV146" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="147" spans="152:152">
       <c r="EV147" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="148" spans="152:152">
       <c r="EV148" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="149" spans="152:152">
       <c r="EV149" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="150" spans="152:152">
       <c r="EV150" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="151" spans="152:152">
       <c r="EV151" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="152" spans="152:152">
       <c r="EV152" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="153" spans="152:152">
       <c r="EV153" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="154" spans="152:152">
       <c r="EV154" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="155" spans="152:152">
       <c r="EV155" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="156" spans="152:152">
       <c r="EV156" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="157" spans="152:152">
       <c r="EV157" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="158" spans="152:152">
       <c r="EV158" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="159" spans="152:152">
       <c r="EV159" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="160" spans="152:152">
       <c r="EV160" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="161" spans="152:152">
       <c r="EV161" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="162" spans="152:152">
       <c r="EV162" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="163" spans="152:152">
       <c r="EV163" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="164" spans="152:152">
       <c r="EV164" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="165" spans="152:152">
       <c r="EV165" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="166" spans="152:152">
       <c r="EV166" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="167" spans="152:152">
       <c r="EV167" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="168" spans="152:152">
       <c r="EV168" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="169" spans="152:152">
       <c r="EV169" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="170" spans="152:152">
       <c r="EV170" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="171" spans="152:152">
       <c r="EV171" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="172" spans="152:152">
       <c r="EV172" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="173" spans="152:152">
       <c r="EV173" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="174" spans="152:152">
       <c r="EV174" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="175" spans="152:152">
       <c r="EV175" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="176" spans="152:152">
       <c r="EV176" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="177" spans="152:152">
       <c r="EV177" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="178" spans="152:152">
       <c r="EV178" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="179" spans="152:152">
       <c r="EV179" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="180" spans="152:152">
       <c r="EV180" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="181" spans="152:152">
       <c r="EV181" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="182" spans="152:152">
       <c r="EV182" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="183" spans="152:152">
       <c r="EV183" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="184" spans="152:152">
       <c r="EV184" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="185" spans="152:152">
       <c r="EV185" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="186" spans="152:152">
       <c r="EV186" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="187" spans="152:152">
       <c r="EV187" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="188" spans="152:152">
       <c r="EV188" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="189" spans="152:152">
       <c r="EV189" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="190" spans="152:152">
       <c r="EV190" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="191" spans="152:152">
       <c r="EV191" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="192" spans="152:152">
       <c r="EV192" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="193" spans="152:152">
       <c r="EV193" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="194" spans="152:152">
       <c r="EV194" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="195" spans="152:152">
       <c r="EV195" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="196" spans="152:152">
       <c r="EV196" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="197" spans="152:152">
       <c r="EV197" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="198" spans="152:152">
       <c r="EV198" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="199" spans="152:152">
       <c r="EV199" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="200" spans="152:152">
       <c r="EV200" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="201" spans="152:152">
       <c r="EV201" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="202" spans="152:152">
       <c r="EV202" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="203" spans="152:152">
       <c r="EV203" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="204" spans="152:152">
       <c r="EV204" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="205" spans="152:152">
       <c r="EV205" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="206" spans="152:152">
       <c r="EV206" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="207" spans="152:152">
       <c r="EV207" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="208" spans="152:152">
       <c r="EV208" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="209" spans="152:152">
       <c r="EV209" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="210" spans="152:152">
       <c r="EV210" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="211" spans="152:152">
       <c r="EV211" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="212" spans="152:152">
       <c r="EV212" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="213" spans="152:152">
       <c r="EV213" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="214" spans="152:152">
       <c r="EV214" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="215" spans="152:152">
       <c r="EV215" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="216" spans="152:152">
       <c r="EV216" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="217" spans="152:152">
       <c r="EV217" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="218" spans="152:152">
       <c r="EV218" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="219" spans="152:152">
       <c r="EV219" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="220" spans="152:152">
       <c r="EV220" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="221" spans="152:152">
       <c r="EV221" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="222" spans="152:152">
       <c r="EV222" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="223" spans="152:152">
       <c r="EV223" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="224" spans="152:152">
       <c r="EV224" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="225" spans="152:152">
       <c r="EV225" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="226" spans="152:152">
       <c r="EV226" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="227" spans="152:152">
       <c r="EV227" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="228" spans="152:152">
       <c r="EV228" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="229" spans="152:152">
       <c r="EV229" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="230" spans="152:152">
       <c r="EV230" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="231" spans="152:152">
       <c r="EV231" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="232" spans="152:152">
       <c r="EV232" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="233" spans="152:152">
       <c r="EV233" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="234" spans="152:152">
       <c r="EV234" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="235" spans="152:152">
       <c r="EV235" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="236" spans="152:152">
       <c r="EV236" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="237" spans="152:152">
       <c r="EV237" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="238" spans="152:152">
       <c r="EV238" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="239" spans="152:152">
       <c r="EV239" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="240" spans="152:152">
       <c r="EV240" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="241" spans="152:152">
       <c r="EV241" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="242" spans="152:152">
       <c r="EV242" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="243" spans="152:152">
       <c r="EV243" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="244" spans="152:152">
       <c r="EV244" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="245" spans="152:152">
       <c r="EV245" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="246" spans="152:152">
       <c r="EV246" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="247" spans="152:152">
       <c r="EV247" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="248" spans="152:152">
       <c r="EV248" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="249" spans="152:152">
       <c r="EV249" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="250" spans="152:152">
       <c r="EV250" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="251" spans="152:152">
       <c r="EV251" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="252" spans="152:152">
       <c r="EV252" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="253" spans="152:152">
       <c r="EV253" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="254" spans="152:152">
       <c r="EV254" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="255" spans="152:152">
       <c r="EV255" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="256" spans="152:152">
       <c r="EV256" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="257" spans="152:152">
       <c r="EV257" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="258" spans="152:152">
       <c r="EV258" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="259" spans="152:152">
       <c r="EV259" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="260" spans="152:152">
       <c r="EV260" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="261" spans="152:152">
       <c r="EV261" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="262" spans="152:152">
       <c r="EV262" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="263" spans="152:152">
       <c r="EV263" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="264" spans="152:152">
       <c r="EV264" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="265" spans="152:152">
       <c r="EV265" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="266" spans="152:152">
       <c r="EV266" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="267" spans="152:152">
       <c r="EV267" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="268" spans="152:152">
       <c r="EV268" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="269" spans="152:152">
       <c r="EV269" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="270" spans="152:152">
       <c r="EV270" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="271" spans="152:152">
       <c r="EV271" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="272" spans="152:152">
       <c r="EV272" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="273" spans="152:152">
       <c r="EV273" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="274" spans="152:152">
       <c r="EV274" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="275" spans="152:152">
       <c r="EV275" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="276" spans="152:152">
       <c r="EV276" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="277" spans="152:152">
       <c r="EV277" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="278" spans="152:152">
       <c r="EV278" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="279" spans="152:152">
       <c r="EV279" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="280" spans="152:152">
       <c r="EV280" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="281" spans="152:152">
       <c r="EV281" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="282" spans="152:152">
       <c r="EV282" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="283" spans="152:152">
       <c r="EV283" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="284" spans="152:152">
       <c r="EV284" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="285" spans="152:152">
       <c r="EV285" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="286" spans="152:152">
       <c r="EV286" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="287" spans="152:152">
       <c r="EV287" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="288" spans="152:152">
       <c r="EV288" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="289" spans="152:152">
       <c r="EV289" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="290" spans="152:152">
       <c r="EV290" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="291" spans="152:152">
       <c r="EV291" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="292" spans="152:152">
       <c r="EV292" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="293" spans="152:152">
       <c r="EV293" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="294" spans="152:152">
       <c r="EV294" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
   </sheetData>
